--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week01/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/go/1870067581</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/ganga/1879903219</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/with-me/1874015492</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/miss-that/1875987505</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/old-technology/1867531318</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/alice/1874333652</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/tonto/1879859729</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/mariah/1874948938</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/blackhole/1873882200</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/walk/1875008123</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/flammable/1879896026</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/gentleman/1876982929</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/nyx00/1878551807</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/helicopters/1870313516</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/my-loving/1875970777</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/beautiful/1864389804</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/control-freak/1859044257</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/done-for/1873391195</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/moonlight/1878731568</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/free/1872250568</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/mantis/1868686720</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/the-blade/1876388273</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/the-place/1869119815</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/facts/1878765800</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/me-you/1878168773</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/badman/1877577830</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/automatic/1875133428</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-01</v>
+        <v>2026-03-02</v>
       </c>
       <c r="E99" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L100"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought)</v>
+        <v>Dog</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
+        <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-02</v>
@@ -451,36 +451,36 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>The Mountain</v>
+        <v>Torn</v>
       </c>
       <c r="G2" t="str">
-        <v>4:57</v>
+        <v>2:37</v>
       </c>
       <c r="H2" t="str">
-        <v>Gorillaz</v>
+        <v>Cobrah</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
+        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237742</v>
+        <v>https://music.apple.com/us/album/dog/1871594546</v>
       </c>
       <c r="L2" t="str">
-        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought) - Gorillaz</v>
+        <v>Dog - Cobrah</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>GO</v>
+        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought)</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>https://music.apple.com/us/song/go/1870067581</v>
+        <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-02</v>
@@ -489,36 +489,36 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>DEADLINE - EP</v>
+        <v>The Mountain</v>
       </c>
       <c r="G3" t="str">
-        <v>3:15</v>
+        <v>4:57</v>
       </c>
       <c r="H3" t="str">
-        <v>BLACKPINK</v>
+        <v>Gorillaz</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
-        <v>https://music.apple.com/us/artist/blackpink/1141774019</v>
+        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
       </c>
       <c r="K3" t="str">
-        <v>https://music.apple.com/us/album/go/1870067304</v>
+        <v>https://music.apple.com/us/album/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237742</v>
       </c>
       <c r="L3" t="str">
-        <v>GO - BLACKPINK</v>
+        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought) - Gorillaz</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Risk It All</v>
+        <v>GO</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
+        <v>https://music.apple.com/us/song/go/1870067581</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-02</v>
@@ -527,36 +527,36 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>The Romantic</v>
+        <v>DEADLINE - EP</v>
       </c>
       <c r="G4" t="str">
-        <v>3:24</v>
+        <v>3:15</v>
       </c>
       <c r="H4" t="str">
-        <v>Bruno Mars</v>
+        <v>BLACKPINK</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/blackpink/1141774019</v>
       </c>
       <c r="K4" t="str">
-        <v>https://music.apple.com/us/album/risk-it-all/1866732792</v>
+        <v>https://music.apple.com/us/album/go/1870067304</v>
       </c>
       <c r="L4" t="str">
-        <v>Risk It All - Bruno Mars</v>
+        <v>GO - BLACKPINK</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>FEVER DREAM</v>
+        <v>Risk It All</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
+        <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-02</v>
@@ -565,36 +565,36 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>FEVER DREAM - Single</v>
+        <v>The Romantic</v>
       </c>
       <c r="G5" t="str">
-        <v>2:33</v>
+        <v>3:24</v>
       </c>
       <c r="H5" t="str">
-        <v>Alex Warren</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/fever-dream/1879983782</v>
+        <v>https://music.apple.com/us/album/risk-it-all/1866732792</v>
       </c>
       <c r="L5" t="str">
-        <v>FEVER DREAM - Alex Warren</v>
+        <v>Risk It All - Bruno Mars</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Nightingale Lane.</v>
+        <v>FEVER DREAM</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
+        <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-02</v>
@@ -603,36 +603,36 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>FEVER DREAM - Single</v>
       </c>
       <c r="G6" t="str">
-        <v>5:02</v>
+        <v>2:33</v>
       </c>
       <c r="H6" t="str">
-        <v>RAYE</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K6" t="str">
-        <v>https://music.apple.com/us/album/nightingale-lane/1871085677</v>
+        <v>https://music.apple.com/us/album/fever-dream/1879983782</v>
       </c>
       <c r="L6" t="str">
-        <v>Nightingale Lane. - RAYE</v>
+        <v>FEVER DREAM - Alex Warren</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Made It On Our Own</v>
+        <v>Nightingale Lane.</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
+        <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-02</v>
@@ -641,36 +641,36 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>Made It On Our Own - Single</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G7" t="str">
-        <v>2:49</v>
+        <v>5:02</v>
       </c>
       <c r="H7" t="str">
-        <v>Yeat</v>
+        <v>RAYE</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K7" t="str">
-        <v>https://music.apple.com/us/album/made-it-on-our-own/1880447179</v>
+        <v>https://music.apple.com/us/album/nightingale-lane/1871085677</v>
       </c>
       <c r="L7" t="str">
-        <v>Made It On Our Own - Yeat</v>
+        <v>Nightingale Lane. - RAYE</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ganga</v>
+        <v>Made It On Our Own</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>https://music.apple.com/us/song/ganga/1879903219</v>
+        <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-02</v>
@@ -679,36 +679,36 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>DINASTÍA (DELUXE)</v>
+        <v>Made It On Our Own - Single</v>
       </c>
       <c r="G8" t="str">
-        <v>2:45</v>
+        <v>2:49</v>
       </c>
       <c r="H8" t="str">
-        <v>Peso Pluma</v>
+        <v>Yeat</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
-        <v>https://music.apple.com/us/artist/peso-pluma/1500139475</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K8" t="str">
-        <v>https://music.apple.com/us/album/ganga/1879902711</v>
+        <v>https://music.apple.com/us/album/made-it-on-our-own/1880447179</v>
       </c>
       <c r="L8" t="str">
-        <v>ganga - Peso Pluma</v>
+        <v>Made It On Our Own - Yeat</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>WITH ME</v>
+        <v>ganga</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/with-me/1874015492</v>
+        <v>https://music.apple.com/us/song/ganga/1879903219</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-02</v>
@@ -717,36 +717,36 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>DINASTÍA (DELUXE)</v>
       </c>
       <c r="G9" t="str">
-        <v>3:03</v>
+        <v>2:45</v>
       </c>
       <c r="H9" t="str">
-        <v>John Summit</v>
+        <v>Peso Pluma</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/peso-pluma/1500139475</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/with-me/1874015470</v>
+        <v>https://music.apple.com/us/album/ganga/1879902711</v>
       </c>
       <c r="L9" t="str">
-        <v>WITH ME - John Summit</v>
+        <v>ganga - Peso Pluma</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Sorry... I Meant Tonight (Bonus)</v>
+        <v>WITH ME</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
+        <v>https://music.apple.com/us/song/with-me/1874015492</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-02</v>
@@ -755,36 +755,36 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>Cloud 9</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G10" t="str">
-        <v>3:33</v>
+        <v>3:03</v>
       </c>
       <c r="H10" t="str">
-        <v>Megan Moroney</v>
+        <v>John Summit</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K10" t="str">
-        <v>https://music.apple.com/us/album/sorry-i-meant-tonight-bonus/1880181535</v>
+        <v>https://music.apple.com/us/album/with-me/1874015470</v>
       </c>
       <c r="L10" t="str">
-        <v>Sorry... I Meant Tonight (Bonus) - Megan Moroney</v>
+        <v>WITH ME - John Summit</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Miss That</v>
+        <v>Sorry... I Meant Tonight (Bonus)</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/miss-that/1875987505</v>
+        <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-02</v>
@@ -793,36 +793,36 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>Miss That - Single</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G11" t="str">
-        <v>2:56</v>
+        <v>3:33</v>
       </c>
       <c r="H11" t="str">
-        <v>Naomi Sharon</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/miss-that/1875987504</v>
+        <v>https://music.apple.com/us/album/sorry-i-meant-tonight-bonus/1880181535</v>
       </c>
       <c r="L11" t="str">
-        <v>Miss That - Naomi Sharon</v>
+        <v>Sorry... I Meant Tonight (Bonus) - Megan Moroney</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>glass houses</v>
+        <v>Miss That</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
+        <v>https://music.apple.com/us/song/miss-that/1875987505</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-02</v>
@@ -831,36 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>ghosted - EP</v>
+        <v>Miss That - Single</v>
       </c>
       <c r="G12" t="str">
-        <v>2:09</v>
+        <v>2:56</v>
       </c>
       <c r="H12" t="str">
-        <v>Saint Harison</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
+        <v>https://music.apple.com/us/album/miss-that/1875987504</v>
       </c>
       <c r="L12" t="str">
-        <v>glass houses - Saint Harison</v>
+        <v>Miss That - Naomi Sharon</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>OLD TECHNOLOGY</v>
+        <v>glass houses</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
+        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-02</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G13" t="str">
-        <v>2:39</v>
+        <v>2:09</v>
       </c>
       <c r="H13" t="str">
-        <v>Slayyyter</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
+        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
       </c>
       <c r="L13" t="str">
-        <v>OLD TECHNOLOGY - Slayyyter</v>
+        <v>glass houses - Saint Harison</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ALICE</v>
+        <v>OLD TECHNOLOGY</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/alice/1874333652</v>
+        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-02</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>PAREIDOLIA - EP</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G14" t="str">
-        <v>4:39</v>
+        <v>2:39</v>
       </c>
       <c r="H14" t="str">
-        <v>Erin LeCount</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/alice/1874333566</v>
+        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
       </c>
       <c r="L14" t="str">
-        <v>ALICE - Erin LeCount</v>
+        <v>OLD TECHNOLOGY - Slayyyter</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Tiny Light</v>
+        <v>ALICE</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
+        <v>https://music.apple.com/us/song/alice/1874333652</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-02</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Tiny Light - Single</v>
+        <v>PAREIDOLIA - EP</v>
       </c>
       <c r="G15" t="str">
-        <v>3:27</v>
+        <v>4:39</v>
       </c>
       <c r="H15" t="str">
-        <v>SEVENTEEN</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
+        <v>https://music.apple.com/us/album/alice/1874333566</v>
       </c>
       <c r="L15" t="str">
-        <v>Tiny Light - SEVENTEEN</v>
+        <v>ALICE - Erin LeCount</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!)</v>
+        <v>Tiny Light</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
+        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-02</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
+        <v>Tiny Light - Single</v>
       </c>
       <c r="G16" t="str">
-        <v>2:50</v>
+        <v>3:27</v>
       </c>
       <c r="H16" t="str">
-        <v>aespa</v>
+        <v>SEVENTEEN</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
+        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
       </c>
       <c r="L16" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
+        <v>Tiny Light - SEVENTEEN</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>16 YEAR OLD DRANK</v>
+        <v>Keychain (FROM THE FILM K-POPS!)</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
+        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-02</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>It's Us Vol. 2</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
       </c>
       <c r="G17" t="str">
-        <v>3:23</v>
+        <v>2:50</v>
       </c>
       <c r="H17" t="str">
-        <v>Concrete Boys</v>
+        <v>aespa</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
+        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
       </c>
       <c r="L17" t="str">
-        <v>16 YEAR OLD DRANK - Concrete Boys</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>If I Leave</v>
+        <v>16 YEAR OLD DRANK</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
+        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-02</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>It's Us Vol. 2</v>
       </c>
       <c r="G18" t="str">
-        <v>3:00</v>
+        <v>3:23</v>
       </c>
       <c r="H18" t="str">
-        <v>Mitski</v>
+        <v>Concrete Boys</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
+        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
       </c>
       <c r="L18" t="str">
-        <v>If I Leave - Mitski</v>
+        <v>16 YEAR OLD DRANK - Concrete Boys</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Time Will Tell</v>
+        <v>If I Leave</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
+        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-02</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Time Will Tell - Single</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G19" t="str">
-        <v>3:04</v>
+        <v>3:00</v>
       </c>
       <c r="H19" t="str">
-        <v>Lee Brice</v>
+        <v>Mitski</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
+        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
       </c>
       <c r="L19" t="str">
-        <v>Time Will Tell - Lee Brice</v>
+        <v>If I Leave - Mitski</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>How I Get</v>
+        <v>Time Will Tell</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
+        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-02</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>Time Will Tell - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>3:39</v>
+        <v>3:04</v>
       </c>
       <c r="H20" t="str">
-        <v>Laufey</v>
+        <v>Lee Brice</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
+        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
       </c>
       <c r="L20" t="str">
-        <v>How I Get - Laufey</v>
+        <v>Time Will Tell - Lee Brice</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7)</v>
+        <v>How I Get</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
+        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-02</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
+        <v>A Matter of Time: The Final Hour</v>
       </c>
       <c r="G21" t="str">
-        <v>3:19</v>
+        <v>3:39</v>
       </c>
       <c r="H21" t="str">
-        <v>Jessie Murph</v>
+        <v>Laufey</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
+        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
+        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
       </c>
       <c r="L21" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
+        <v>How I Get - Laufey</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Tonto</v>
+        <v>Criminal (From the Original Motion Picture Scream 7)</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/tonto/1879859729</v>
+        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-02</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Tonto - Single</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>2:20</v>
+        <v>3:19</v>
       </c>
       <c r="H22" t="str">
-        <v>J Balvin</v>
+        <v>Jessie Murph</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/tonto/1879859725</v>
+        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
       </c>
       <c r="L22" t="str">
-        <v>Tonto - J Balvin</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>nothin lasts 4ever</v>
+        <v>Tonto</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
+        <v>https://music.apple.com/us/song/tonto/1879859729</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-02</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>nothin lasts 4ever - Single</v>
+        <v>Tonto - Single</v>
       </c>
       <c r="G23" t="str">
-        <v>2:41</v>
+        <v>2:20</v>
       </c>
       <c r="H23" t="str">
-        <v>BLOND:ISH</v>
+        <v>J Balvin</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
+        <v>https://music.apple.com/us/album/tonto/1879859725</v>
       </c>
       <c r="L23" t="str">
-        <v>nothin lasts 4ever - BLOND:ISH</v>
+        <v>Tonto - J Balvin</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>MUERDO Mi LENGUA</v>
+        <v>nothin lasts 4ever</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
+        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-02</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>MUERDO Mi LENGUA - Single</v>
+        <v>nothin lasts 4ever - Single</v>
       </c>
       <c r="G24" t="str">
-        <v>2:50</v>
+        <v>2:41</v>
       </c>
       <c r="H24" t="str">
-        <v>Bautiii</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
+        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
       </c>
       <c r="L24" t="str">
-        <v>MUERDO Mi LENGUA - Bautiii</v>
+        <v>nothin lasts 4ever - BLOND:ISH</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage]</v>
+        <v>MUERDO Mi LENGUA</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
+        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-02</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
+        <v>MUERDO Mi LENGUA - Single</v>
       </c>
       <c r="G25" t="str">
-        <v>3:41</v>
+        <v>2:50</v>
       </c>
       <c r="H25" t="str">
-        <v>Mýa</v>
+        <v>Bautiii</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
+        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
       </c>
       <c r="L25" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
+        <v>MUERDO Mi LENGUA - Bautiii</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Smugglers &amp; Scholars</v>
+        <v>ASAP (Remix) [feat. 21 Savage]</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
+        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-02</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>FENIAN</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
       </c>
       <c r="G26" t="str">
-        <v>3:11</v>
+        <v>3:41</v>
       </c>
       <c r="H26" t="str">
-        <v>Kneecap</v>
+        <v>Mýa</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
+        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
       </c>
       <c r="L26" t="str">
-        <v>Smugglers &amp; Scholars - Kneecap</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>What You Want</v>
+        <v>Smugglers &amp; Scholars</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-02</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>What You Want - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G27" t="str">
-        <v>3:08</v>
+        <v>3:11</v>
       </c>
       <c r="H27" t="str">
-        <v>Angèle</v>
+        <v>Kneecap</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
       </c>
       <c r="L27" t="str">
-        <v>What You Want - Angèle</v>
+        <v>Smugglers &amp; Scholars - Kneecap</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>psychokiller</v>
+        <v>What You Want</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
+        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-02</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>getting up to no good</v>
+        <v>What You Want - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>1:53</v>
+        <v>3:08</v>
       </c>
       <c r="H28" t="str">
-        <v>Artemas</v>
+        <v>Angèle</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
+        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
       </c>
       <c r="L28" t="str">
-        <v>psychokiller - Artemas</v>
+        <v>What You Want - Angèle</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>DISNEY PRINCESS</v>
+        <v>psychokiller</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
+        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-02</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>HADES</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G29" t="str">
-        <v>4:05</v>
+        <v>1:53</v>
       </c>
       <c r="H29" t="str">
-        <v>Melanie Martinez</v>
+        <v>Artemas</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
+        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
       </c>
       <c r="L29" t="str">
-        <v>DISNEY PRINCESS - Melanie Martinez</v>
+        <v>psychokiller - Artemas</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>mariah</v>
+        <v>DISNEY PRINCESS</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/mariah/1874948938</v>
+        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-02</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>songs i couldn't forget - EP</v>
+        <v>HADES</v>
       </c>
       <c r="G30" t="str">
-        <v>2:48</v>
+        <v>4:05</v>
       </c>
       <c r="H30" t="str">
-        <v>Lauv</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/mariah/1874948926</v>
+        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
       </c>
       <c r="L30" t="str">
-        <v>mariah - Lauv</v>
+        <v>DISNEY PRINCESS - Melanie Martinez</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>BLACKHOLE</v>
+        <v>mariah</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
+        <v>https://music.apple.com/us/song/mariah/1874948938</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-02</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>REVIVE+</v>
+        <v>songs i couldn't forget - EP</v>
       </c>
       <c r="G31" t="str">
-        <v>3:14</v>
+        <v>2:48</v>
       </c>
       <c r="H31" t="str">
-        <v>IVE</v>
+        <v>Lauv</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
+        <v>https://music.apple.com/us/album/mariah/1874948926</v>
       </c>
       <c r="L31" t="str">
-        <v>BLACKHOLE - IVE</v>
+        <v>mariah - Lauv</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Walk</v>
+        <v>BLACKHOLE</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/walk/1875008123</v>
+        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-02</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Walk - Single</v>
+        <v>REVIVE+</v>
       </c>
       <c r="G32" t="str">
-        <v>2:56</v>
+        <v>3:14</v>
       </c>
       <c r="H32" t="str">
-        <v>Skye Newman</v>
+        <v>IVE</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/walk/1875008118</v>
+        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
       </c>
       <c r="L32" t="str">
-        <v>Walk - Skye Newman</v>
+        <v>BLACKHOLE - IVE</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>FLAMMABLE</v>
+        <v>Walk</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/flammable/1879896026</v>
+        <v>https://music.apple.com/us/song/walk/1875008123</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-02</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>FLAMMABLE - Single</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>3:17</v>
+        <v>2:56</v>
       </c>
       <c r="H33" t="str">
-        <v>Swae Lee</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/flammable/1879896025</v>
+        <v>https://music.apple.com/us/album/walk/1875008118</v>
       </c>
       <c r="L33" t="str">
-        <v>FLAMMABLE - Swae Lee</v>
+        <v>Walk - Skye Newman</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>mutual destruction</v>
+        <v>FLAMMABLE</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
+        <v>https://music.apple.com/us/song/flammable/1879896026</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-02</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>mutual destruction - Single</v>
+        <v>FLAMMABLE - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>2:31</v>
+        <v>3:17</v>
       </c>
       <c r="H34" t="str">
-        <v>kenzie</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
+        <v>https://music.apple.com/us/album/flammable/1879896025</v>
       </c>
       <c r="L34" t="str">
-        <v>mutual destruction - kenzie</v>
+        <v>FLAMMABLE - Swae Lee</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Dear Worry</v>
+        <v>mutual destruction</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
+        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-02</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Dear Worry - Single</v>
+        <v>mutual destruction - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>3:01</v>
+        <v>2:31</v>
       </c>
       <c r="H35" t="str">
-        <v>Common People</v>
+        <v>kenzie</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
+        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
       </c>
       <c r="L35" t="str">
-        <v>Dear Worry - Common People</v>
+        <v>mutual destruction - kenzie</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Gentleman</v>
+        <v>Dear Worry</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
+        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-02</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Gentleman - Single</v>
+        <v>Dear Worry - Single</v>
       </c>
       <c r="G36" t="str">
-        <v>2:16</v>
+        <v>3:01</v>
       </c>
       <c r="H36" t="str">
-        <v>Towa Bird</v>
+        <v>Common People</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
+        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
       </c>
       <c r="L36" t="str">
-        <v>Gentleman - Towa Bird</v>
+        <v>Dear Worry - Common People</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>NYX00</v>
+        <v>Gentleman</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
+        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-02</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>NYX00 - Single</v>
+        <v>Gentleman - Single</v>
       </c>
       <c r="G37" t="str">
-        <v>3:00</v>
+        <v>2:16</v>
       </c>
       <c r="H37" t="str">
-        <v>Dei V</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
+        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
       </c>
       <c r="L37" t="str">
-        <v>NYX00 - Dei V</v>
+        <v>Gentleman - Towa Bird</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Helicopters</v>
+        <v>NYX00</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
+        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-02</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>HELP(2)</v>
+        <v>NYX00 - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>3:58</v>
+        <v>3:00</v>
       </c>
       <c r="H38" t="str">
-        <v>Ezra Collective</v>
+        <v>Dei V</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
+        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
       </c>
       <c r="L38" t="str">
-        <v>Helicopters - Ezra Collective</v>
+        <v>NYX00 - Dei V</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
+        <v>Helicopters</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
+        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-02</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Max Richter: Hamnet Live</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G39" t="str">
-        <v>4:58</v>
+        <v>3:58</v>
       </c>
       <c r="H39" t="str">
-        <v>Max Richter</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
+        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
       </c>
       <c r="L39" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
+        <v>Helicopters - Ezra Collective</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>It's You I Want</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
+        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-02</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
+        <v>Max Richter: Hamnet Live</v>
       </c>
       <c r="G40" t="str">
-        <v>1:39</v>
+        <v>4:58</v>
       </c>
       <c r="H40" t="str">
-        <v>Kris Bowers</v>
+        <v>Max Richter</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
+        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
+        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
       </c>
       <c r="L40" t="str">
-        <v>It's You I Want - Kris Bowers</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>If I Was With You</v>
+        <v>It's You I Want</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
+        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-02</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>If I Was With You - Single</v>
+        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
       </c>
       <c r="G41" t="str">
-        <v>3:25</v>
+        <v>1:39</v>
       </c>
       <c r="H41" t="str">
-        <v>Presley Regier</v>
+        <v>Kris Bowers</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
+        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
       </c>
       <c r="L41" t="str">
-        <v>If I Was With You - Presley Regier</v>
+        <v>It's You I Want - Kris Bowers</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Stay With Me</v>
+        <v>If I Was With You</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
+        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-02</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>If I Was With You - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>3:47</v>
+        <v>3:25</v>
       </c>
       <c r="H42" t="str">
-        <v>Nessa Barrett</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
+        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
       </c>
       <c r="L42" t="str">
-        <v>Stay With Me - Nessa Barrett</v>
+        <v>If I Was With You - Presley Regier</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>My Loving</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-02</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>My Loving - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G43" t="str">
-        <v>2:50</v>
+        <v>3:47</v>
       </c>
       <c r="H43" t="str">
-        <v>Sonny Fodera</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
       </c>
       <c r="L43" t="str">
-        <v>My Loving - Sonny Fodera</v>
+        <v>Stay With Me - Nessa Barrett</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Easy On The Eyes</v>
+        <v>My Loving</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
+        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-02</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Easy On The Eyes - Single</v>
+        <v>My Loving - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>3:44</v>
+        <v>2:50</v>
       </c>
       <c r="H44" t="str">
-        <v>Willow Avalon</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
+        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
       </c>
       <c r="L44" t="str">
-        <v>Easy On The Eyes - Willow Avalon</v>
+        <v>My Loving - Sonny Fodera</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Beautiful</v>
+        <v>Easy On The Eyes</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
+        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-02</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Let It Die Here</v>
+        <v>Easy On The Eyes - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>3:47</v>
+        <v>3:44</v>
       </c>
       <c r="H45" t="str">
-        <v>Linda Perry</v>
+        <v>Willow Avalon</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
+        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
       </c>
       <c r="L45" t="str">
-        <v>Beautiful - Linda Perry</v>
+        <v>Easy On The Eyes - Willow Avalon</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3")</v>
+        <v>Beautiful</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
+        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-02</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G46" t="str">
-        <v>4:34</v>
+        <v>3:47</v>
       </c>
       <c r="H46" t="str">
-        <v>Jason Segel</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
+        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
       </c>
       <c r="L46" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
+        <v>Beautiful - Linda Perry</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Control Freak</v>
+        <v>Nightswimming (from "Shrinking: Season 3")</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
+        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-02</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Control Freak - Single</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>2:53</v>
+        <v>4:34</v>
       </c>
       <c r="H47" t="str">
-        <v>Broadside</v>
+        <v>Jason Segel</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/broadside/169939373</v>
+        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
+        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
       </c>
       <c r="L47" t="str">
-        <v>Control Freak - Broadside</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Done For</v>
+        <v>Control Freak</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/done-for/1873391195</v>
+        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-02</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Done For - Single</v>
+        <v>Control Freak - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>2:33</v>
+        <v>2:53</v>
       </c>
       <c r="H48" t="str">
-        <v>Max McNown</v>
+        <v>Broadside</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/broadside/169939373</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/done-for/1873391193</v>
+        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
       </c>
       <c r="L48" t="str">
-        <v>Done For - Max McNown</v>
+        <v>Control Freak - Broadside</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Ready for the Ride</v>
+        <v>Done For</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
+        <v>https://music.apple.com/us/song/done-for/1873391195</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-02</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Ready for the Ride - Single</v>
+        <v>Done For - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>3:27</v>
+        <v>2:33</v>
       </c>
       <c r="H49" t="str">
-        <v>Sean Paul</v>
+        <v>Max McNown</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
+        <v>https://music.apple.com/us/album/done-for/1873391193</v>
       </c>
       <c r="L49" t="str">
-        <v>Ready for the Ride - Sean Paul</v>
+        <v>Done For - Max McNown</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>push the pipe</v>
+        <v>Ready for the Ride</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
+        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-02</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>HYPERYOUTH (afterparty)</v>
+        <v>Ready for the Ride - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>3:08</v>
+        <v>3:27</v>
       </c>
       <c r="H50" t="str">
-        <v>Joey Valence &amp; Brae</v>
+        <v>Sean Paul</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
+        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
+        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
       </c>
       <c r="L50" t="str">
-        <v>push the pipe - Joey Valence &amp; Brae</v>
+        <v>Ready for the Ride - Sean Paul</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>push the pipe</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-02</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>With No Due Respect</v>
+        <v>HYPERYOUTH (afterparty)</v>
       </c>
       <c r="G51" t="str">
-        <v>3:13</v>
+        <v>3:08</v>
       </c>
       <c r="H51" t="str">
-        <v>Foggieraw</v>
+        <v>Joey Valence &amp; Brae</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
       </c>
       <c r="L51" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>push the pipe - Joey Valence &amp; Brae</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Moonlight</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-02</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>McKenzie 2.0</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G52" t="str">
-        <v>2:00</v>
+        <v>3:13</v>
       </c>
       <c r="H52" t="str">
-        <v>FattMack</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L52" t="str">
-        <v>Moonlight - FattMack</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Boat Named After You</v>
+        <v>Moonlight</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
+        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-02</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Boat Named After You - Single</v>
+        <v>McKenzie 2.0</v>
       </c>
       <c r="G53" t="str">
-        <v>3:56</v>
+        <v>2:00</v>
       </c>
       <c r="H53" t="str">
-        <v>ERNEST</v>
+        <v>FattMack</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
+        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
       </c>
       <c r="L53" t="str">
-        <v>Boat Named After You - ERNEST</v>
+        <v>Moonlight - FattMack</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>fall into you</v>
+        <v>Boat Named After You</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
+        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-02</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>fall into you - Single</v>
+        <v>Boat Named After You - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>3:28</v>
+        <v>3:56</v>
       </c>
       <c r="H54" t="str">
-        <v>Camylio</v>
+        <v>ERNEST</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
+        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
       </c>
       <c r="L54" t="str">
-        <v>fall into you - Camylio</v>
+        <v>Boat Named After You - ERNEST</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Van Gogh</v>
+        <v>fall into you</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
+        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-02</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Tales of a Failed Shapeshifter</v>
+        <v>fall into you - Single</v>
       </c>
       <c r="G55" t="str">
-        <v>2:25</v>
+        <v>3:28</v>
       </c>
       <c r="H55" t="str">
-        <v>Em Beihold</v>
+        <v>Camylio</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
+        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
       </c>
       <c r="L55" t="str">
-        <v>Van Gogh - Em Beihold</v>
+        <v>fall into you - Camylio</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>popstar Nervous</v>
+        <v>Van Gogh</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
+        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-02</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>the rumors are true</v>
+        <v>Tales of a Failed Shapeshifter</v>
       </c>
       <c r="G56" t="str">
         <v>2:25</v>
       </c>
       <c r="H56" t="str">
-        <v>DC THE DON</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
+        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
       </c>
       <c r="L56" t="str">
-        <v>popstar Nervous - DC THE DON</v>
+        <v>Van Gogh - Em Beihold</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Free</v>
+        <v>popstar Nervous</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/free/1872250568</v>
+        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-02</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Free - Single</v>
+        <v>the rumors are true</v>
       </c>
       <c r="G57" t="str">
-        <v>3:08</v>
+        <v>2:25</v>
       </c>
       <c r="H57" t="str">
-        <v>Beartooth</v>
+        <v>DC THE DON</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/free/1872250308</v>
+        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
       </c>
       <c r="L57" t="str">
-        <v>Free - Beartooth</v>
+        <v>popstar Nervous - DC THE DON</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>never come never morning</v>
+        <v>Free</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
+        <v>https://music.apple.com/us/song/free/1872250568</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-02</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>a short history of decay</v>
+        <v>Free - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:39</v>
+        <v>3:08</v>
       </c>
       <c r="H58" t="str">
-        <v>Nothing</v>
+        <v>Beartooth</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/nothing/593213453</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
+        <v>https://music.apple.com/us/album/free/1872250308</v>
       </c>
       <c r="L58" t="str">
-        <v>never come never morning - Nothing</v>
+        <v>Free - Beartooth</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Over My Head</v>
+        <v>never come never morning</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
+        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-02</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>A Beautiful Lie (20 Year Anniversary)</v>
+        <v>a short history of decay</v>
       </c>
       <c r="G59" t="str">
-        <v>2:28</v>
+        <v>3:39</v>
       </c>
       <c r="H59" t="str">
-        <v>Thirty Seconds to Mars</v>
+        <v>Nothing</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
+        <v>https://music.apple.com/us/artist/nothing/593213453</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
+        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
       </c>
       <c r="L59" t="str">
-        <v>Over My Head - Thirty Seconds to Mars</v>
+        <v>never come never morning - Nothing</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Mantis</v>
+        <v>Over My Head</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/mantis/1868686720</v>
+        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-02</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Creature of Habit</v>
+        <v>A Beautiful Lie (20 Year Anniversary)</v>
       </c>
       <c r="G60" t="str">
-        <v>4:40</v>
+        <v>2:28</v>
       </c>
       <c r="H60" t="str">
-        <v>Courtney Barnett</v>
+        <v>Thirty Seconds to Mars</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/mantis/1868686713</v>
+        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
       </c>
       <c r="L60" t="str">
-        <v>Mantis - Courtney Barnett</v>
+        <v>Over My Head - Thirty Seconds to Mars</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Soft Launch</v>
+        <v>Mantis</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
+        <v>https://music.apple.com/us/song/mantis/1868686720</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-02</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Soft Launch - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G61" t="str">
-        <v>2:25</v>
+        <v>4:40</v>
       </c>
       <c r="H61" t="str">
-        <v>Cely</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/cely/1259609505</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
+        <v>https://music.apple.com/us/album/mantis/1868686713</v>
       </c>
       <c r="L61" t="str">
-        <v>Soft Launch - Cely</v>
+        <v>Mantis - Courtney Barnett</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>picky choosy</v>
+        <v>Soft Launch</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
+        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-02</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Soft Launch - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>2:53</v>
+        <v>2:25</v>
       </c>
       <c r="H62" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Cely</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/cely/1259609505</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
+        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
       </c>
       <c r="L62" t="str">
-        <v>picky choosy - Chelsea Jordan</v>
+        <v>Soft Launch - Cely</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>La Mala Era Yo</v>
+        <v>picky choosy</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
+        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-02</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>La Mala Era Yo - Single</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G63" t="str">
-        <v>2:30</v>
+        <v>2:53</v>
       </c>
       <c r="H63" t="str">
-        <v>Kany García</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
+        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
       </c>
       <c r="L63" t="str">
-        <v>La Mala Era Yo - Kany García</v>
+        <v>picky choosy - Chelsea Jordan</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Quiet Part Loud</v>
+        <v>La Mala Era Yo</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
+        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-02</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Joy Next Door</v>
+        <v>La Mala Era Yo - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>3:08</v>
+        <v>2:30</v>
       </c>
       <c r="H64" t="str">
-        <v>The Maine</v>
+        <v>Kany García</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
+        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
       </c>
       <c r="L64" t="str">
-        <v>Quiet Part Loud - The Maine</v>
+        <v>La Mala Era Yo - Kany García</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>favorite girl</v>
+        <v>Quiet Part Loud</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
+        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-02</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>favorite girl - Single</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G65" t="str">
-        <v>3:24</v>
+        <v>3:08</v>
       </c>
       <c r="H65" t="str">
-        <v>Alaina Castillo</v>
+        <v>The Maine</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
+        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
       </c>
       <c r="L65" t="str">
-        <v>favorite girl - Alaina Castillo</v>
+        <v>Quiet Part Loud - The Maine</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>The Blade</v>
+        <v>favorite girl</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
+        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-02</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>The Blade - Single</v>
+        <v>favorite girl - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>3:15</v>
+        <v>3:24</v>
       </c>
       <c r="H66" t="str">
-        <v>Kingfishr</v>
+        <v>Alaina Castillo</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
+        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
       </c>
       <c r="L66" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>favorite girl - Alaina Castillo</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Blunt Force Blues</v>
+        <v>The Blade</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
+        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-02</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Into Oblivion</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>4:11</v>
+        <v>3:15</v>
       </c>
       <c r="H67" t="str">
-        <v>Lamb of God</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
+        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
       </c>
       <c r="L67" t="str">
-        <v>Blunt Force Blues - Lamb of God</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>The Black Scorpion</v>
+        <v>Blunt Force Blues</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
+        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-02</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>The Great Satan</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G68" t="str">
-        <v>1:33</v>
+        <v>4:11</v>
       </c>
       <c r="H68" t="str">
-        <v>Rob Zombie</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
+        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
       </c>
       <c r="L68" t="str">
-        <v>The Black Scorpion - Rob Zombie</v>
+        <v>Blunt Force Blues - Lamb of God</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>The Place</v>
+        <v>The Black Scorpion</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/the-place/1869119815</v>
+        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-02</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G69" t="str">
-        <v>5:58</v>
+        <v>1:33</v>
       </c>
       <c r="H69" t="str">
-        <v>Sepultura</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/the-place/1869119453</v>
+        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
       </c>
       <c r="L69" t="str">
-        <v>The Place - Sepultura</v>
+        <v>The Black Scorpion - Rob Zombie</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>SONG OF THE SWAMP</v>
+        <v>The Place</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
+        <v>https://music.apple.com/us/song/the-place/1869119815</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-02</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G70" t="str">
-        <v>3:18</v>
+        <v>5:58</v>
       </c>
       <c r="H70" t="str">
-        <v>Wage War</v>
+        <v>Sepultura</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
+        <v>https://music.apple.com/us/album/the-place/1869119453</v>
       </c>
       <c r="L70" t="str">
-        <v>SONG OF THE SWAMP - Wage War</v>
+        <v>The Place - Sepultura</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez)</v>
+        <v>SONG OF THE SWAMP</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
+        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-02</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G71" t="str">
-        <v>2:26</v>
+        <v>3:18</v>
       </c>
       <c r="H71" t="str">
-        <v>LOS DOS DE TAMAULIPAS</v>
+        <v>Wage War</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
+        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
       </c>
       <c r="L71" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
+        <v>SONG OF THE SWAMP - Wage War</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Tu Cárcel</v>
+        <v>Súper Snake (feat. Luis R Conriquez)</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
+        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-02</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Tu Cárcel - Single</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:36</v>
+        <v>2:26</v>
       </c>
       <c r="H72" t="str">
-        <v>Morat</v>
+        <v>LOS DOS DE TAMAULIPAS</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/morat/955657302</v>
+        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
+        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
       </c>
       <c r="L72" t="str">
-        <v>Tu Cárcel - Morat</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Facts</v>
+        <v>Tu Cárcel</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/facts/1878765800</v>
+        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-02</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>BE VERY AFRAID (Vol. 1)</v>
+        <v>Tu Cárcel - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>3:29</v>
+        <v>3:36</v>
       </c>
       <c r="H73" t="str">
-        <v>CHASE B</v>
+        <v>Morat</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
+        <v>https://music.apple.com/us/artist/morat/955657302</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/facts/1878765796</v>
+        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
       </c>
       <c r="L73" t="str">
-        <v>Facts - CHASE B</v>
+        <v>Tu Cárcel - Morat</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>me &amp; you</v>
+        <v>Facts</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/me-you/1878168773</v>
+        <v>https://music.apple.com/us/song/facts/1878765800</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-02</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>big country</v>
+        <v>BE VERY AFRAID (Vol. 1)</v>
       </c>
       <c r="G74" t="str">
-        <v>2:29</v>
+        <v>3:29</v>
       </c>
       <c r="H74" t="str">
-        <v>sosocamo</v>
+        <v>CHASE B</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
+        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/me-you/1878168770</v>
+        <v>https://music.apple.com/us/album/facts/1878765796</v>
       </c>
       <c r="L74" t="str">
-        <v>me &amp; you - sosocamo</v>
+        <v>Facts - CHASE B</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>badman</v>
+        <v>me &amp; you</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/badman/1877577830</v>
+        <v>https://music.apple.com/us/song/me-you/1878168773</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-02</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>badman - Single</v>
+        <v>big country</v>
       </c>
       <c r="G75" t="str">
-        <v>2:54</v>
+        <v>2:29</v>
       </c>
       <c r="H75" t="str">
-        <v>nomi.</v>
+        <v>sosocamo</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
+        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/badman/1877577829</v>
+        <v>https://music.apple.com/us/album/me-you/1878168770</v>
       </c>
       <c r="L75" t="str">
-        <v>badman - nomi.</v>
+        <v>me &amp; you - sosocamo</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Shut It Down</v>
+        <v>badman</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
+        <v>https://music.apple.com/us/song/badman/1877577830</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-02</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Shut It Down - Single</v>
+        <v>badman - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>2:26</v>
+        <v>2:54</v>
       </c>
       <c r="H76" t="str">
-        <v>TheARTI$t</v>
+        <v>nomi.</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
+        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
+        <v>https://music.apple.com/us/album/badman/1877577829</v>
       </c>
       <c r="L76" t="str">
-        <v>Shut It Down - TheARTI$t</v>
+        <v>badman - nomi.</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>AUTOMATIC</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/automatic/1875133428</v>
+        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-02</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>AUTOMATIC - Single</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>2:08</v>
+        <v>2:26</v>
       </c>
       <c r="H77" t="str">
-        <v>Hulvey</v>
+        <v>TheARTI$t</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/automatic/1875133426</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
       </c>
       <c r="L77" t="str">
-        <v>AUTOMATIC - Hulvey</v>
+        <v>Shut It Down - TheARTI$t</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Leaving Egypt</v>
+        <v>AUTOMATIC</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
+        <v>https://music.apple.com/us/song/automatic/1875133428</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-02</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Leaving Egypt - Single</v>
+        <v>AUTOMATIC - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>3:17</v>
+        <v>2:08</v>
       </c>
       <c r="H78" t="str">
-        <v>Alex Jude</v>
+        <v>Hulvey</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
+        <v>https://music.apple.com/us/album/automatic/1875133426</v>
       </c>
       <c r="L78" t="str">
-        <v>Leaving Egypt - Alex Jude</v>
+        <v>AUTOMATIC - Hulvey</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Not Your Mother</v>
+        <v>Leaving Egypt</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
+        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-02</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Not Your Mother - Single</v>
+        <v>Leaving Egypt - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:03</v>
+        <v>3:17</v>
       </c>
       <c r="H79" t="str">
-        <v>gracie</v>
+        <v>Alex Jude</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
+        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
+        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
       </c>
       <c r="L79" t="str">
-        <v>Not Your Mother - gracie</v>
+        <v>Leaving Egypt - Alex Jude</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
+        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-02</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>3:50</v>
+        <v>3:03</v>
       </c>
       <c r="H80" t="str">
-        <v>Social Distortion</v>
+        <v>gracie</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
+        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
       </c>
       <c r="L80" t="str">
-        <v>Born to Kill - Social Distortion</v>
+        <v>Not Your Mother - gracie</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>When the Love is Gone</v>
+        <v>Born to Kill</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
+        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-02</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>When the Love is Gone - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G81" t="str">
-        <v>3:20</v>
+        <v>3:50</v>
       </c>
       <c r="H81" t="str">
-        <v>Des Rocs</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
+        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
       </c>
       <c r="L81" t="str">
-        <v>When the Love is Gone - Des Rocs</v>
+        <v>Born to Kill - Social Distortion</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Miami Crest</v>
+        <v>When the Love is Gone</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
+        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-02</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Miami Crest - Single</v>
+        <v>When the Love is Gone - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>2:39</v>
+        <v>3:20</v>
       </c>
       <c r="H82" t="str">
-        <v>Namasenda</v>
+        <v>Des Rocs</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
+        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
+        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
       </c>
       <c r="L82" t="str">
-        <v>Miami Crest - Namasenda</v>
+        <v>When the Love is Gone - Des Rocs</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Say No Prayer</v>
+        <v>Miami Crest</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
+        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-02</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Say No Prayer - Single</v>
+        <v>Miami Crest - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>2:29</v>
+        <v>2:39</v>
       </c>
       <c r="H83" t="str">
-        <v>oskar med k</v>
+        <v>Namasenda</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
+        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
+        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
       </c>
       <c r="L83" t="str">
-        <v>Say No Prayer - oskar med k</v>
+        <v>Miami Crest - Namasenda</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>You Always Liked Me Better When I Was Stoned</v>
+        <v>Say No Prayer</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
+        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-02</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - Single</v>
+        <v>Say No Prayer - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>3:09</v>
+        <v>2:29</v>
       </c>
       <c r="H84" t="str">
-        <v>eee gee</v>
+        <v>oskar med k</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
+        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
+        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
       </c>
       <c r="L84" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
+        <v>Say No Prayer - oskar med k</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Pink Tongue</v>
+        <v>You Always Liked Me Better When I Was Stoned</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
+        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-02</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Porcelain Heart</v>
+        <v>You Always Liked Me Better When I Was Stoned - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:43</v>
+        <v>3:09</v>
       </c>
       <c r="H85" t="str">
-        <v>Diane Emerita</v>
+        <v>eee gee</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
+        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
+        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
       </c>
       <c r="L85" t="str">
-        <v>Pink Tongue - Diane Emerita</v>
+        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Hey, Bluebird</v>
+        <v>Pink Tongue</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
+        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-02</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Hey, Bluebird - Single</v>
+        <v>Porcelain Heart</v>
       </c>
       <c r="G86" t="str">
-        <v>3:23</v>
+        <v>3:43</v>
       </c>
       <c r="H86" t="str">
-        <v>Ber</v>
+        <v>Diane Emerita</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/ber/1020679397</v>
+        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
+        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
       </c>
       <c r="L86" t="str">
-        <v>Hey, Bluebird - Ber</v>
+        <v>Pink Tongue - Diane Emerita</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>You’ll Be The Proof</v>
+        <v>Hey, Bluebird</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
+        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-02</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>You’ll Be The Proof - Single</v>
+        <v>Hey, Bluebird - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>3:26</v>
+        <v>3:23</v>
       </c>
       <c r="H87" t="str">
-        <v>Forest Blakk</v>
+        <v>Ber</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
+        <v>https://music.apple.com/us/artist/ber/1020679397</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
+        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
       </c>
       <c r="L87" t="str">
-        <v>You’ll Be The Proof - Forest Blakk</v>
+        <v>Hey, Bluebird - Ber</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Heartbeat</v>
+        <v>You’ll Be The Proof</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
+        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-02</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Heartbeat - Single</v>
+        <v>You’ll Be The Proof - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>2:52</v>
+        <v>3:26</v>
       </c>
       <c r="H88" t="str">
-        <v>Lola Blue</v>
+        <v>Forest Blakk</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
+        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
       </c>
       <c r="L88" t="str">
-        <v>Heartbeat - Lola Blue</v>
+        <v>You’ll Be The Proof - Forest Blakk</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Imitation (how to become you)</v>
+        <v>Heartbeat</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
+        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-02</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Imitation (how to become you) - Single</v>
+        <v>Heartbeat - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>4:16</v>
+        <v>2:52</v>
       </c>
       <c r="H89" t="str">
-        <v>doggone</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
+        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
       </c>
       <c r="L89" t="str">
-        <v>Imitation (how to become you) - doggone</v>
+        <v>Heartbeat - Lola Blue</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>I’m Every Woman</v>
+        <v>Imitation (how to become you)</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
+        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-02</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Cover Girl - EP</v>
+        <v>Imitation (how to become you) - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>4:35</v>
+        <v>4:16</v>
       </c>
       <c r="H90" t="str">
-        <v>Ashley Jackson</v>
+        <v>doggone</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
+        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
+        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
       </c>
       <c r="L90" t="str">
-        <v>I’m Every Woman - Ashley Jackson</v>
+        <v>Imitation (how to become you) - doggone</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Hard To See (feat. Norah Jones)</v>
+        <v>I’m Every Woman</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
+        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-02</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Infinite Source Of Heat</v>
+        <v>Cover Girl - EP</v>
       </c>
       <c r="G91" t="str">
-        <v>2:46</v>
+        <v>4:35</v>
       </c>
       <c r="H91" t="str">
-        <v>Chris Morrissey</v>
+        <v>Ashley Jackson</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
+        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
+        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
       </c>
       <c r="L91" t="str">
-        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
+        <v>I’m Every Woman - Ashley Jackson</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Slow Tonight</v>
+        <v>Hard To See (feat. Norah Jones)</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
+        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-02</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Full Circle</v>
+        <v>Infinite Source Of Heat</v>
       </c>
       <c r="G92" t="str">
-        <v>3:12</v>
+        <v>2:46</v>
       </c>
       <c r="H92" t="str">
-        <v>Tom Misch</v>
+        <v>Chris Morrissey</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
+        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
       </c>
       <c r="L92" t="str">
-        <v>Slow Tonight - Tom Misch</v>
+        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Freak No More</v>
+        <v>Slow Tonight</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
+        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-02</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Freak No More - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G93" t="str">
-        <v>3:57</v>
+        <v>3:12</v>
       </c>
       <c r="H93" t="str">
-        <v>AC Slater</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
+        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
       </c>
       <c r="L93" t="str">
-        <v>Freak No More - AC Slater</v>
+        <v>Slow Tonight - Tom Misch</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Don't Stop</v>
+        <v>Freak No More</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
+        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-02</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Don't Stop - Single</v>
+        <v>Freak No More - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>2:55</v>
+        <v>3:57</v>
       </c>
       <c r="H94" t="str">
-        <v>HoneyLuv</v>
+        <v>AC Slater</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
+        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
+        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
       </c>
       <c r="L94" t="str">
-        <v>Don't Stop - HoneyLuv</v>
+        <v>Freak No More - AC Slater</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Cause I Do</v>
+        <v>Don't Stop</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
+        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-02</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Cause I Do - Single</v>
+        <v>Don't Stop - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>2:39</v>
+        <v>2:55</v>
       </c>
       <c r="H95" t="str">
-        <v>Preston Pablo</v>
+        <v>HoneyLuv</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
+        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
+        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
       </c>
       <c r="L95" t="str">
-        <v>Cause I Do - Preston Pablo</v>
+        <v>Don't Stop - HoneyLuv</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Morning Comes</v>
+        <v>Cause I Do</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
+        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-02</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Cause I Do - Single</v>
       </c>
       <c r="G96" t="str">
-        <v>4:11</v>
+        <v>2:39</v>
       </c>
       <c r="H96" t="str">
-        <v>Ty Myers</v>
+        <v>Preston Pablo</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
+        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
       </c>
       <c r="L96" t="str">
-        <v>Morning Comes - Ty Myers</v>
+        <v>Cause I Do - Preston Pablo</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>BETTER ON ME</v>
+        <v>Morning Comes</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
+        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-02</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>BETTER ON ME - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G97" t="str">
-        <v>3:24</v>
+        <v>4:11</v>
       </c>
       <c r="H97" t="str">
-        <v>Johnny Huynh</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
+        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
       </c>
       <c r="L97" t="str">
-        <v>BETTER ON ME - Johnny Huynh</v>
+        <v>Morning Comes - Ty Myers</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Speed or Perish</v>
+        <v>BETTER ON ME</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-02</v>
@@ -4099,68 +4099,106 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>Leather Temple</v>
+        <v>BETTER ON ME - Single</v>
       </c>
       <c r="G98" t="str">
-        <v>4:30</v>
+        <v>3:24</v>
       </c>
       <c r="H98" t="str">
-        <v>Carpenter Brut</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
       </c>
       <c r="L98" t="str">
-        <v>Speed or Perish - Carpenter Brut</v>
+        <v>BETTER ON ME - Johnny Huynh</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
+        <v>Speed or Perish</v>
+      </c>
+      <c r="B99" t="str">
+        <v/>
+      </c>
+      <c r="C99" t="str">
+        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+      </c>
+      <c r="D99" t="str">
+        <v>2026-03-02</v>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v>Leather Temple</v>
+      </c>
+      <c r="G99" t="str">
+        <v>4:30</v>
+      </c>
+      <c r="H99" t="str">
+        <v>Carpenter Brut</v>
+      </c>
+      <c r="I99" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J99" t="str">
+        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+      </c>
+      <c r="K99" t="str">
+        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+      </c>
+      <c r="L99" t="str">
+        <v>Speed or Perish - Carpenter Brut</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
         <v>The Scumbag Grift</v>
       </c>
-      <c r="B99" t="str">
-        <v/>
-      </c>
-      <c r="C99" t="str">
+      <c r="B100" t="str">
+        <v/>
+      </c>
+      <c r="C100" t="str">
         <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
       </c>
-      <c r="D99" t="str">
-        <v>2026-03-02</v>
-      </c>
-      <c r="E99" t="str">
-        <v/>
-      </c>
-      <c r="F99" t="str">
+      <c r="D100" t="str">
+        <v>2026-03-02</v>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
         <v>Cheap Heat</v>
       </c>
-      <c r="G99" t="str">
+      <c r="G100" t="str">
         <v>2:27</v>
       </c>
-      <c r="H99" t="str">
+      <c r="H100" t="str">
         <v>A Wilhelm Scream</v>
       </c>
-      <c r="I99" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J99" t="str">
+      <c r="I100" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J100" t="str">
         <v>https://music.apple.com/us/artist/a-wilhelm-scream/7375447</v>
       </c>
-      <c r="K99" t="str">
+      <c r="K100" t="str">
         <v>https://music.apple.com/us/album/the-scumbag-grift/1870588948</v>
       </c>
-      <c r="L99" t="str">
+      <c r="L100" t="str">
         <v>The Scumbag Grift - A Wilhelm Scream</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L99"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L100"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:L101"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/go/1870067581</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/ganga/1879903219</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/with-me/1874015492</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/miss-that/1875987505</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/old-technology/1867531318</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/alice/1874333652</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/tonto/1879859729</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/mariah/1874948938</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/blackhole/1873882200</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/walk/1875008123</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/flammable/1879896026</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1690,2515 +1690,2553 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>mutual destruction</v>
+        <v>3am (Remix)</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
+        <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>mutual destruction - Single</v>
+        <v>3am (Remix) - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>2:31</v>
+        <v>2:44</v>
       </c>
       <c r="H35" t="str">
-        <v>kenzie</v>
+        <v>Łaszewo</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/%C5%82aszewo/1438035296</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
+        <v>https://music.apple.com/us/album/3am-remix/1878278386</v>
       </c>
       <c r="L35" t="str">
-        <v>mutual destruction - kenzie</v>
+        <v>3am (Remix) - Łaszewo</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Dear Worry</v>
+        <v>mutual destruction</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
+        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Dear Worry - Single</v>
+        <v>mutual destruction - Single</v>
       </c>
       <c r="G36" t="str">
-        <v>3:01</v>
+        <v>2:31</v>
       </c>
       <c r="H36" t="str">
-        <v>Common People</v>
+        <v>kenzie</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
+        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
       </c>
       <c r="L36" t="str">
-        <v>Dear Worry - Common People</v>
+        <v>mutual destruction - kenzie</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Gentleman</v>
+        <v>Dear Worry</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
+        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Gentleman - Single</v>
+        <v>Dear Worry - Single</v>
       </c>
       <c r="G37" t="str">
-        <v>2:16</v>
+        <v>3:01</v>
       </c>
       <c r="H37" t="str">
-        <v>Towa Bird</v>
+        <v>Common People</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
+        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
       </c>
       <c r="L37" t="str">
-        <v>Gentleman - Towa Bird</v>
+        <v>Dear Worry - Common People</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>NYX00</v>
+        <v>Gentleman</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
+        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>NYX00 - Single</v>
+        <v>Gentleman - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>3:00</v>
+        <v>2:16</v>
       </c>
       <c r="H38" t="str">
-        <v>Dei V</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
+        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
       </c>
       <c r="L38" t="str">
-        <v>NYX00 - Dei V</v>
+        <v>Gentleman - Towa Bird</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Helicopters</v>
+        <v>NYX00</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
+        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>HELP(2)</v>
+        <v>NYX00 - Single</v>
       </c>
       <c r="G39" t="str">
-        <v>3:58</v>
+        <v>3:00</v>
       </c>
       <c r="H39" t="str">
-        <v>Ezra Collective</v>
+        <v>Dei V</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
+        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
       </c>
       <c r="L39" t="str">
-        <v>Helicopters - Ezra Collective</v>
+        <v>NYX00 - Dei V</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
+        <v>Helicopters</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
+        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Max Richter: Hamnet Live</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G40" t="str">
-        <v>4:58</v>
+        <v>3:58</v>
       </c>
       <c r="H40" t="str">
-        <v>Max Richter</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
+        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
       </c>
       <c r="L40" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
+        <v>Helicopters - Ezra Collective</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>It's You I Want</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
+        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
+        <v>Max Richter: Hamnet Live</v>
       </c>
       <c r="G41" t="str">
-        <v>1:39</v>
+        <v>4:58</v>
       </c>
       <c r="H41" t="str">
-        <v>Kris Bowers</v>
+        <v>Max Richter</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
+        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
+        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
       </c>
       <c r="L41" t="str">
-        <v>It's You I Want - Kris Bowers</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>If I Was With You</v>
+        <v>It's You I Want</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
+        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>If I Was With You - Single</v>
+        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
       </c>
       <c r="G42" t="str">
-        <v>3:25</v>
+        <v>1:39</v>
       </c>
       <c r="H42" t="str">
-        <v>Presley Regier</v>
+        <v>Kris Bowers</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
+        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
       </c>
       <c r="L42" t="str">
-        <v>If I Was With You - Presley Regier</v>
+        <v>It's You I Want - Kris Bowers</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Stay With Me</v>
+        <v>If I Was With You</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
+        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>If I Was With You - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>3:47</v>
+        <v>3:25</v>
       </c>
       <c r="H43" t="str">
-        <v>Nessa Barrett</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
+        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
       </c>
       <c r="L43" t="str">
-        <v>Stay With Me - Nessa Barrett</v>
+        <v>If I Was With You - Presley Regier</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>My Loving</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>My Loving - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G44" t="str">
-        <v>2:50</v>
+        <v>3:47</v>
       </c>
       <c r="H44" t="str">
-        <v>Sonny Fodera</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
       </c>
       <c r="L44" t="str">
-        <v>My Loving - Sonny Fodera</v>
+        <v>Stay With Me - Nessa Barrett</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Easy On The Eyes</v>
+        <v>My Loving</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
+        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Easy On The Eyes - Single</v>
+        <v>My Loving - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>3:44</v>
+        <v>2:50</v>
       </c>
       <c r="H45" t="str">
-        <v>Willow Avalon</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
+        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
       </c>
       <c r="L45" t="str">
-        <v>Easy On The Eyes - Willow Avalon</v>
+        <v>My Loving - Sonny Fodera</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Beautiful</v>
+        <v>Easy On The Eyes</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
+        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Let It Die Here</v>
+        <v>Easy On The Eyes - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>3:47</v>
+        <v>3:44</v>
       </c>
       <c r="H46" t="str">
-        <v>Linda Perry</v>
+        <v>Willow Avalon</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
+        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
       </c>
       <c r="L46" t="str">
-        <v>Beautiful - Linda Perry</v>
+        <v>Easy On The Eyes - Willow Avalon</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3")</v>
+        <v>Beautiful</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
+        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G47" t="str">
-        <v>4:34</v>
+        <v>3:47</v>
       </c>
       <c r="H47" t="str">
-        <v>Jason Segel</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
+        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
       </c>
       <c r="L47" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
+        <v>Beautiful - Linda Perry</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Control Freak</v>
+        <v>Nightswimming (from "Shrinking: Season 3")</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
+        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Control Freak - Single</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>2:53</v>
+        <v>4:34</v>
       </c>
       <c r="H48" t="str">
-        <v>Broadside</v>
+        <v>Jason Segel</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/broadside/169939373</v>
+        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
+        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
       </c>
       <c r="L48" t="str">
-        <v>Control Freak - Broadside</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Done For</v>
+        <v>Control Freak</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/done-for/1873391195</v>
+        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Done For - Single</v>
+        <v>Control Freak - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>2:33</v>
+        <v>2:53</v>
       </c>
       <c r="H49" t="str">
-        <v>Max McNown</v>
+        <v>Broadside</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/broadside/169939373</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/done-for/1873391193</v>
+        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
       </c>
       <c r="L49" t="str">
-        <v>Done For - Max McNown</v>
+        <v>Control Freak - Broadside</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Ready for the Ride</v>
+        <v>Done For</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
+        <v>https://music.apple.com/us/song/done-for/1873391195</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Ready for the Ride - Single</v>
+        <v>Done For - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>3:27</v>
+        <v>2:33</v>
       </c>
       <c r="H50" t="str">
-        <v>Sean Paul</v>
+        <v>Max McNown</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
+        <v>https://music.apple.com/us/album/done-for/1873391193</v>
       </c>
       <c r="L50" t="str">
-        <v>Ready for the Ride - Sean Paul</v>
+        <v>Done For - Max McNown</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>push the pipe</v>
+        <v>Ready for the Ride</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
+        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>HYPERYOUTH (afterparty)</v>
+        <v>Ready for the Ride - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>3:08</v>
+        <v>3:27</v>
       </c>
       <c r="H51" t="str">
-        <v>Joey Valence &amp; Brae</v>
+        <v>Sean Paul</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
+        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
+        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
       </c>
       <c r="L51" t="str">
-        <v>push the pipe - Joey Valence &amp; Brae</v>
+        <v>Ready for the Ride - Sean Paul</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>push the pipe</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>With No Due Respect</v>
+        <v>HYPERYOUTH (afterparty)</v>
       </c>
       <c r="G52" t="str">
-        <v>3:13</v>
+        <v>3:08</v>
       </c>
       <c r="H52" t="str">
-        <v>Foggieraw</v>
+        <v>Joey Valence &amp; Brae</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
       </c>
       <c r="L52" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>push the pipe - Joey Valence &amp; Brae</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Moonlight</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>McKenzie 2.0</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G53" t="str">
-        <v>2:00</v>
+        <v>3:13</v>
       </c>
       <c r="H53" t="str">
-        <v>FattMack</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L53" t="str">
-        <v>Moonlight - FattMack</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Boat Named After You</v>
+        <v>Moonlight</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
+        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Boat Named After You - Single</v>
+        <v>McKenzie 2.0</v>
       </c>
       <c r="G54" t="str">
-        <v>3:56</v>
+        <v>2:00</v>
       </c>
       <c r="H54" t="str">
-        <v>ERNEST</v>
+        <v>FattMack</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
+        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
       </c>
       <c r="L54" t="str">
-        <v>Boat Named After You - ERNEST</v>
+        <v>Moonlight - FattMack</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>fall into you</v>
+        <v>Boat Named After You</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
+        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>fall into you - Single</v>
+        <v>Boat Named After You - Single</v>
       </c>
       <c r="G55" t="str">
-        <v>3:28</v>
+        <v>3:56</v>
       </c>
       <c r="H55" t="str">
-        <v>Camylio</v>
+        <v>ERNEST</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
+        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
       </c>
       <c r="L55" t="str">
-        <v>fall into you - Camylio</v>
+        <v>Boat Named After You - ERNEST</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Van Gogh</v>
+        <v>fall into you</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
+        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Tales of a Failed Shapeshifter</v>
+        <v>fall into you - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>2:25</v>
+        <v>3:28</v>
       </c>
       <c r="H56" t="str">
-        <v>Em Beihold</v>
+        <v>Camylio</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
+        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
       </c>
       <c r="L56" t="str">
-        <v>Van Gogh - Em Beihold</v>
+        <v>fall into you - Camylio</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>popstar Nervous</v>
+        <v>Van Gogh</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
+        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>the rumors are true</v>
+        <v>Tales of a Failed Shapeshifter</v>
       </c>
       <c r="G57" t="str">
         <v>2:25</v>
       </c>
       <c r="H57" t="str">
-        <v>DC THE DON</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
+        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
       </c>
       <c r="L57" t="str">
-        <v>popstar Nervous - DC THE DON</v>
+        <v>Van Gogh - Em Beihold</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Free</v>
+        <v>popstar Nervous</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/free/1872250568</v>
+        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Free - Single</v>
+        <v>the rumors are true - EP</v>
       </c>
       <c r="G58" t="str">
-        <v>3:08</v>
+        <v>2:25</v>
       </c>
       <c r="H58" t="str">
-        <v>Beartooth</v>
+        <v>DC THE DON</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/free/1872250308</v>
+        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
       </c>
       <c r="L58" t="str">
-        <v>Free - Beartooth</v>
+        <v>popstar Nervous - DC THE DON</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>never come never morning</v>
+        <v>Free</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
+        <v>https://music.apple.com/us/song/free/1872250568</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>a short history of decay</v>
+        <v>Free - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>3:39</v>
+        <v>3:08</v>
       </c>
       <c r="H59" t="str">
-        <v>Nothing</v>
+        <v>Beartooth</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/nothing/593213453</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
+        <v>https://music.apple.com/us/album/free/1872250308</v>
       </c>
       <c r="L59" t="str">
-        <v>never come never morning - Nothing</v>
+        <v>Free - Beartooth</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Over My Head</v>
+        <v>never come never morning</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
+        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>A Beautiful Lie (20 Year Anniversary)</v>
+        <v>a short history of decay</v>
       </c>
       <c r="G60" t="str">
-        <v>2:28</v>
+        <v>3:39</v>
       </c>
       <c r="H60" t="str">
-        <v>Thirty Seconds to Mars</v>
+        <v>Nothing</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
+        <v>https://music.apple.com/us/artist/nothing/593213453</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
+        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
       </c>
       <c r="L60" t="str">
-        <v>Over My Head - Thirty Seconds to Mars</v>
+        <v>never come never morning - Nothing</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Mantis</v>
+        <v>Over My Head</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/mantis/1868686720</v>
+        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Creature of Habit</v>
+        <v>A Beautiful Lie (20 Year Anniversary)</v>
       </c>
       <c r="G61" t="str">
-        <v>4:40</v>
+        <v>2:28</v>
       </c>
       <c r="H61" t="str">
-        <v>Courtney Barnett</v>
+        <v>Thirty Seconds to Mars</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/mantis/1868686713</v>
+        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
       </c>
       <c r="L61" t="str">
-        <v>Mantis - Courtney Barnett</v>
+        <v>Over My Head - Thirty Seconds to Mars</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Soft Launch</v>
+        <v>Mantis</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
+        <v>https://music.apple.com/us/song/mantis/1868686720</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Soft Launch - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G62" t="str">
-        <v>2:25</v>
+        <v>4:40</v>
       </c>
       <c r="H62" t="str">
-        <v>Cely</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/cely/1259609505</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
+        <v>https://music.apple.com/us/album/mantis/1868686713</v>
       </c>
       <c r="L62" t="str">
-        <v>Soft Launch - Cely</v>
+        <v>Mantis - Courtney Barnett</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>picky choosy</v>
+        <v>Soft Launch</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
+        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Soft Launch - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>2:53</v>
+        <v>2:25</v>
       </c>
       <c r="H63" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Cely</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/cely/1259609505</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
+        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
       </c>
       <c r="L63" t="str">
-        <v>picky choosy - Chelsea Jordan</v>
+        <v>Soft Launch - Cely</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>La Mala Era Yo</v>
+        <v>picky choosy</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
+        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>La Mala Era Yo - Single</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G64" t="str">
-        <v>2:30</v>
+        <v>2:53</v>
       </c>
       <c r="H64" t="str">
-        <v>Kany García</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
+        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
       </c>
       <c r="L64" t="str">
-        <v>La Mala Era Yo - Kany García</v>
+        <v>picky choosy - Chelsea Jordan</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Quiet Part Loud</v>
+        <v>La Mala Era Yo</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
+        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Joy Next Door</v>
+        <v>La Mala Era Yo - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>3:08</v>
+        <v>2:30</v>
       </c>
       <c r="H65" t="str">
-        <v>The Maine</v>
+        <v>Kany García</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
+        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
       </c>
       <c r="L65" t="str">
-        <v>Quiet Part Loud - The Maine</v>
+        <v>La Mala Era Yo - Kany García</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>favorite girl</v>
+        <v>Quiet Part Loud</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
+        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>favorite girl - Single</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G66" t="str">
-        <v>3:24</v>
+        <v>3:08</v>
       </c>
       <c r="H66" t="str">
-        <v>Alaina Castillo</v>
+        <v>The Maine</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
+        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
       </c>
       <c r="L66" t="str">
-        <v>favorite girl - Alaina Castillo</v>
+        <v>Quiet Part Loud - The Maine</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>The Blade</v>
+        <v>favorite girl</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
+        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>The Blade - Single</v>
+        <v>favorite girl - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>3:15</v>
+        <v>3:24</v>
       </c>
       <c r="H67" t="str">
-        <v>Kingfishr</v>
+        <v>Alaina Castillo</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
+        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
       </c>
       <c r="L67" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>favorite girl - Alaina Castillo</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Blunt Force Blues</v>
+        <v>The Blade</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
+        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Into Oblivion</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>4:11</v>
+        <v>3:15</v>
       </c>
       <c r="H68" t="str">
-        <v>Lamb of God</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
+        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
       </c>
       <c r="L68" t="str">
-        <v>Blunt Force Blues - Lamb of God</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>The Black Scorpion</v>
+        <v>Blunt Force Blues</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
+        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>The Great Satan</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G69" t="str">
-        <v>1:33</v>
+        <v>4:11</v>
       </c>
       <c r="H69" t="str">
-        <v>Rob Zombie</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
+        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
       </c>
       <c r="L69" t="str">
-        <v>The Black Scorpion - Rob Zombie</v>
+        <v>Blunt Force Blues - Lamb of God</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>The Place</v>
+        <v>The Black Scorpion</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/the-place/1869119815</v>
+        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G70" t="str">
-        <v>5:58</v>
+        <v>1:33</v>
       </c>
       <c r="H70" t="str">
-        <v>Sepultura</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/the-place/1869119453</v>
+        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
       </c>
       <c r="L70" t="str">
-        <v>The Place - Sepultura</v>
+        <v>The Black Scorpion - Rob Zombie</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>SONG OF THE SWAMP</v>
+        <v>The Place</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
+        <v>https://music.apple.com/us/song/the-place/1869119815</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G71" t="str">
-        <v>3:18</v>
+        <v>5:58</v>
       </c>
       <c r="H71" t="str">
-        <v>Wage War</v>
+        <v>Sepultura</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
+        <v>https://music.apple.com/us/album/the-place/1869119453</v>
       </c>
       <c r="L71" t="str">
-        <v>SONG OF THE SWAMP - Wage War</v>
+        <v>The Place - Sepultura</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez)</v>
+        <v>SONG OF THE SWAMP</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
+        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G72" t="str">
-        <v>2:26</v>
+        <v>3:18</v>
       </c>
       <c r="H72" t="str">
-        <v>LOS DOS DE TAMAULIPAS</v>
+        <v>Wage War</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
+        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
       </c>
       <c r="L72" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
+        <v>SONG OF THE SWAMP - Wage War</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Tu Cárcel</v>
+        <v>Súper Snake (feat. Luis R Conriquez)</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
+        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Tu Cárcel - Single</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>3:36</v>
+        <v>2:26</v>
       </c>
       <c r="H73" t="str">
-        <v>Morat</v>
+        <v>LOS DOS DE TAMAULIPAS</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/morat/955657302</v>
+        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
+        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
       </c>
       <c r="L73" t="str">
-        <v>Tu Cárcel - Morat</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Facts</v>
+        <v>Tu Cárcel</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/facts/1878765800</v>
+        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>BE VERY AFRAID (Vol. 1)</v>
+        <v>Tu Cárcel - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>3:29</v>
+        <v>3:36</v>
       </c>
       <c r="H74" t="str">
-        <v>CHASE B</v>
+        <v>Morat</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
+        <v>https://music.apple.com/us/artist/morat/955657302</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/facts/1878765796</v>
+        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
       </c>
       <c r="L74" t="str">
-        <v>Facts - CHASE B</v>
+        <v>Tu Cárcel - Morat</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>me &amp; you</v>
+        <v>Facts</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/me-you/1878168773</v>
+        <v>https://music.apple.com/us/song/facts/1878765800</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>big country</v>
+        <v>BE VERY AFRAID (Vol. 1)</v>
       </c>
       <c r="G75" t="str">
-        <v>2:29</v>
+        <v>3:29</v>
       </c>
       <c r="H75" t="str">
-        <v>sosocamo</v>
+        <v>CHASE B</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
+        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/me-you/1878168770</v>
+        <v>https://music.apple.com/us/album/facts/1878765796</v>
       </c>
       <c r="L75" t="str">
-        <v>me &amp; you - sosocamo</v>
+        <v>Facts - CHASE B</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>badman</v>
+        <v>me &amp; you</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/badman/1877577830</v>
+        <v>https://music.apple.com/us/song/me-you/1878168773</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>badman - Single</v>
+        <v>big country</v>
       </c>
       <c r="G76" t="str">
-        <v>2:54</v>
+        <v>2:29</v>
       </c>
       <c r="H76" t="str">
-        <v>nomi.</v>
+        <v>sosocamo</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
+        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/badman/1877577829</v>
+        <v>https://music.apple.com/us/album/me-you/1878168770</v>
       </c>
       <c r="L76" t="str">
-        <v>badman - nomi.</v>
+        <v>me &amp; you - sosocamo</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Shut It Down</v>
+        <v>badman</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
+        <v>https://music.apple.com/us/song/badman/1877577830</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Shut It Down - Single</v>
+        <v>badman - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>2:26</v>
+        <v>2:54</v>
       </c>
       <c r="H77" t="str">
-        <v>TheARTI$t</v>
+        <v>nomi.</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
+        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
+        <v>https://music.apple.com/us/album/badman/1877577829</v>
       </c>
       <c r="L77" t="str">
-        <v>Shut It Down - TheARTI$t</v>
+        <v>badman - nomi.</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>AUTOMATIC</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/automatic/1875133428</v>
+        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>AUTOMATIC - Single</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>2:08</v>
+        <v>2:26</v>
       </c>
       <c r="H78" t="str">
-        <v>Hulvey</v>
+        <v>TheARTI$t</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/automatic/1875133426</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
       </c>
       <c r="L78" t="str">
-        <v>AUTOMATIC - Hulvey</v>
+        <v>Shut It Down - TheARTI$t</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Leaving Egypt</v>
+        <v>AUTOMATIC</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
+        <v>https://music.apple.com/us/song/automatic/1875133428</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Leaving Egypt - Single</v>
+        <v>AUTOMATIC - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:17</v>
+        <v>2:08</v>
       </c>
       <c r="H79" t="str">
-        <v>Alex Jude</v>
+        <v>Hulvey</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
+        <v>https://music.apple.com/us/album/automatic/1875133426</v>
       </c>
       <c r="L79" t="str">
-        <v>Leaving Egypt - Alex Jude</v>
+        <v>AUTOMATIC - Hulvey</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Not Your Mother</v>
+        <v>Leaving Egypt</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
+        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Not Your Mother - Single</v>
+        <v>Leaving Egypt - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>3:03</v>
+        <v>3:17</v>
       </c>
       <c r="H80" t="str">
-        <v>gracie</v>
+        <v>Alex Jude</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
+        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
+        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
       </c>
       <c r="L80" t="str">
-        <v>Not Your Mother - gracie</v>
+        <v>Leaving Egypt - Alex Jude</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
+        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>3:50</v>
+        <v>3:03</v>
       </c>
       <c r="H81" t="str">
-        <v>Social Distortion</v>
+        <v>gracie</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
+        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
       </c>
       <c r="L81" t="str">
-        <v>Born to Kill - Social Distortion</v>
+        <v>Not Your Mother - gracie</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>When the Love is Gone</v>
+        <v>Born to Kill</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
+        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>When the Love is Gone - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G82" t="str">
-        <v>3:20</v>
+        <v>3:50</v>
       </c>
       <c r="H82" t="str">
-        <v>Des Rocs</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
+        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
       </c>
       <c r="L82" t="str">
-        <v>When the Love is Gone - Des Rocs</v>
+        <v>Born to Kill - Social Distortion</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Miami Crest</v>
+        <v>When the Love is Gone</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
+        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Miami Crest - Single</v>
+        <v>When the Love is Gone - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>2:39</v>
+        <v>3:20</v>
       </c>
       <c r="H83" t="str">
-        <v>Namasenda</v>
+        <v>Des Rocs</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
+        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
+        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
       </c>
       <c r="L83" t="str">
-        <v>Miami Crest - Namasenda</v>
+        <v>When the Love is Gone - Des Rocs</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Say No Prayer</v>
+        <v>Miami Crest</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
+        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Say No Prayer - Single</v>
+        <v>Miami Crest - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>2:29</v>
+        <v>2:39</v>
       </c>
       <c r="H84" t="str">
-        <v>oskar med k</v>
+        <v>Namasenda</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
+        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
+        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
       </c>
       <c r="L84" t="str">
-        <v>Say No Prayer - oskar med k</v>
+        <v>Miami Crest - Namasenda</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>You Always Liked Me Better When I Was Stoned</v>
+        <v>Say No Prayer</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
+        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - Single</v>
+        <v>Say No Prayer - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:09</v>
+        <v>2:29</v>
       </c>
       <c r="H85" t="str">
-        <v>eee gee</v>
+        <v>oskar med k</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
+        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
+        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
       </c>
       <c r="L85" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
+        <v>Say No Prayer - oskar med k</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Pink Tongue</v>
+        <v>You Always Liked Me Better When I Was Stoned</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
+        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Porcelain Heart</v>
+        <v>You Always Liked Me Better When I Was Stoned - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>3:43</v>
+        <v>3:09</v>
       </c>
       <c r="H86" t="str">
-        <v>Diane Emerita</v>
+        <v>eee gee</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
+        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
+        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
       </c>
       <c r="L86" t="str">
-        <v>Pink Tongue - Diane Emerita</v>
+        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Hey, Bluebird</v>
+        <v>Pink Tongue</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
+        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Hey, Bluebird - Single</v>
+        <v>Porcelain Heart</v>
       </c>
       <c r="G87" t="str">
-        <v>3:23</v>
+        <v>3:43</v>
       </c>
       <c r="H87" t="str">
-        <v>Ber</v>
+        <v>Diane Emerita</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/ber/1020679397</v>
+        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
+        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
       </c>
       <c r="L87" t="str">
-        <v>Hey, Bluebird - Ber</v>
+        <v>Pink Tongue - Diane Emerita</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>You’ll Be The Proof</v>
+        <v>Hey, Bluebird</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
+        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>You’ll Be The Proof - Single</v>
+        <v>Hey, Bluebird - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>3:26</v>
+        <v>3:23</v>
       </c>
       <c r="H88" t="str">
-        <v>Forest Blakk</v>
+        <v>Ber</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
+        <v>https://music.apple.com/us/artist/ber/1020679397</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
+        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
       </c>
       <c r="L88" t="str">
-        <v>You’ll Be The Proof - Forest Blakk</v>
+        <v>Hey, Bluebird - Ber</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Heartbeat</v>
+        <v>You’ll Be The Proof</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
+        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Heartbeat - Single</v>
+        <v>You’ll Be The Proof - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>2:52</v>
+        <v>3:26</v>
       </c>
       <c r="H89" t="str">
-        <v>Lola Blue</v>
+        <v>Forest Blakk</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
+        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
       </c>
       <c r="L89" t="str">
-        <v>Heartbeat - Lola Blue</v>
+        <v>You’ll Be The Proof - Forest Blakk</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Imitation (how to become you)</v>
+        <v>Heartbeat</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
+        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Imitation (how to become you) - Single</v>
+        <v>Heartbeat - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>4:16</v>
+        <v>2:52</v>
       </c>
       <c r="H90" t="str">
-        <v>doggone</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
+        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
       </c>
       <c r="L90" t="str">
-        <v>Imitation (how to become you) - doggone</v>
+        <v>Heartbeat - Lola Blue</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>I’m Every Woman</v>
+        <v>Imitation (how to become you)</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
+        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Cover Girl - EP</v>
+        <v>Imitation (how to become you) - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>4:35</v>
+        <v>4:16</v>
       </c>
       <c r="H91" t="str">
-        <v>Ashley Jackson</v>
+        <v>doggone</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
+        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
+        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
       </c>
       <c r="L91" t="str">
-        <v>I’m Every Woman - Ashley Jackson</v>
+        <v>Imitation (how to become you) - doggone</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Hard To See (feat. Norah Jones)</v>
+        <v>I’m Every Woman</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
+        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Infinite Source Of Heat</v>
+        <v>Cover Girl - EP</v>
       </c>
       <c r="G92" t="str">
-        <v>2:46</v>
+        <v>4:35</v>
       </c>
       <c r="H92" t="str">
-        <v>Chris Morrissey</v>
+        <v>Ashley Jackson</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
+        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
+        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
       </c>
       <c r="L92" t="str">
-        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
+        <v>I’m Every Woman - Ashley Jackson</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Slow Tonight</v>
+        <v>Hard To See (feat. Norah Jones)</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
+        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Full Circle</v>
+        <v>Infinite Source Of Heat</v>
       </c>
       <c r="G93" t="str">
-        <v>3:12</v>
+        <v>2:46</v>
       </c>
       <c r="H93" t="str">
-        <v>Tom Misch</v>
+        <v>Chris Morrissey</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
+        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
       </c>
       <c r="L93" t="str">
-        <v>Slow Tonight - Tom Misch</v>
+        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Freak No More</v>
+        <v>Slow Tonight</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
+        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Freak No More - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G94" t="str">
-        <v>3:57</v>
+        <v>3:12</v>
       </c>
       <c r="H94" t="str">
-        <v>AC Slater</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
+        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
       </c>
       <c r="L94" t="str">
-        <v>Freak No More - AC Slater</v>
+        <v>Slow Tonight - Tom Misch</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Don't Stop</v>
+        <v>Freak No More</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
+        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Don't Stop - Single</v>
+        <v>Freak No More - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>2:55</v>
+        <v>3:57</v>
       </c>
       <c r="H95" t="str">
-        <v>HoneyLuv</v>
+        <v>AC Slater</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
+        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
+        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
       </c>
       <c r="L95" t="str">
-        <v>Don't Stop - HoneyLuv</v>
+        <v>Freak No More - AC Slater</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Cause I Do</v>
+        <v>Don't Stop</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
+        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Cause I Do - Single</v>
+        <v>Don't Stop - Single</v>
       </c>
       <c r="G96" t="str">
-        <v>2:39</v>
+        <v>2:55</v>
       </c>
       <c r="H96" t="str">
-        <v>Preston Pablo</v>
+        <v>HoneyLuv</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
+        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
+        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
       </c>
       <c r="L96" t="str">
-        <v>Cause I Do - Preston Pablo</v>
+        <v>Don't Stop - HoneyLuv</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Morning Comes</v>
+        <v>Cause I Do</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
+        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Cause I Do - Single</v>
       </c>
       <c r="G97" t="str">
-        <v>4:11</v>
+        <v>2:39</v>
       </c>
       <c r="H97" t="str">
-        <v>Ty Myers</v>
+        <v>Preston Pablo</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
+        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
       </c>
       <c r="L97" t="str">
-        <v>Morning Comes - Ty Myers</v>
+        <v>Cause I Do - Preston Pablo</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>BETTER ON ME</v>
+        <v>Morning Comes</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
+        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>BETTER ON ME - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G98" t="str">
-        <v>3:24</v>
+        <v>4:11</v>
       </c>
       <c r="H98" t="str">
-        <v>Johnny Huynh</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
+        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
       </c>
       <c r="L98" t="str">
-        <v>BETTER ON ME - Johnny Huynh</v>
+        <v>Morning Comes - Ty Myers</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Speed or Perish</v>
+        <v>BETTER ON ME</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-02</v>
+        <v>2026-03-03</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>Leather Temple</v>
+        <v>BETTER ON ME - Single</v>
       </c>
       <c r="G99" t="str">
-        <v>4:30</v>
+        <v>3:24</v>
       </c>
       <c r="H99" t="str">
-        <v>Carpenter Brut</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
       </c>
       <c r="L99" t="str">
-        <v>Speed or Perish - Carpenter Brut</v>
+        <v>BETTER ON ME - Johnny Huynh</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Speed or Perish</v>
+      </c>
+      <c r="B100" t="str">
+        <v/>
+      </c>
+      <c r="C100" t="str">
+        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+      </c>
+      <c r="D100" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v>Leather Temple</v>
+      </c>
+      <c r="G100" t="str">
+        <v>4:30</v>
+      </c>
+      <c r="H100" t="str">
+        <v>Carpenter Brut</v>
+      </c>
+      <c r="I100" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J100" t="str">
+        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+      </c>
+      <c r="K100" t="str">
+        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+      </c>
+      <c r="L100" t="str">
+        <v>Speed or Perish - Carpenter Brut</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
         <v>The Scumbag Grift</v>
       </c>
-      <c r="B100" t="str">
-        <v/>
-      </c>
-      <c r="C100" t="str">
+      <c r="B101" t="str">
+        <v/>
+      </c>
+      <c r="C101" t="str">
         <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
       </c>
-      <c r="D100" t="str">
-        <v>2026-03-02</v>
-      </c>
-      <c r="E100" t="str">
-        <v/>
-      </c>
-      <c r="F100" t="str">
+      <c r="D101" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
         <v>Cheap Heat</v>
       </c>
-      <c r="G100" t="str">
+      <c r="G101" t="str">
         <v>2:27</v>
       </c>
-      <c r="H100" t="str">
+      <c r="H101" t="str">
         <v>A Wilhelm Scream</v>
       </c>
-      <c r="I100" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J100" t="str">
+      <c r="I101" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J101" t="str">
         <v>https://music.apple.com/us/artist/a-wilhelm-scream/7375447</v>
       </c>
-      <c r="K100" t="str">
+      <c r="K101" t="str">
         <v>https://music.apple.com/us/album/the-scumbag-grift/1870588948</v>
       </c>
-      <c r="L100" t="str">
+      <c r="L101" t="str">
         <v>The Scumbag Grift - A Wilhelm Scream</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L101"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week01/titles.xlsx
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>BE VERY AFRAID (Vol. 1)</v>
+        <v>Be Very Afraid (Vol. 1)</v>
       </c>
       <c r="G75" t="str">
         <v>3:29</v>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L102"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Dog</v>
+        <v>SOMEWHERE ELSE</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/dog/1871594836</v>
+        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-03</v>
@@ -451,25 +451,25 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Torn</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G2" t="str">
-        <v>2:37</v>
+        <v>4:11</v>
       </c>
       <c r="H2" t="str">
-        <v>Cobrah</v>
+        <v>TOMORA</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/dog/1871594546</v>
+        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
       </c>
       <c r="L2" t="str">
-        <v>Dog - Cobrah</v>
+        <v>SOMEWHERE ELSE - TOMORA</v>
       </c>
     </row>
     <row r="3">
@@ -854,13 +854,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>glass houses</v>
+        <v>Dog</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
+        <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-03</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>ghosted - EP</v>
+        <v>Torn</v>
       </c>
       <c r="G13" t="str">
-        <v>2:09</v>
+        <v>2:37</v>
       </c>
       <c r="H13" t="str">
-        <v>Saint Harison</v>
+        <v>Cobrah</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
+        <v>https://music.apple.com/us/album/dog/1871594546</v>
       </c>
       <c r="L13" t="str">
-        <v>glass houses - Saint Harison</v>
+        <v>Dog - Cobrah</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>OLD TECHNOLOGY</v>
+        <v>glass houses</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
+        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-03</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G14" t="str">
-        <v>2:39</v>
+        <v>2:09</v>
       </c>
       <c r="H14" t="str">
-        <v>Slayyyter</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
+        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
       </c>
       <c r="L14" t="str">
-        <v>OLD TECHNOLOGY - Slayyyter</v>
+        <v>glass houses - Saint Harison</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ALICE</v>
+        <v>OLD TECHNOLOGY</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/alice/1874333652</v>
+        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-03</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>PAREIDOLIA - EP</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G15" t="str">
-        <v>4:39</v>
+        <v>2:39</v>
       </c>
       <c r="H15" t="str">
-        <v>Erin LeCount</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/alice/1874333566</v>
+        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
       </c>
       <c r="L15" t="str">
-        <v>ALICE - Erin LeCount</v>
+        <v>OLD TECHNOLOGY - Slayyyter</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Tiny Light</v>
+        <v>ALICE</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
+        <v>https://music.apple.com/us/song/alice/1874333652</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-03</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Tiny Light - Single</v>
+        <v>PAREIDOLIA - EP</v>
       </c>
       <c r="G16" t="str">
-        <v>3:27</v>
+        <v>4:39</v>
       </c>
       <c r="H16" t="str">
-        <v>SEVENTEEN</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
+        <v>https://music.apple.com/us/album/alice/1874333566</v>
       </c>
       <c r="L16" t="str">
-        <v>Tiny Light - SEVENTEEN</v>
+        <v>ALICE - Erin LeCount</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!)</v>
+        <v>Tiny Light</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
+        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-03</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
+        <v>Tiny Light - Single</v>
       </c>
       <c r="G17" t="str">
-        <v>2:50</v>
+        <v>3:27</v>
       </c>
       <c r="H17" t="str">
-        <v>aespa</v>
+        <v>SEVENTEEN</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
+        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
       </c>
       <c r="L17" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
+        <v>Tiny Light - SEVENTEEN</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>16 YEAR OLD DRANK</v>
+        <v>Keychain (FROM THE FILM K-POPS!)</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
+        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-03</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>It's Us Vol. 2</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>3:23</v>
+        <v>2:50</v>
       </c>
       <c r="H18" t="str">
-        <v>Concrete Boys</v>
+        <v>aespa</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
+        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
       </c>
       <c r="L18" t="str">
-        <v>16 YEAR OLD DRANK - Concrete Boys</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>If I Leave</v>
+        <v>16 YEAR OLD DRANK</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
+        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-03</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>It's Us Vol. 2</v>
       </c>
       <c r="G19" t="str">
-        <v>3:00</v>
+        <v>3:23</v>
       </c>
       <c r="H19" t="str">
-        <v>Mitski</v>
+        <v>Concrete Boys</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
+        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
       </c>
       <c r="L19" t="str">
-        <v>If I Leave - Mitski</v>
+        <v>16 YEAR OLD DRANK - Concrete Boys</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Time Will Tell</v>
+        <v>If I Leave</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
+        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-03</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Time Will Tell - Single</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G20" t="str">
-        <v>3:04</v>
+        <v>3:00</v>
       </c>
       <c r="H20" t="str">
-        <v>Lee Brice</v>
+        <v>Mitski</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
+        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
       </c>
       <c r="L20" t="str">
-        <v>Time Will Tell - Lee Brice</v>
+        <v>If I Leave - Mitski</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>How I Get</v>
+        <v>Time Will Tell</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
+        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-03</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>Time Will Tell - Single</v>
       </c>
       <c r="G21" t="str">
-        <v>3:39</v>
+        <v>3:04</v>
       </c>
       <c r="H21" t="str">
-        <v>Laufey</v>
+        <v>Lee Brice</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
+        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
       </c>
       <c r="L21" t="str">
-        <v>How I Get - Laufey</v>
+        <v>Time Will Tell - Lee Brice</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7)</v>
+        <v>How I Get</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
+        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-03</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
+        <v>A Matter of Time: The Final Hour</v>
       </c>
       <c r="G22" t="str">
-        <v>3:19</v>
+        <v>3:39</v>
       </c>
       <c r="H22" t="str">
-        <v>Jessie Murph</v>
+        <v>Laufey</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
+        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
+        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
       </c>
       <c r="L22" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
+        <v>How I Get - Laufey</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Tonto</v>
+        <v>Criminal (From the Original Motion Picture Scream 7)</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/tonto/1879859729</v>
+        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-03</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Tonto - Single</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
       </c>
       <c r="G23" t="str">
-        <v>2:20</v>
+        <v>3:19</v>
       </c>
       <c r="H23" t="str">
-        <v>J Balvin</v>
+        <v>Jessie Murph</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/tonto/1879859725</v>
+        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
       </c>
       <c r="L23" t="str">
-        <v>Tonto - J Balvin</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>nothin lasts 4ever</v>
+        <v>Tonto</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
+        <v>https://music.apple.com/us/song/tonto/1879859729</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-03</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>nothin lasts 4ever - Single</v>
+        <v>Tonto - Single</v>
       </c>
       <c r="G24" t="str">
-        <v>2:41</v>
+        <v>2:20</v>
       </c>
       <c r="H24" t="str">
-        <v>BLOND:ISH</v>
+        <v>J Balvin</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
+        <v>https://music.apple.com/us/album/tonto/1879859725</v>
       </c>
       <c r="L24" t="str">
-        <v>nothin lasts 4ever - BLOND:ISH</v>
+        <v>Tonto - J Balvin</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>MUERDO Mi LENGUA</v>
+        <v>nothin lasts 4ever</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
+        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-03</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>MUERDO Mi LENGUA - Single</v>
+        <v>nothin lasts 4ever - Single</v>
       </c>
       <c r="G25" t="str">
-        <v>2:50</v>
+        <v>2:41</v>
       </c>
       <c r="H25" t="str">
-        <v>Bautiii</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
+        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
       </c>
       <c r="L25" t="str">
-        <v>MUERDO Mi LENGUA - Bautiii</v>
+        <v>nothin lasts 4ever - BLOND:ISH</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage]</v>
+        <v>MUERDO Mi LENGUA</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
+        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-03</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
+        <v>MUERDO Mi LENGUA - Single</v>
       </c>
       <c r="G26" t="str">
-        <v>3:41</v>
+        <v>2:50</v>
       </c>
       <c r="H26" t="str">
-        <v>Mýa</v>
+        <v>Bautiii</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
+        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
       </c>
       <c r="L26" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
+        <v>MUERDO Mi LENGUA - Bautiii</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Smugglers &amp; Scholars</v>
+        <v>ASAP (Remix) [feat. 21 Savage]</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
+        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-03</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>FENIAN</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>3:11</v>
+        <v>3:41</v>
       </c>
       <c r="H27" t="str">
-        <v>Kneecap</v>
+        <v>Mýa</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
+        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
       </c>
       <c r="L27" t="str">
-        <v>Smugglers &amp; Scholars - Kneecap</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>What You Want</v>
+        <v>Smugglers &amp; Scholars</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-03</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>What You Want - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G28" t="str">
-        <v>3:08</v>
+        <v>3:11</v>
       </c>
       <c r="H28" t="str">
-        <v>Angèle</v>
+        <v>Kneecap</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
       </c>
       <c r="L28" t="str">
-        <v>What You Want - Angèle</v>
+        <v>Smugglers &amp; Scholars - Kneecap</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>psychokiller</v>
+        <v>What You Want</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
+        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-03</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>getting up to no good</v>
+        <v>What You Want - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>1:53</v>
+        <v>3:08</v>
       </c>
       <c r="H29" t="str">
-        <v>Artemas</v>
+        <v>Angèle</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
+        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
       </c>
       <c r="L29" t="str">
-        <v>psychokiller - Artemas</v>
+        <v>What You Want - Angèle</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>DISNEY PRINCESS</v>
+        <v>psychokiller</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
+        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-03</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>HADES</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G30" t="str">
-        <v>4:05</v>
+        <v>1:53</v>
       </c>
       <c r="H30" t="str">
-        <v>Melanie Martinez</v>
+        <v>Artemas</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
+        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
       </c>
       <c r="L30" t="str">
-        <v>DISNEY PRINCESS - Melanie Martinez</v>
+        <v>psychokiller - Artemas</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>mariah</v>
+        <v>DISNEY PRINCESS</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/mariah/1874948938</v>
+        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-03</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>songs i couldn't forget - EP</v>
+        <v>HADES</v>
       </c>
       <c r="G31" t="str">
-        <v>2:48</v>
+        <v>4:05</v>
       </c>
       <c r="H31" t="str">
-        <v>Lauv</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/mariah/1874948926</v>
+        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
       </c>
       <c r="L31" t="str">
-        <v>mariah - Lauv</v>
+        <v>DISNEY PRINCESS - Melanie Martinez</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>BLACKHOLE</v>
+        <v>mariah</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
+        <v>https://music.apple.com/us/song/mariah/1874948938</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-03</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>REVIVE+</v>
+        <v>songs i couldn't forget - EP</v>
       </c>
       <c r="G32" t="str">
-        <v>3:14</v>
+        <v>2:48</v>
       </c>
       <c r="H32" t="str">
-        <v>IVE</v>
+        <v>Lauv</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
+        <v>https://music.apple.com/us/album/mariah/1874948926</v>
       </c>
       <c r="L32" t="str">
-        <v>BLACKHOLE - IVE</v>
+        <v>mariah - Lauv</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Walk</v>
+        <v>BLACKHOLE</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/walk/1875008123</v>
+        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-03</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Walk - Single</v>
+        <v>REVIVE+</v>
       </c>
       <c r="G33" t="str">
-        <v>2:56</v>
+        <v>3:14</v>
       </c>
       <c r="H33" t="str">
-        <v>Skye Newman</v>
+        <v>IVE</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/walk/1875008118</v>
+        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
       </c>
       <c r="L33" t="str">
-        <v>Walk - Skye Newman</v>
+        <v>BLACKHOLE - IVE</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>FLAMMABLE</v>
+        <v>Walk</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/flammable/1879896026</v>
+        <v>https://music.apple.com/us/song/walk/1875008123</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-03</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>FLAMMABLE - Single</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>3:17</v>
+        <v>2:56</v>
       </c>
       <c r="H34" t="str">
-        <v>Swae Lee</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/flammable/1879896025</v>
+        <v>https://music.apple.com/us/album/walk/1875008118</v>
       </c>
       <c r="L34" t="str">
-        <v>FLAMMABLE - Swae Lee</v>
+        <v>Walk - Skye Newman</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>3am (Remix)</v>
+        <v>FLAMMABLE</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
+        <v>https://music.apple.com/us/song/flammable/1879896026</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-03</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3am (Remix) - Single</v>
+        <v>FLAMMABLE - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>2:44</v>
+        <v>3:17</v>
       </c>
       <c r="H35" t="str">
-        <v>Łaszewo</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/%C5%82aszewo/1438035296</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/3am-remix/1878278386</v>
+        <v>https://music.apple.com/us/album/flammable/1879896025</v>
       </c>
       <c r="L35" t="str">
-        <v>3am (Remix) - Łaszewo</v>
+        <v>FLAMMABLE - Swae Lee</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>mutual destruction</v>
+        <v>3am (Remix)</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
+        <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-03</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>mutual destruction - Single</v>
+        <v>3am (Remix) - Single</v>
       </c>
       <c r="G36" t="str">
-        <v>2:31</v>
+        <v>2:44</v>
       </c>
       <c r="H36" t="str">
-        <v>kenzie</v>
+        <v>Łaszewo</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/%C5%82aszewo/1438035296</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
+        <v>https://music.apple.com/us/album/3am-remix/1878278386</v>
       </c>
       <c r="L36" t="str">
-        <v>mutual destruction - kenzie</v>
+        <v>3am (Remix) - Łaszewo</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Dear Worry</v>
+        <v>mutual destruction</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
+        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-03</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Dear Worry - Single</v>
+        <v>mutual destruction - Single</v>
       </c>
       <c r="G37" t="str">
-        <v>3:01</v>
+        <v>2:31</v>
       </c>
       <c r="H37" t="str">
-        <v>Common People</v>
+        <v>kenzie</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
+        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
       </c>
       <c r="L37" t="str">
-        <v>Dear Worry - Common People</v>
+        <v>mutual destruction - kenzie</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Gentleman</v>
+        <v>Dear Worry</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
+        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-03</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Gentleman - Single</v>
+        <v>Dear Worry - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>2:16</v>
+        <v>3:01</v>
       </c>
       <c r="H38" t="str">
-        <v>Towa Bird</v>
+        <v>Common People</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
+        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
       </c>
       <c r="L38" t="str">
-        <v>Gentleman - Towa Bird</v>
+        <v>Dear Worry - Common People</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>NYX00</v>
+        <v>Gentleman</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
+        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-03</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>NYX00 - Single</v>
+        <v>Gentleman - Single</v>
       </c>
       <c r="G39" t="str">
-        <v>3:00</v>
+        <v>2:16</v>
       </c>
       <c r="H39" t="str">
-        <v>Dei V</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
+        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
       </c>
       <c r="L39" t="str">
-        <v>NYX00 - Dei V</v>
+        <v>Gentleman - Towa Bird</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Helicopters</v>
+        <v>NYX00</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
+        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-03</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>HELP(2)</v>
+        <v>NYX00 - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>3:58</v>
+        <v>3:00</v>
       </c>
       <c r="H40" t="str">
-        <v>Ezra Collective</v>
+        <v>Dei V</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
+        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
       </c>
       <c r="L40" t="str">
-        <v>Helicopters - Ezra Collective</v>
+        <v>NYX00 - Dei V</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
+        <v>Helicopters</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
+        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-03</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Max Richter: Hamnet Live</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G41" t="str">
-        <v>4:58</v>
+        <v>3:58</v>
       </c>
       <c r="H41" t="str">
-        <v>Max Richter</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
+        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
       </c>
       <c r="L41" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
+        <v>Helicopters - Ezra Collective</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>It's You I Want</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
+        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-03</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
+        <v>Max Richter: Hamnet Live</v>
       </c>
       <c r="G42" t="str">
-        <v>1:39</v>
+        <v>4:58</v>
       </c>
       <c r="H42" t="str">
-        <v>Kris Bowers</v>
+        <v>Max Richter</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
+        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
+        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
       </c>
       <c r="L42" t="str">
-        <v>It's You I Want - Kris Bowers</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>If I Was With You</v>
+        <v>It's You I Want</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
+        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-03</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>If I Was With You - Single</v>
+        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
       </c>
       <c r="G43" t="str">
-        <v>3:25</v>
+        <v>1:39</v>
       </c>
       <c r="H43" t="str">
-        <v>Presley Regier</v>
+        <v>Kris Bowers</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
+        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
       </c>
       <c r="L43" t="str">
-        <v>If I Was With You - Presley Regier</v>
+        <v>It's You I Want - Kris Bowers</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Stay With Me</v>
+        <v>If I Was With You</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
+        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-03</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>If I Was With You - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>3:47</v>
+        <v>3:25</v>
       </c>
       <c r="H44" t="str">
-        <v>Nessa Barrett</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
+        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
       </c>
       <c r="L44" t="str">
-        <v>Stay With Me - Nessa Barrett</v>
+        <v>If I Was With You - Presley Regier</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>My Loving</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-03</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>My Loving - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G45" t="str">
-        <v>2:50</v>
+        <v>3:47</v>
       </c>
       <c r="H45" t="str">
-        <v>Sonny Fodera</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
       </c>
       <c r="L45" t="str">
-        <v>My Loving - Sonny Fodera</v>
+        <v>Stay With Me - Nessa Barrett</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Easy On The Eyes</v>
+        <v>My Loving</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
+        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-03</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Easy On The Eyes - Single</v>
+        <v>My Loving - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>3:44</v>
+        <v>2:50</v>
       </c>
       <c r="H46" t="str">
-        <v>Willow Avalon</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
+        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
       </c>
       <c r="L46" t="str">
-        <v>Easy On The Eyes - Willow Avalon</v>
+        <v>My Loving - Sonny Fodera</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Beautiful</v>
+        <v>Easy On The Eyes</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
+        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-03</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Let It Die Here</v>
+        <v>Easy On The Eyes - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>3:47</v>
+        <v>3:44</v>
       </c>
       <c r="H47" t="str">
-        <v>Linda Perry</v>
+        <v>Willow Avalon</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
+        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
       </c>
       <c r="L47" t="str">
-        <v>Beautiful - Linda Perry</v>
+        <v>Easy On The Eyes - Willow Avalon</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3")</v>
+        <v>Beautiful</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
+        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-03</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G48" t="str">
-        <v>4:34</v>
+        <v>3:47</v>
       </c>
       <c r="H48" t="str">
-        <v>Jason Segel</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
+        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
       </c>
       <c r="L48" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
+        <v>Beautiful - Linda Perry</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Control Freak</v>
+        <v>Nightswimming (from "Shrinking: Season 3")</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
+        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-03</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Control Freak - Single</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>2:53</v>
+        <v>4:34</v>
       </c>
       <c r="H49" t="str">
-        <v>Broadside</v>
+        <v>Jason Segel</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/broadside/169939373</v>
+        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
+        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
       </c>
       <c r="L49" t="str">
-        <v>Control Freak - Broadside</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Done For</v>
+        <v>Control Freak</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/done-for/1873391195</v>
+        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-03</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Done For - Single</v>
+        <v>Control Freak - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>2:33</v>
+        <v>2:53</v>
       </c>
       <c r="H50" t="str">
-        <v>Max McNown</v>
+        <v>Broadside</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/broadside/169939373</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/done-for/1873391193</v>
+        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
       </c>
       <c r="L50" t="str">
-        <v>Done For - Max McNown</v>
+        <v>Control Freak - Broadside</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Ready for the Ride</v>
+        <v>Done For</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
+        <v>https://music.apple.com/us/song/done-for/1873391195</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-03</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Ready for the Ride - Single</v>
+        <v>Done For - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>3:27</v>
+        <v>2:33</v>
       </c>
       <c r="H51" t="str">
-        <v>Sean Paul</v>
+        <v>Max McNown</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
+        <v>https://music.apple.com/us/album/done-for/1873391193</v>
       </c>
       <c r="L51" t="str">
-        <v>Ready for the Ride - Sean Paul</v>
+        <v>Done For - Max McNown</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>push the pipe</v>
+        <v>Ready for the Ride</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
+        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-03</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>HYPERYOUTH (afterparty)</v>
+        <v>Ready for the Ride - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>3:08</v>
+        <v>3:27</v>
       </c>
       <c r="H52" t="str">
-        <v>Joey Valence &amp; Brae</v>
+        <v>Sean Paul</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
+        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
+        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
       </c>
       <c r="L52" t="str">
-        <v>push the pipe - Joey Valence &amp; Brae</v>
+        <v>Ready for the Ride - Sean Paul</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>push the pipe</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-03</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>With No Due Respect</v>
+        <v>HYPERYOUTH (afterparty)</v>
       </c>
       <c r="G53" t="str">
-        <v>3:13</v>
+        <v>3:08</v>
       </c>
       <c r="H53" t="str">
-        <v>Foggieraw</v>
+        <v>Joey Valence &amp; Brae</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
       </c>
       <c r="L53" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>push the pipe - Joey Valence &amp; Brae</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Moonlight</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-03</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>McKenzie 2.0</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G54" t="str">
-        <v>2:00</v>
+        <v>3:13</v>
       </c>
       <c r="H54" t="str">
-        <v>FattMack</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L54" t="str">
-        <v>Moonlight - FattMack</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Boat Named After You</v>
+        <v>Moonlight</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
+        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-03</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Boat Named After You - Single</v>
+        <v>McKenzie 2.0</v>
       </c>
       <c r="G55" t="str">
-        <v>3:56</v>
+        <v>2:00</v>
       </c>
       <c r="H55" t="str">
-        <v>ERNEST</v>
+        <v>FattMack</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
+        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
       </c>
       <c r="L55" t="str">
-        <v>Boat Named After You - ERNEST</v>
+        <v>Moonlight - FattMack</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>fall into you</v>
+        <v>Boat Named After You</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
+        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-03</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>fall into you - Single</v>
+        <v>Boat Named After You - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>3:28</v>
+        <v>3:56</v>
       </c>
       <c r="H56" t="str">
-        <v>Camylio</v>
+        <v>ERNEST</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
+        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
       </c>
       <c r="L56" t="str">
-        <v>fall into you - Camylio</v>
+        <v>Boat Named After You - ERNEST</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Van Gogh</v>
+        <v>fall into you</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
+        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-03</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Tales of a Failed Shapeshifter</v>
+        <v>fall into you - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>2:25</v>
+        <v>3:28</v>
       </c>
       <c r="H57" t="str">
-        <v>Em Beihold</v>
+        <v>Camylio</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
+        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
       </c>
       <c r="L57" t="str">
-        <v>Van Gogh - Em Beihold</v>
+        <v>fall into you - Camylio</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>popstar Nervous</v>
+        <v>Van Gogh</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
+        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-03</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>the rumors are true - EP</v>
+        <v>Tales of a Failed Shapeshifter</v>
       </c>
       <c r="G58" t="str">
         <v>2:25</v>
       </c>
       <c r="H58" t="str">
-        <v>DC THE DON</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
+        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
       </c>
       <c r="L58" t="str">
-        <v>popstar Nervous - DC THE DON</v>
+        <v>Van Gogh - Em Beihold</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Free</v>
+        <v>popstar Nervous</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/free/1872250568</v>
+        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-03</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Free - Single</v>
+        <v>the rumors are true - EP</v>
       </c>
       <c r="G59" t="str">
-        <v>3:08</v>
+        <v>2:25</v>
       </c>
       <c r="H59" t="str">
-        <v>Beartooth</v>
+        <v>DC THE DON</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/free/1872250308</v>
+        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
       </c>
       <c r="L59" t="str">
-        <v>Free - Beartooth</v>
+        <v>popstar Nervous - DC THE DON</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>never come never morning</v>
+        <v>Free</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
+        <v>https://music.apple.com/us/song/free/1872250568</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-03</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>a short history of decay</v>
+        <v>Free - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>3:39</v>
+        <v>3:08</v>
       </c>
       <c r="H60" t="str">
-        <v>Nothing</v>
+        <v>Beartooth</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/nothing/593213453</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
+        <v>https://music.apple.com/us/album/free/1872250308</v>
       </c>
       <c r="L60" t="str">
-        <v>never come never morning - Nothing</v>
+        <v>Free - Beartooth</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Over My Head</v>
+        <v>never come never morning</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
+        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-03</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>A Beautiful Lie (20 Year Anniversary)</v>
+        <v>a short history of decay</v>
       </c>
       <c r="G61" t="str">
-        <v>2:28</v>
+        <v>3:39</v>
       </c>
       <c r="H61" t="str">
-        <v>Thirty Seconds to Mars</v>
+        <v>Nothing</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
+        <v>https://music.apple.com/us/artist/nothing/593213453</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
+        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
       </c>
       <c r="L61" t="str">
-        <v>Over My Head - Thirty Seconds to Mars</v>
+        <v>never come never morning - Nothing</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Mantis</v>
+        <v>Over My Head</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/mantis/1868686720</v>
+        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-03</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Creature of Habit</v>
+        <v>A Beautiful Lie (20 Year Anniversary)</v>
       </c>
       <c r="G62" t="str">
-        <v>4:40</v>
+        <v>2:30</v>
       </c>
       <c r="H62" t="str">
-        <v>Courtney Barnett</v>
+        <v>Thirty Seconds to Mars</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/mantis/1868686713</v>
+        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
       </c>
       <c r="L62" t="str">
-        <v>Mantis - Courtney Barnett</v>
+        <v>Over My Head - Thirty Seconds to Mars</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Soft Launch</v>
+        <v>Mantis</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
+        <v>https://music.apple.com/us/song/mantis/1868686720</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-03</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Soft Launch - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G63" t="str">
-        <v>2:25</v>
+        <v>4:40</v>
       </c>
       <c r="H63" t="str">
-        <v>Cely</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/cely/1259609505</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
+        <v>https://music.apple.com/us/album/mantis/1868686713</v>
       </c>
       <c r="L63" t="str">
-        <v>Soft Launch - Cely</v>
+        <v>Mantis - Courtney Barnett</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>picky choosy</v>
+        <v>Soft Launch</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
+        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-03</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Soft Launch - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>2:53</v>
+        <v>2:25</v>
       </c>
       <c r="H64" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Cely</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/cely/1259609505</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
+        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
       </c>
       <c r="L64" t="str">
-        <v>picky choosy - Chelsea Jordan</v>
+        <v>Soft Launch - Cely</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>La Mala Era Yo</v>
+        <v>picky choosy</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
+        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-03</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>La Mala Era Yo - Single</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G65" t="str">
-        <v>2:30</v>
+        <v>2:53</v>
       </c>
       <c r="H65" t="str">
-        <v>Kany García</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
+        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
       </c>
       <c r="L65" t="str">
-        <v>La Mala Era Yo - Kany García</v>
+        <v>picky choosy - Chelsea Jordan</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Quiet Part Loud</v>
+        <v>La Mala Era Yo</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
+        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-03</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Joy Next Door</v>
+        <v>La Mala Era Yo - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>3:08</v>
+        <v>2:30</v>
       </c>
       <c r="H66" t="str">
-        <v>The Maine</v>
+        <v>Kany García</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
+        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
       </c>
       <c r="L66" t="str">
-        <v>Quiet Part Loud - The Maine</v>
+        <v>La Mala Era Yo - Kany García</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>favorite girl</v>
+        <v>Quiet Part Loud</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
+        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-03</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>favorite girl - Single</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G67" t="str">
-        <v>3:24</v>
+        <v>3:08</v>
       </c>
       <c r="H67" t="str">
-        <v>Alaina Castillo</v>
+        <v>The Maine</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
+        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
       </c>
       <c r="L67" t="str">
-        <v>favorite girl - Alaina Castillo</v>
+        <v>Quiet Part Loud - The Maine</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>The Blade</v>
+        <v>favorite girl</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
+        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-03</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>The Blade - Single</v>
+        <v>favorite girl - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>3:15</v>
+        <v>3:24</v>
       </c>
       <c r="H68" t="str">
-        <v>Kingfishr</v>
+        <v>Alaina Castillo</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
+        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
       </c>
       <c r="L68" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>favorite girl - Alaina Castillo</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Blunt Force Blues</v>
+        <v>The Blade</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
+        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-03</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Into Oblivion</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>4:11</v>
+        <v>3:15</v>
       </c>
       <c r="H69" t="str">
-        <v>Lamb of God</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
+        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
       </c>
       <c r="L69" t="str">
-        <v>Blunt Force Blues - Lamb of God</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>The Black Scorpion</v>
+        <v>Blunt Force Blues</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
+        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-03</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>The Great Satan</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G70" t="str">
-        <v>1:33</v>
+        <v>4:11</v>
       </c>
       <c r="H70" t="str">
-        <v>Rob Zombie</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
+        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
       </c>
       <c r="L70" t="str">
-        <v>The Black Scorpion - Rob Zombie</v>
+        <v>Blunt Force Blues - Lamb of God</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>The Place</v>
+        <v>The Black Scorpion</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/the-place/1869119815</v>
+        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-03</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G71" t="str">
-        <v>5:58</v>
+        <v>1:33</v>
       </c>
       <c r="H71" t="str">
-        <v>Sepultura</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/the-place/1869119453</v>
+        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
       </c>
       <c r="L71" t="str">
-        <v>The Place - Sepultura</v>
+        <v>The Black Scorpion - Rob Zombie</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>SONG OF THE SWAMP</v>
+        <v>The Place</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
+        <v>https://music.apple.com/us/song/the-place/1869119815</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-03</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G72" t="str">
-        <v>3:18</v>
+        <v>5:58</v>
       </c>
       <c r="H72" t="str">
-        <v>Wage War</v>
+        <v>Sepultura</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
+        <v>https://music.apple.com/us/album/the-place/1869119453</v>
       </c>
       <c r="L72" t="str">
-        <v>SONG OF THE SWAMP - Wage War</v>
+        <v>The Place - Sepultura</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez)</v>
+        <v>SONG OF THE SWAMP</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
+        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-03</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G73" t="str">
-        <v>2:26</v>
+        <v>3:18</v>
       </c>
       <c r="H73" t="str">
-        <v>LOS DOS DE TAMAULIPAS</v>
+        <v>Wage War</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
+        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
       </c>
       <c r="L73" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
+        <v>SONG OF THE SWAMP - Wage War</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Tu Cárcel</v>
+        <v>Súper Snake (feat. Luis R Conriquez)</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
+        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-03</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Tu Cárcel - Single</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>3:36</v>
+        <v>2:26</v>
       </c>
       <c r="H74" t="str">
-        <v>Morat</v>
+        <v>LOS DOS DE TAMAULIPAS</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/morat/955657302</v>
+        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
+        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
       </c>
       <c r="L74" t="str">
-        <v>Tu Cárcel - Morat</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Facts</v>
+        <v>Tu Cárcel</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/facts/1878765800</v>
+        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-03</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Be Very Afraid (Vol. 1)</v>
+        <v>Tu Cárcel - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>3:29</v>
+        <v>3:36</v>
       </c>
       <c r="H75" t="str">
-        <v>CHASE B</v>
+        <v>Morat</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
+        <v>https://music.apple.com/us/artist/morat/955657302</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/facts/1878765796</v>
+        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
       </c>
       <c r="L75" t="str">
-        <v>Facts - CHASE B</v>
+        <v>Tu Cárcel - Morat</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>me &amp; you</v>
+        <v>Facts</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/me-you/1878168773</v>
+        <v>https://music.apple.com/us/song/facts/1878765800</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-03</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>big country</v>
+        <v>Be Very Afraid (Vol. 1)</v>
       </c>
       <c r="G76" t="str">
-        <v>2:29</v>
+        <v>3:29</v>
       </c>
       <c r="H76" t="str">
-        <v>sosocamo</v>
+        <v>CHASE B</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
+        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/me-you/1878168770</v>
+        <v>https://music.apple.com/us/album/facts/1878765796</v>
       </c>
       <c r="L76" t="str">
-        <v>me &amp; you - sosocamo</v>
+        <v>Facts - CHASE B</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>badman</v>
+        <v>me &amp; you</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/badman/1877577830</v>
+        <v>https://music.apple.com/us/song/me-you/1878168773</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-03</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>badman - Single</v>
+        <v>big country</v>
       </c>
       <c r="G77" t="str">
-        <v>2:54</v>
+        <v>2:29</v>
       </c>
       <c r="H77" t="str">
-        <v>nomi.</v>
+        <v>sosocamo</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
+        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/badman/1877577829</v>
+        <v>https://music.apple.com/us/album/me-you/1878168770</v>
       </c>
       <c r="L77" t="str">
-        <v>badman - nomi.</v>
+        <v>me &amp; you - sosocamo</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Shut It Down</v>
+        <v>badman</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
+        <v>https://music.apple.com/us/song/badman/1877577830</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-03</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Shut It Down - Single</v>
+        <v>badman - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>2:26</v>
+        <v>2:54</v>
       </c>
       <c r="H78" t="str">
-        <v>TheARTI$t</v>
+        <v>nomi.</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
+        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
+        <v>https://music.apple.com/us/album/badman/1877577829</v>
       </c>
       <c r="L78" t="str">
-        <v>Shut It Down - TheARTI$t</v>
+        <v>badman - nomi.</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>AUTOMATIC</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/automatic/1875133428</v>
+        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-03</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>AUTOMATIC - Single</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>2:08</v>
+        <v>2:26</v>
       </c>
       <c r="H79" t="str">
-        <v>Hulvey</v>
+        <v>TheARTI$t</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/automatic/1875133426</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
       </c>
       <c r="L79" t="str">
-        <v>AUTOMATIC - Hulvey</v>
+        <v>Shut It Down - TheARTI$t</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Leaving Egypt</v>
+        <v>AUTOMATIC</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
+        <v>https://music.apple.com/us/song/automatic/1875133428</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-03</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Leaving Egypt - Single</v>
+        <v>AUTOMATIC - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>3:17</v>
+        <v>2:08</v>
       </c>
       <c r="H80" t="str">
-        <v>Alex Jude</v>
+        <v>Hulvey</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
+        <v>https://music.apple.com/us/album/automatic/1875133426</v>
       </c>
       <c r="L80" t="str">
-        <v>Leaving Egypt - Alex Jude</v>
+        <v>AUTOMATIC - Hulvey</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Not Your Mother</v>
+        <v>Leaving Egypt</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
+        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-03</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Not Your Mother - Single</v>
+        <v>Leaving Egypt - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>3:03</v>
+        <v>3:17</v>
       </c>
       <c r="H81" t="str">
-        <v>gracie</v>
+        <v>Alex Jude</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
+        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
+        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
       </c>
       <c r="L81" t="str">
-        <v>Not Your Mother - gracie</v>
+        <v>Leaving Egypt - Alex Jude</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
+        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-03</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>3:50</v>
+        <v>3:03</v>
       </c>
       <c r="H82" t="str">
-        <v>Social Distortion</v>
+        <v>gracie</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
+        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
       </c>
       <c r="L82" t="str">
-        <v>Born to Kill - Social Distortion</v>
+        <v>Not Your Mother - gracie</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>When the Love is Gone</v>
+        <v>Born to Kill</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
+        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-03</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>When the Love is Gone - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G83" t="str">
-        <v>3:20</v>
+        <v>3:50</v>
       </c>
       <c r="H83" t="str">
-        <v>Des Rocs</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
+        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
       </c>
       <c r="L83" t="str">
-        <v>When the Love is Gone - Des Rocs</v>
+        <v>Born to Kill - Social Distortion</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Miami Crest</v>
+        <v>When the Love is Gone</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
+        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-03</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Miami Crest - Single</v>
+        <v>When the Love is Gone - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>2:39</v>
+        <v>3:20</v>
       </c>
       <c r="H84" t="str">
-        <v>Namasenda</v>
+        <v>Des Rocs</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
+        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
+        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
       </c>
       <c r="L84" t="str">
-        <v>Miami Crest - Namasenda</v>
+        <v>When the Love is Gone - Des Rocs</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Say No Prayer</v>
+        <v>Miami Crest</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
+        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-03</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Say No Prayer - Single</v>
+        <v>Miami Crest - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>2:29</v>
+        <v>2:39</v>
       </c>
       <c r="H85" t="str">
-        <v>oskar med k</v>
+        <v>Namasenda</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
+        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
+        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
       </c>
       <c r="L85" t="str">
-        <v>Say No Prayer - oskar med k</v>
+        <v>Miami Crest - Namasenda</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>You Always Liked Me Better When I Was Stoned</v>
+        <v>Say No Prayer</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
+        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-03</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - Single</v>
+        <v>Say No Prayer - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>3:09</v>
+        <v>2:29</v>
       </c>
       <c r="H86" t="str">
-        <v>eee gee</v>
+        <v>oskar med k</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
+        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
+        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
       </c>
       <c r="L86" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
+        <v>Say No Prayer - oskar med k</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Pink Tongue</v>
+        <v>You Always Liked Me Better When I Was Stoned</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
+        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-03</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Porcelain Heart</v>
+        <v>You Always Liked Me Better When I Was Stoned - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>3:43</v>
+        <v>3:09</v>
       </c>
       <c r="H87" t="str">
-        <v>Diane Emerita</v>
+        <v>eee gee</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
+        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
+        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
       </c>
       <c r="L87" t="str">
-        <v>Pink Tongue - Diane Emerita</v>
+        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Hey, Bluebird</v>
+        <v>Pink Tongue</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
+        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-03</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Hey, Bluebird - Single</v>
+        <v>Porcelain Heart</v>
       </c>
       <c r="G88" t="str">
-        <v>3:23</v>
+        <v>3:43</v>
       </c>
       <c r="H88" t="str">
-        <v>Ber</v>
+        <v>Diane Emerita</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/ber/1020679397</v>
+        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
+        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
       </c>
       <c r="L88" t="str">
-        <v>Hey, Bluebird - Ber</v>
+        <v>Pink Tongue - Diane Emerita</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>You’ll Be The Proof</v>
+        <v>Hey, Bluebird</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
+        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-03</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>You’ll Be The Proof - Single</v>
+        <v>Hey, Bluebird - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>3:26</v>
+        <v>3:23</v>
       </c>
       <c r="H89" t="str">
-        <v>Forest Blakk</v>
+        <v>Ber</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
+        <v>https://music.apple.com/us/artist/ber/1020679397</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
+        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
       </c>
       <c r="L89" t="str">
-        <v>You’ll Be The Proof - Forest Blakk</v>
+        <v>Hey, Bluebird - Ber</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Heartbeat</v>
+        <v>You’ll Be The Proof</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
+        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-03</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Heartbeat - Single</v>
+        <v>You’ll Be The Proof - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>2:52</v>
+        <v>3:26</v>
       </c>
       <c r="H90" t="str">
-        <v>Lola Blue</v>
+        <v>Forest Blakk</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
+        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
       </c>
       <c r="L90" t="str">
-        <v>Heartbeat - Lola Blue</v>
+        <v>You’ll Be The Proof - Forest Blakk</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Imitation (how to become you)</v>
+        <v>Heartbeat</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
+        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-03</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Imitation (how to become you) - Single</v>
+        <v>Heartbeat - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>4:16</v>
+        <v>2:52</v>
       </c>
       <c r="H91" t="str">
-        <v>doggone</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
+        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
       </c>
       <c r="L91" t="str">
-        <v>Imitation (how to become you) - doggone</v>
+        <v>Heartbeat - Lola Blue</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>I’m Every Woman</v>
+        <v>Imitation (how to become you)</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
+        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-03</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Cover Girl - EP</v>
+        <v>Imitation (how to become you) - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>4:35</v>
+        <v>4:16</v>
       </c>
       <c r="H92" t="str">
-        <v>Ashley Jackson</v>
+        <v>doggone</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
+        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
+        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
       </c>
       <c r="L92" t="str">
-        <v>I’m Every Woman - Ashley Jackson</v>
+        <v>Imitation (how to become you) - doggone</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Hard To See (feat. Norah Jones)</v>
+        <v>I’m Every Woman</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
+        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-03</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Infinite Source Of Heat</v>
+        <v>Cover Girl - EP</v>
       </c>
       <c r="G93" t="str">
-        <v>2:46</v>
+        <v>4:35</v>
       </c>
       <c r="H93" t="str">
-        <v>Chris Morrissey</v>
+        <v>Ashley Jackson</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
+        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
+        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
       </c>
       <c r="L93" t="str">
-        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
+        <v>I’m Every Woman - Ashley Jackson</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Slow Tonight</v>
+        <v>Hard To See (feat. Norah Jones)</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
+        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-03</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Full Circle</v>
+        <v>Infinite Source Of Heat</v>
       </c>
       <c r="G94" t="str">
-        <v>3:12</v>
+        <v>2:46</v>
       </c>
       <c r="H94" t="str">
-        <v>Tom Misch</v>
+        <v>Chris Morrissey</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
+        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
       </c>
       <c r="L94" t="str">
-        <v>Slow Tonight - Tom Misch</v>
+        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Freak No More</v>
+        <v>Slow Tonight</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
+        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-03</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Freak No More - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G95" t="str">
-        <v>3:57</v>
+        <v>3:12</v>
       </c>
       <c r="H95" t="str">
-        <v>AC Slater</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
+        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
       </c>
       <c r="L95" t="str">
-        <v>Freak No More - AC Slater</v>
+        <v>Slow Tonight - Tom Misch</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Don't Stop</v>
+        <v>Freak No More</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
+        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-03</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Don't Stop - Single</v>
+        <v>Freak No More - Single</v>
       </c>
       <c r="G96" t="str">
-        <v>2:55</v>
+        <v>3:57</v>
       </c>
       <c r="H96" t="str">
-        <v>HoneyLuv</v>
+        <v>AC Slater</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
+        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
+        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
       </c>
       <c r="L96" t="str">
-        <v>Don't Stop - HoneyLuv</v>
+        <v>Freak No More - AC Slater</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Cause I Do</v>
+        <v>Don't Stop</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
+        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-03</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Cause I Do - Single</v>
+        <v>Don't Stop - Single</v>
       </c>
       <c r="G97" t="str">
-        <v>2:39</v>
+        <v>2:55</v>
       </c>
       <c r="H97" t="str">
-        <v>Preston Pablo</v>
+        <v>HoneyLuv</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
+        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
+        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
       </c>
       <c r="L97" t="str">
-        <v>Cause I Do - Preston Pablo</v>
+        <v>Don't Stop - HoneyLuv</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Morning Comes</v>
+        <v>Cause I Do</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
+        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-03</v>
@@ -4099,36 +4099,36 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Cause I Do - Single</v>
       </c>
       <c r="G98" t="str">
-        <v>4:11</v>
+        <v>2:39</v>
       </c>
       <c r="H98" t="str">
-        <v>Ty Myers</v>
+        <v>Preston Pablo</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
+        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
       </c>
       <c r="L98" t="str">
-        <v>Morning Comes - Ty Myers</v>
+        <v>Cause I Do - Preston Pablo</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>BETTER ON ME</v>
+        <v>Morning Comes</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
+        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-03</v>
@@ -4137,36 +4137,36 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>BETTER ON ME - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G99" t="str">
-        <v>3:24</v>
+        <v>4:11</v>
       </c>
       <c r="H99" t="str">
-        <v>Johnny Huynh</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
+        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
       </c>
       <c r="L99" t="str">
-        <v>BETTER ON ME - Johnny Huynh</v>
+        <v>Morning Comes - Ty Myers</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Speed or Perish</v>
+        <v>BETTER ON ME</v>
       </c>
       <c r="B100" t="str">
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-03</v>
@@ -4175,68 +4175,106 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>Leather Temple</v>
+        <v>BETTER ON ME - Single</v>
       </c>
       <c r="G100" t="str">
-        <v>4:30</v>
+        <v>3:24</v>
       </c>
       <c r="H100" t="str">
-        <v>Carpenter Brut</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
       </c>
       <c r="L100" t="str">
-        <v>Speed or Perish - Carpenter Brut</v>
+        <v>BETTER ON ME - Johnny Huynh</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
+        <v>Speed or Perish</v>
+      </c>
+      <c r="B101" t="str">
+        <v/>
+      </c>
+      <c r="C101" t="str">
+        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+      </c>
+      <c r="D101" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v>Leather Temple</v>
+      </c>
+      <c r="G101" t="str">
+        <v>4:30</v>
+      </c>
+      <c r="H101" t="str">
+        <v>Carpenter Brut</v>
+      </c>
+      <c r="I101" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J101" t="str">
+        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+      </c>
+      <c r="K101" t="str">
+        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+      </c>
+      <c r="L101" t="str">
+        <v>Speed or Perish - Carpenter Brut</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
         <v>The Scumbag Grift</v>
       </c>
-      <c r="B101" t="str">
-        <v/>
-      </c>
-      <c r="C101" t="str">
+      <c r="B102" t="str">
+        <v/>
+      </c>
+      <c r="C102" t="str">
         <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
       </c>
-      <c r="D101" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="E101" t="str">
-        <v/>
-      </c>
-      <c r="F101" t="str">
+      <c r="D102" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
         <v>Cheap Heat</v>
       </c>
-      <c r="G101" t="str">
+      <c r="G102" t="str">
         <v>2:27</v>
       </c>
-      <c r="H101" t="str">
+      <c r="H102" t="str">
         <v>A Wilhelm Scream</v>
       </c>
-      <c r="I101" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J101" t="str">
+      <c r="I102" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J102" t="str">
         <v>https://music.apple.com/us/artist/a-wilhelm-scream/7375447</v>
       </c>
-      <c r="K101" t="str">
+      <c r="K102" t="str">
         <v>https://music.apple.com/us/album/the-scumbag-grift/1870588948</v>
       </c>
-      <c r="L101" t="str">
+      <c r="L102" t="str">
         <v>The Scumbag Grift - A Wilhelm Scream</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L101"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L102"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week01/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/go/1870067581</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/ganga/1879903219</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/with-me/1874015492</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/miss-that/1875987505</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/old-technology/1867531318</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/alice/1874333652</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/tonto/1879859729</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/mariah/1874948938</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/blackhole/1873882200</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/walk/1875008123</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/flammable/1879896026</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/gentleman/1876982929</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/nyx00/1878551807</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/helicopters/1870313516</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/my-loving/1875970777</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/beautiful/1864389804</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/control-freak/1859044257</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/done-for/1873391195</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/moonlight/1878731568</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/free/1872250568</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/mantis/1868686720</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/the-blade/1876388273</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/the-place/1869119815</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/facts/1878765800</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/me-you/1878168773</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/badman/1877577830</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/automatic/1875133428</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-03</v>
+        <v>2026-03-04</v>
       </c>
       <c r="E102" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:L103"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SOMEWHERE ELSE</v>
+        <v>Medicine</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
+        <v>https://music.apple.com/us/song/medicine/1874168009</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-04</v>
@@ -451,25 +451,25 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>COME CLOSER</v>
+        <v>Medicine - Single</v>
       </c>
       <c r="G2" t="str">
-        <v>4:11</v>
+        <v>2:34</v>
       </c>
       <c r="H2" t="str">
-        <v>TOMORA</v>
+        <v>Channel Tres</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
+        <v>https://music.apple.com/us/album/medicine/1874168007</v>
       </c>
       <c r="L2" t="str">
-        <v>SOMEWHERE ELSE - TOMORA</v>
+        <v>Medicine - Channel Tres</v>
       </c>
     </row>
     <row r="3">
@@ -854,13 +854,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Dog</v>
+        <v>SOMEWHERE ELSE</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/dog/1871594836</v>
+        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-04</v>
@@ -869,25 +869,25 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Torn</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G13" t="str">
-        <v>2:37</v>
+        <v>4:11</v>
       </c>
       <c r="H13" t="str">
-        <v>Cobrah</v>
+        <v>TOMORA</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/dog/1871594546</v>
+        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
       </c>
       <c r="L13" t="str">
-        <v>Dog - Cobrah</v>
+        <v>SOMEWHERE ELSE - TOMORA</v>
       </c>
     </row>
     <row r="14">
@@ -930,13 +930,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>OLD TECHNOLOGY</v>
+        <v>Dog</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
+        <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-04</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>Torn</v>
       </c>
       <c r="G15" t="str">
-        <v>2:39</v>
+        <v>2:37</v>
       </c>
       <c r="H15" t="str">
-        <v>Slayyyter</v>
+        <v>Cobrah</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
+        <v>https://music.apple.com/us/album/dog/1871594546</v>
       </c>
       <c r="L15" t="str">
-        <v>OLD TECHNOLOGY - Slayyyter</v>
+        <v>Dog - Cobrah</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ALICE</v>
+        <v>OLD TECHNOLOGY</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/alice/1874333652</v>
+        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-04</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>PAREIDOLIA - EP</v>
+        <v>WOR$T GIRL IN AMERICA</v>
       </c>
       <c r="G16" t="str">
-        <v>4:39</v>
+        <v>2:39</v>
       </c>
       <c r="H16" t="str">
-        <v>Erin LeCount</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/alice/1874333566</v>
+        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
       </c>
       <c r="L16" t="str">
-        <v>ALICE - Erin LeCount</v>
+        <v>OLD TECHNOLOGY - Slayyyter</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Tiny Light</v>
+        <v>ALICE</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
+        <v>https://music.apple.com/us/song/alice/1874333652</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-04</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Tiny Light - Single</v>
+        <v>PAREIDOLIA - EP</v>
       </c>
       <c r="G17" t="str">
-        <v>3:27</v>
+        <v>4:39</v>
       </c>
       <c r="H17" t="str">
-        <v>SEVENTEEN</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
+        <v>https://music.apple.com/us/album/alice/1874333566</v>
       </c>
       <c r="L17" t="str">
-        <v>Tiny Light - SEVENTEEN</v>
+        <v>ALICE - Erin LeCount</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!)</v>
+        <v>Tiny Light</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
+        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-04</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
+        <v>Tiny Light - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>2:50</v>
+        <v>3:27</v>
       </c>
       <c r="H18" t="str">
-        <v>aespa</v>
+        <v>SEVENTEEN</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
+        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
       </c>
       <c r="L18" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
+        <v>Tiny Light - SEVENTEEN</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>16 YEAR OLD DRANK</v>
+        <v>Keychain (FROM THE FILM K-POPS!)</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
+        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-04</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>It's Us Vol. 2</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>3:23</v>
+        <v>2:50</v>
       </c>
       <c r="H19" t="str">
-        <v>Concrete Boys</v>
+        <v>aespa</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
+        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
       </c>
       <c r="L19" t="str">
-        <v>16 YEAR OLD DRANK - Concrete Boys</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>If I Leave</v>
+        <v>16 YEAR OLD DRANK</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
+        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-04</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>It's Us Vol. 2</v>
       </c>
       <c r="G20" t="str">
-        <v>3:00</v>
+        <v>3:23</v>
       </c>
       <c r="H20" t="str">
-        <v>Mitski</v>
+        <v>Concrete Boys</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
+        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
       </c>
       <c r="L20" t="str">
-        <v>If I Leave - Mitski</v>
+        <v>16 YEAR OLD DRANK - Concrete Boys</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Time Will Tell</v>
+        <v>If I Leave</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
+        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-04</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>Time Will Tell - Single</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G21" t="str">
-        <v>3:04</v>
+        <v>3:00</v>
       </c>
       <c r="H21" t="str">
-        <v>Lee Brice</v>
+        <v>Mitski</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
+        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
       </c>
       <c r="L21" t="str">
-        <v>Time Will Tell - Lee Brice</v>
+        <v>If I Leave - Mitski</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>How I Get</v>
+        <v>Time Will Tell</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
+        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-04</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>Time Will Tell - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>3:39</v>
+        <v>3:04</v>
       </c>
       <c r="H22" t="str">
-        <v>Laufey</v>
+        <v>Lee Brice</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
+        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
       </c>
       <c r="L22" t="str">
-        <v>How I Get - Laufey</v>
+        <v>Time Will Tell - Lee Brice</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7)</v>
+        <v>How I Get</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
+        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-04</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
+        <v>A Matter of Time: The Final Hour</v>
       </c>
       <c r="G23" t="str">
-        <v>3:19</v>
+        <v>3:39</v>
       </c>
       <c r="H23" t="str">
-        <v>Jessie Murph</v>
+        <v>Laufey</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
+        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
+        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
       </c>
       <c r="L23" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
+        <v>How I Get - Laufey</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Tonto</v>
+        <v>Criminal (From the Original Motion Picture Scream 7)</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/tonto/1879859729</v>
+        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-04</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Tonto - Single</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
       </c>
       <c r="G24" t="str">
-        <v>2:20</v>
+        <v>3:19</v>
       </c>
       <c r="H24" t="str">
-        <v>J Balvin</v>
+        <v>Jessie Murph</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/tonto/1879859725</v>
+        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
       </c>
       <c r="L24" t="str">
-        <v>Tonto - J Balvin</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>nothin lasts 4ever</v>
+        <v>Tonto</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
+        <v>https://music.apple.com/us/song/tonto/1879859729</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-04</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>nothin lasts 4ever - Single</v>
+        <v>Tonto - Single</v>
       </c>
       <c r="G25" t="str">
-        <v>2:41</v>
+        <v>2:20</v>
       </c>
       <c r="H25" t="str">
-        <v>BLOND:ISH</v>
+        <v>J Balvin</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
+        <v>https://music.apple.com/us/album/tonto/1879859725</v>
       </c>
       <c r="L25" t="str">
-        <v>nothin lasts 4ever - BLOND:ISH</v>
+        <v>Tonto - J Balvin</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>MUERDO Mi LENGUA</v>
+        <v>nothin lasts 4ever</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
+        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-04</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>MUERDO Mi LENGUA - Single</v>
+        <v>nothin lasts 4ever - Single</v>
       </c>
       <c r="G26" t="str">
-        <v>2:50</v>
+        <v>2:41</v>
       </c>
       <c r="H26" t="str">
-        <v>Bautiii</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
+        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
       </c>
       <c r="L26" t="str">
-        <v>MUERDO Mi LENGUA - Bautiii</v>
+        <v>nothin lasts 4ever - BLOND:ISH</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage]</v>
+        <v>MUERDO Mi LENGUA</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
+        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-04</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
+        <v>MUERDO Mi LENGUA - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>3:41</v>
+        <v>2:50</v>
       </c>
       <c r="H27" t="str">
-        <v>Mýa</v>
+        <v>Bautiii</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
+        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
       </c>
       <c r="L27" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
+        <v>MUERDO Mi LENGUA - Bautiii</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Smugglers &amp; Scholars</v>
+        <v>ASAP (Remix) [feat. 21 Savage]</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
+        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-04</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>FENIAN</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>3:11</v>
+        <v>3:41</v>
       </c>
       <c r="H28" t="str">
-        <v>Kneecap</v>
+        <v>Mýa</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
+        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
       </c>
       <c r="L28" t="str">
-        <v>Smugglers &amp; Scholars - Kneecap</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>What You Want</v>
+        <v>Smugglers &amp; Scholars</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-04</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>What You Want - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G29" t="str">
-        <v>3:08</v>
+        <v>3:11</v>
       </c>
       <c r="H29" t="str">
-        <v>Angèle</v>
+        <v>Kneecap</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
       </c>
       <c r="L29" t="str">
-        <v>What You Want - Angèle</v>
+        <v>Smugglers &amp; Scholars - Kneecap</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>psychokiller</v>
+        <v>What You Want</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
+        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-04</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>getting up to no good</v>
+        <v>What You Want - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>1:53</v>
+        <v>3:08</v>
       </c>
       <c r="H30" t="str">
-        <v>Artemas</v>
+        <v>Angèle</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
+        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
       </c>
       <c r="L30" t="str">
-        <v>psychokiller - Artemas</v>
+        <v>What You Want - Angèle</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>DISNEY PRINCESS</v>
+        <v>psychokiller</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
+        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-04</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>HADES</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G31" t="str">
-        <v>4:05</v>
+        <v>1:53</v>
       </c>
       <c r="H31" t="str">
-        <v>Melanie Martinez</v>
+        <v>Artemas</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
+        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
       </c>
       <c r="L31" t="str">
-        <v>DISNEY PRINCESS - Melanie Martinez</v>
+        <v>psychokiller - Artemas</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>mariah</v>
+        <v>DISNEY PRINCESS</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/mariah/1874948938</v>
+        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-04</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>songs i couldn't forget - EP</v>
+        <v>HADES</v>
       </c>
       <c r="G32" t="str">
-        <v>2:48</v>
+        <v>4:05</v>
       </c>
       <c r="H32" t="str">
-        <v>Lauv</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/mariah/1874948926</v>
+        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
       </c>
       <c r="L32" t="str">
-        <v>mariah - Lauv</v>
+        <v>DISNEY PRINCESS - Melanie Martinez</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>BLACKHOLE</v>
+        <v>mariah</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
+        <v>https://music.apple.com/us/song/mariah/1874948938</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-04</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>REVIVE+</v>
+        <v>songs i couldn't forget - EP</v>
       </c>
       <c r="G33" t="str">
-        <v>3:14</v>
+        <v>2:48</v>
       </c>
       <c r="H33" t="str">
-        <v>IVE</v>
+        <v>Lauv</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
+        <v>https://music.apple.com/us/album/mariah/1874948926</v>
       </c>
       <c r="L33" t="str">
-        <v>BLACKHOLE - IVE</v>
+        <v>mariah - Lauv</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Walk</v>
+        <v>BLACKHOLE</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/walk/1875008123</v>
+        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-04</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Walk - Single</v>
+        <v>REVIVE+</v>
       </c>
       <c r="G34" t="str">
-        <v>2:56</v>
+        <v>3:14</v>
       </c>
       <c r="H34" t="str">
-        <v>Skye Newman</v>
+        <v>IVE</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/walk/1875008118</v>
+        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
       </c>
       <c r="L34" t="str">
-        <v>Walk - Skye Newman</v>
+        <v>BLACKHOLE - IVE</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>FLAMMABLE</v>
+        <v>Walk</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/flammable/1879896026</v>
+        <v>https://music.apple.com/us/song/walk/1875008123</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-04</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>FLAMMABLE - Single</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>3:17</v>
+        <v>2:56</v>
       </c>
       <c r="H35" t="str">
-        <v>Swae Lee</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/flammable/1879896025</v>
+        <v>https://music.apple.com/us/album/walk/1875008118</v>
       </c>
       <c r="L35" t="str">
-        <v>FLAMMABLE - Swae Lee</v>
+        <v>Walk - Skye Newman</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>3am (Remix)</v>
+        <v>FLAMMABLE</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
+        <v>https://music.apple.com/us/song/flammable/1879896026</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-04</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3am (Remix) - Single</v>
+        <v>FLAMMABLE - Single</v>
       </c>
       <c r="G36" t="str">
-        <v>2:44</v>
+        <v>3:17</v>
       </c>
       <c r="H36" t="str">
-        <v>Łaszewo</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/%C5%82aszewo/1438035296</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/3am-remix/1878278386</v>
+        <v>https://music.apple.com/us/album/flammable/1879896025</v>
       </c>
       <c r="L36" t="str">
-        <v>3am (Remix) - Łaszewo</v>
+        <v>FLAMMABLE - Swae Lee</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>mutual destruction</v>
+        <v>3am (Remix)</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
+        <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-04</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>mutual destruction - Single</v>
+        <v>3am (Remix) - Single</v>
       </c>
       <c r="G37" t="str">
-        <v>2:31</v>
+        <v>2:44</v>
       </c>
       <c r="H37" t="str">
-        <v>kenzie</v>
+        <v>Łaszewo</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/%C5%82aszewo/1438035296</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
+        <v>https://music.apple.com/us/album/3am-remix/1878278386</v>
       </c>
       <c r="L37" t="str">
-        <v>mutual destruction - kenzie</v>
+        <v>3am (Remix) - Łaszewo</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Dear Worry</v>
+        <v>mutual destruction</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
+        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-04</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Dear Worry - Single</v>
+        <v>mutual destruction - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>3:01</v>
+        <v>2:31</v>
       </c>
       <c r="H38" t="str">
-        <v>Common People</v>
+        <v>kenzie</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
+        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
       </c>
       <c r="L38" t="str">
-        <v>Dear Worry - Common People</v>
+        <v>mutual destruction - kenzie</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Gentleman</v>
+        <v>Dear Worry</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
+        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-04</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Gentleman - Single</v>
+        <v>Dear Worry - Single</v>
       </c>
       <c r="G39" t="str">
-        <v>2:16</v>
+        <v>3:01</v>
       </c>
       <c r="H39" t="str">
-        <v>Towa Bird</v>
+        <v>Common People</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
+        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
       </c>
       <c r="L39" t="str">
-        <v>Gentleman - Towa Bird</v>
+        <v>Dear Worry - Common People</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>NYX00</v>
+        <v>Gentleman</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
+        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-04</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>NYX00 - Single</v>
+        <v>Gentleman - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>3:00</v>
+        <v>2:16</v>
       </c>
       <c r="H40" t="str">
-        <v>Dei V</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
+        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
       </c>
       <c r="L40" t="str">
-        <v>NYX00 - Dei V</v>
+        <v>Gentleman - Towa Bird</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Helicopters</v>
+        <v>NYX00</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
+        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-04</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>HELP(2)</v>
+        <v>NYX00 - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>3:58</v>
+        <v>3:00</v>
       </c>
       <c r="H41" t="str">
-        <v>Ezra Collective</v>
+        <v>Dei V</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
+        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
       </c>
       <c r="L41" t="str">
-        <v>Helicopters - Ezra Collective</v>
+        <v>NYX00 - Dei V</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
+        <v>Helicopters</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
+        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-04</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Max Richter: Hamnet Live</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G42" t="str">
-        <v>4:58</v>
+        <v>3:58</v>
       </c>
       <c r="H42" t="str">
-        <v>Max Richter</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
+        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
       </c>
       <c r="L42" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
+        <v>Helicopters - Ezra Collective</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>It's You I Want</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
+        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-04</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
+        <v>Max Richter: Hamnet Live</v>
       </c>
       <c r="G43" t="str">
-        <v>1:39</v>
+        <v>4:58</v>
       </c>
       <c r="H43" t="str">
-        <v>Kris Bowers</v>
+        <v>Max Richter</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
+        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
+        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
       </c>
       <c r="L43" t="str">
-        <v>It's You I Want - Kris Bowers</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>If I Was With You</v>
+        <v>It's You I Want</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
+        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-04</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>If I Was With You - Single</v>
+        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
       </c>
       <c r="G44" t="str">
-        <v>3:25</v>
+        <v>1:39</v>
       </c>
       <c r="H44" t="str">
-        <v>Presley Regier</v>
+        <v>Kris Bowers</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
+        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
       </c>
       <c r="L44" t="str">
-        <v>If I Was With You - Presley Regier</v>
+        <v>It's You I Want - Kris Bowers</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Stay With Me</v>
+        <v>If I Was With You</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
+        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-04</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>If I Was With You - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>3:47</v>
+        <v>3:25</v>
       </c>
       <c r="H45" t="str">
-        <v>Nessa Barrett</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
+        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
       </c>
       <c r="L45" t="str">
-        <v>Stay With Me - Nessa Barrett</v>
+        <v>If I Was With You - Presley Regier</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>My Loving</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-04</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>My Loving - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G46" t="str">
-        <v>2:50</v>
+        <v>3:47</v>
       </c>
       <c r="H46" t="str">
-        <v>Sonny Fodera</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
       </c>
       <c r="L46" t="str">
-        <v>My Loving - Sonny Fodera</v>
+        <v>Stay With Me - Nessa Barrett</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Easy On The Eyes</v>
+        <v>My Loving</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
+        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-04</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Easy On The Eyes - Single</v>
+        <v>My Loving - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>3:44</v>
+        <v>2:50</v>
       </c>
       <c r="H47" t="str">
-        <v>Willow Avalon</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
+        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
       </c>
       <c r="L47" t="str">
-        <v>Easy On The Eyes - Willow Avalon</v>
+        <v>My Loving - Sonny Fodera</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Beautiful</v>
+        <v>Easy On The Eyes</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
+        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-04</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Let It Die Here</v>
+        <v>Easy On The Eyes - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>3:47</v>
+        <v>3:44</v>
       </c>
       <c r="H48" t="str">
-        <v>Linda Perry</v>
+        <v>Willow Avalon</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
+        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
       </c>
       <c r="L48" t="str">
-        <v>Beautiful - Linda Perry</v>
+        <v>Easy On The Eyes - Willow Avalon</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3")</v>
+        <v>Beautiful</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
+        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-04</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G49" t="str">
-        <v>4:34</v>
+        <v>3:47</v>
       </c>
       <c r="H49" t="str">
-        <v>Jason Segel</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
+        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
       </c>
       <c r="L49" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
+        <v>Beautiful - Linda Perry</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Control Freak</v>
+        <v>Nightswimming (from "Shrinking: Season 3")</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
+        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-04</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Control Freak - Single</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>2:53</v>
+        <v>4:34</v>
       </c>
       <c r="H50" t="str">
-        <v>Broadside</v>
+        <v>Jason Segel</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/broadside/169939373</v>
+        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
+        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
       </c>
       <c r="L50" t="str">
-        <v>Control Freak - Broadside</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Done For</v>
+        <v>Control Freak</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/done-for/1873391195</v>
+        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-04</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Done For - Single</v>
+        <v>Control Freak - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>2:33</v>
+        <v>2:53</v>
       </c>
       <c r="H51" t="str">
-        <v>Max McNown</v>
+        <v>Broadside</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/broadside/169939373</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/done-for/1873391193</v>
+        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
       </c>
       <c r="L51" t="str">
-        <v>Done For - Max McNown</v>
+        <v>Control Freak - Broadside</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Ready for the Ride</v>
+        <v>Done For</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
+        <v>https://music.apple.com/us/song/done-for/1873391195</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-04</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Ready for the Ride - Single</v>
+        <v>Done For - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>3:27</v>
+        <v>2:33</v>
       </c>
       <c r="H52" t="str">
-        <v>Sean Paul</v>
+        <v>Max McNown</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
+        <v>https://music.apple.com/us/album/done-for/1873391193</v>
       </c>
       <c r="L52" t="str">
-        <v>Ready for the Ride - Sean Paul</v>
+        <v>Done For - Max McNown</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>push the pipe</v>
+        <v>Ready for the Ride</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
+        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-04</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>HYPERYOUTH (afterparty)</v>
+        <v>Ready for the Ride - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>3:08</v>
+        <v>3:27</v>
       </c>
       <c r="H53" t="str">
-        <v>Joey Valence &amp; Brae</v>
+        <v>Sean Paul</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
+        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
+        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
       </c>
       <c r="L53" t="str">
-        <v>push the pipe - Joey Valence &amp; Brae</v>
+        <v>Ready for the Ride - Sean Paul</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>push the pipe</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-04</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>With No Due Respect</v>
+        <v>HYPERYOUTH (afterparty)</v>
       </c>
       <c r="G54" t="str">
-        <v>3:13</v>
+        <v>3:08</v>
       </c>
       <c r="H54" t="str">
-        <v>Foggieraw</v>
+        <v>Joey Valence &amp; Brae</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
       </c>
       <c r="L54" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>push the pipe - Joey Valence &amp; Brae</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Moonlight</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-04</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>McKenzie 2.0</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G55" t="str">
-        <v>2:00</v>
+        <v>3:13</v>
       </c>
       <c r="H55" t="str">
-        <v>FattMack</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L55" t="str">
-        <v>Moonlight - FattMack</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Boat Named After You</v>
+        <v>Moonlight</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
+        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-04</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Boat Named After You - Single</v>
+        <v>McKenzie 2.0</v>
       </c>
       <c r="G56" t="str">
-        <v>3:56</v>
+        <v>2:00</v>
       </c>
       <c r="H56" t="str">
-        <v>ERNEST</v>
+        <v>FattMack</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
+        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
       </c>
       <c r="L56" t="str">
-        <v>Boat Named After You - ERNEST</v>
+        <v>Moonlight - FattMack</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>fall into you</v>
+        <v>Boat Named After You</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
+        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-04</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>fall into you - Single</v>
+        <v>Boat Named After You - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>3:28</v>
+        <v>3:56</v>
       </c>
       <c r="H57" t="str">
-        <v>Camylio</v>
+        <v>ERNEST</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
+        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
       </c>
       <c r="L57" t="str">
-        <v>fall into you - Camylio</v>
+        <v>Boat Named After You - ERNEST</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Van Gogh</v>
+        <v>fall into you</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
+        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-04</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Tales of a Failed Shapeshifter</v>
+        <v>fall into you - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>2:25</v>
+        <v>3:28</v>
       </c>
       <c r="H58" t="str">
-        <v>Em Beihold</v>
+        <v>Camylio</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
+        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
       </c>
       <c r="L58" t="str">
-        <v>Van Gogh - Em Beihold</v>
+        <v>fall into you - Camylio</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>popstar Nervous</v>
+        <v>Van Gogh</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
+        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-04</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>the rumors are true - EP</v>
+        <v>Tales of a Failed Shapeshifter</v>
       </c>
       <c r="G59" t="str">
         <v>2:25</v>
       </c>
       <c r="H59" t="str">
-        <v>DC THE DON</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
+        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
       </c>
       <c r="L59" t="str">
-        <v>popstar Nervous - DC THE DON</v>
+        <v>Van Gogh - Em Beihold</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Free</v>
+        <v>popstar Nervous</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/free/1872250568</v>
+        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-04</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Free - Single</v>
+        <v>the rumors are true - EP</v>
       </c>
       <c r="G60" t="str">
-        <v>3:08</v>
+        <v>2:25</v>
       </c>
       <c r="H60" t="str">
-        <v>Beartooth</v>
+        <v>DC THE DON</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/free/1872250308</v>
+        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
       </c>
       <c r="L60" t="str">
-        <v>Free - Beartooth</v>
+        <v>popstar Nervous - DC THE DON</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>never come never morning</v>
+        <v>Free</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
+        <v>https://music.apple.com/us/song/free/1872250568</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-04</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>a short history of decay</v>
+        <v>Free - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>3:39</v>
+        <v>3:08</v>
       </c>
       <c r="H61" t="str">
-        <v>Nothing</v>
+        <v>Beartooth</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/nothing/593213453</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
+        <v>https://music.apple.com/us/album/free/1872250308</v>
       </c>
       <c r="L61" t="str">
-        <v>never come never morning - Nothing</v>
+        <v>Free - Beartooth</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Over My Head</v>
+        <v>never come never morning</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
+        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-04</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>A Beautiful Lie (20 Year Anniversary)</v>
+        <v>a short history of decay</v>
       </c>
       <c r="G62" t="str">
-        <v>2:30</v>
+        <v>3:39</v>
       </c>
       <c r="H62" t="str">
-        <v>Thirty Seconds to Mars</v>
+        <v>Nothing</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
+        <v>https://music.apple.com/us/artist/nothing/593213453</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
+        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
       </c>
       <c r="L62" t="str">
-        <v>Over My Head - Thirty Seconds to Mars</v>
+        <v>never come never morning - Nothing</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Mantis</v>
+        <v>Over My Head</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/mantis/1868686720</v>
+        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-04</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Creature of Habit</v>
+        <v>A Beautiful Lie (20 Year Anniversary)</v>
       </c>
       <c r="G63" t="str">
-        <v>4:40</v>
+        <v>2:30</v>
       </c>
       <c r="H63" t="str">
-        <v>Courtney Barnett</v>
+        <v>Thirty Seconds to Mars</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/mantis/1868686713</v>
+        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
       </c>
       <c r="L63" t="str">
-        <v>Mantis - Courtney Barnett</v>
+        <v>Over My Head - Thirty Seconds to Mars</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Soft Launch</v>
+        <v>Mantis</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
+        <v>https://music.apple.com/us/song/mantis/1868686720</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-04</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Soft Launch - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G64" t="str">
-        <v>2:25</v>
+        <v>4:40</v>
       </c>
       <c r="H64" t="str">
-        <v>Cely</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/cely/1259609505</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
+        <v>https://music.apple.com/us/album/mantis/1868686713</v>
       </c>
       <c r="L64" t="str">
-        <v>Soft Launch - Cely</v>
+        <v>Mantis - Courtney Barnett</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>picky choosy</v>
+        <v>Soft Launch</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
+        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-04</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Soft Launch - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>2:53</v>
+        <v>2:25</v>
       </c>
       <c r="H65" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Cely</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/cely/1259609505</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
+        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
       </c>
       <c r="L65" t="str">
-        <v>picky choosy - Chelsea Jordan</v>
+        <v>Soft Launch - Cely</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>La Mala Era Yo</v>
+        <v>picky choosy</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
+        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-04</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>La Mala Era Yo - Single</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G66" t="str">
-        <v>2:30</v>
+        <v>2:53</v>
       </c>
       <c r="H66" t="str">
-        <v>Kany García</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
+        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
       </c>
       <c r="L66" t="str">
-        <v>La Mala Era Yo - Kany García</v>
+        <v>picky choosy - Chelsea Jordan</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Quiet Part Loud</v>
+        <v>La Mala Era Yo</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
+        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-04</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Joy Next Door</v>
+        <v>La Mala Era Yo - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>3:08</v>
+        <v>2:30</v>
       </c>
       <c r="H67" t="str">
-        <v>The Maine</v>
+        <v>Kany García</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
+        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
       </c>
       <c r="L67" t="str">
-        <v>Quiet Part Loud - The Maine</v>
+        <v>La Mala Era Yo - Kany García</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>favorite girl</v>
+        <v>Quiet Part Loud</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
+        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-04</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>favorite girl - Single</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G68" t="str">
-        <v>3:24</v>
+        <v>3:08</v>
       </c>
       <c r="H68" t="str">
-        <v>Alaina Castillo</v>
+        <v>The Maine</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
+        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
       </c>
       <c r="L68" t="str">
-        <v>favorite girl - Alaina Castillo</v>
+        <v>Quiet Part Loud - The Maine</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>The Blade</v>
+        <v>favorite girl</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
+        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-04</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>The Blade - Single</v>
+        <v>favorite girl - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>3:15</v>
+        <v>3:24</v>
       </c>
       <c r="H69" t="str">
-        <v>Kingfishr</v>
+        <v>Alaina Castillo</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
+        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
       </c>
       <c r="L69" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>favorite girl - Alaina Castillo</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Blunt Force Blues</v>
+        <v>The Blade</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
+        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-04</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Into Oblivion</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>4:11</v>
+        <v>3:15</v>
       </c>
       <c r="H70" t="str">
-        <v>Lamb of God</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
+        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
       </c>
       <c r="L70" t="str">
-        <v>Blunt Force Blues - Lamb of God</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>The Black Scorpion</v>
+        <v>Blunt Force Blues</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
+        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-04</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>The Great Satan</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G71" t="str">
-        <v>1:33</v>
+        <v>4:11</v>
       </c>
       <c r="H71" t="str">
-        <v>Rob Zombie</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
+        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
       </c>
       <c r="L71" t="str">
-        <v>The Black Scorpion - Rob Zombie</v>
+        <v>Blunt Force Blues - Lamb of God</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>The Place</v>
+        <v>The Black Scorpion</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/the-place/1869119815</v>
+        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-04</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G72" t="str">
-        <v>5:58</v>
+        <v>1:33</v>
       </c>
       <c r="H72" t="str">
-        <v>Sepultura</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/the-place/1869119453</v>
+        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
       </c>
       <c r="L72" t="str">
-        <v>The Place - Sepultura</v>
+        <v>The Black Scorpion - Rob Zombie</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>SONG OF THE SWAMP</v>
+        <v>The Place</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
+        <v>https://music.apple.com/us/song/the-place/1869119815</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-04</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G73" t="str">
-        <v>3:18</v>
+        <v>5:58</v>
       </c>
       <c r="H73" t="str">
-        <v>Wage War</v>
+        <v>Sepultura</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
+        <v>https://music.apple.com/us/album/the-place/1869119453</v>
       </c>
       <c r="L73" t="str">
-        <v>SONG OF THE SWAMP - Wage War</v>
+        <v>The Place - Sepultura</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez)</v>
+        <v>SONG OF THE SWAMP</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
+        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-04</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G74" t="str">
-        <v>2:26</v>
+        <v>3:18</v>
       </c>
       <c r="H74" t="str">
-        <v>LOS DOS DE TAMAULIPAS</v>
+        <v>Wage War</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
+        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
       </c>
       <c r="L74" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
+        <v>SONG OF THE SWAMP - Wage War</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Tu Cárcel</v>
+        <v>Súper Snake (feat. Luis R Conriquez)</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
+        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-04</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Tu Cárcel - Single</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>3:36</v>
+        <v>2:26</v>
       </c>
       <c r="H75" t="str">
-        <v>Morat</v>
+        <v>LOS DOS DE TAMAULIPAS</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/morat/955657302</v>
+        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
+        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
       </c>
       <c r="L75" t="str">
-        <v>Tu Cárcel - Morat</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Facts</v>
+        <v>Tu Cárcel</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/facts/1878765800</v>
+        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-04</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Be Very Afraid (Vol. 1)</v>
+        <v>Tu Cárcel - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>3:29</v>
+        <v>3:36</v>
       </c>
       <c r="H76" t="str">
-        <v>CHASE B</v>
+        <v>Morat</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
+        <v>https://music.apple.com/us/artist/morat/955657302</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/facts/1878765796</v>
+        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
       </c>
       <c r="L76" t="str">
-        <v>Facts - CHASE B</v>
+        <v>Tu Cárcel - Morat</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>me &amp; you</v>
+        <v>Facts</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/me-you/1878168773</v>
+        <v>https://music.apple.com/us/song/facts/1878765800</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-04</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>big country</v>
+        <v>Be Very Afraid (Vol. 1)</v>
       </c>
       <c r="G77" t="str">
-        <v>2:29</v>
+        <v>3:29</v>
       </c>
       <c r="H77" t="str">
-        <v>sosocamo</v>
+        <v>CHASE B</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
+        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/me-you/1878168770</v>
+        <v>https://music.apple.com/us/album/facts/1878765796</v>
       </c>
       <c r="L77" t="str">
-        <v>me &amp; you - sosocamo</v>
+        <v>Facts - CHASE B</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>badman</v>
+        <v>me &amp; you</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/badman/1877577830</v>
+        <v>https://music.apple.com/us/song/me-you/1878168773</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-04</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>badman - Single</v>
+        <v>big country</v>
       </c>
       <c r="G78" t="str">
-        <v>2:54</v>
+        <v>2:29</v>
       </c>
       <c r="H78" t="str">
-        <v>nomi.</v>
+        <v>sosocamo</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
+        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/badman/1877577829</v>
+        <v>https://music.apple.com/us/album/me-you/1878168770</v>
       </c>
       <c r="L78" t="str">
-        <v>badman - nomi.</v>
+        <v>me &amp; you - sosocamo</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Shut It Down</v>
+        <v>badman</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
+        <v>https://music.apple.com/us/song/badman/1877577830</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-04</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Shut It Down - Single</v>
+        <v>badman - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>2:26</v>
+        <v>2:54</v>
       </c>
       <c r="H79" t="str">
-        <v>TheARTI$t</v>
+        <v>nomi.</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
+        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
+        <v>https://music.apple.com/us/album/badman/1877577829</v>
       </c>
       <c r="L79" t="str">
-        <v>Shut It Down - TheARTI$t</v>
+        <v>badman - nomi.</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>AUTOMATIC</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/automatic/1875133428</v>
+        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-04</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>AUTOMATIC - Single</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>2:08</v>
+        <v>2:26</v>
       </c>
       <c r="H80" t="str">
-        <v>Hulvey</v>
+        <v>TheARTI$t</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/automatic/1875133426</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
       </c>
       <c r="L80" t="str">
-        <v>AUTOMATIC - Hulvey</v>
+        <v>Shut It Down - TheARTI$t</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Leaving Egypt</v>
+        <v>AUTOMATIC</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
+        <v>https://music.apple.com/us/song/automatic/1875133428</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-04</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Leaving Egypt - Single</v>
+        <v>AUTOMATIC - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>3:17</v>
+        <v>2:08</v>
       </c>
       <c r="H81" t="str">
-        <v>Alex Jude</v>
+        <v>Hulvey</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
+        <v>https://music.apple.com/us/album/automatic/1875133426</v>
       </c>
       <c r="L81" t="str">
-        <v>Leaving Egypt - Alex Jude</v>
+        <v>AUTOMATIC - Hulvey</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Not Your Mother</v>
+        <v>Leaving Egypt</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
+        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-04</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Not Your Mother - Single</v>
+        <v>Leaving Egypt - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>3:03</v>
+        <v>3:17</v>
       </c>
       <c r="H82" t="str">
-        <v>gracie</v>
+        <v>Alex Jude</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
+        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
+        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
       </c>
       <c r="L82" t="str">
-        <v>Not Your Mother - gracie</v>
+        <v>Leaving Egypt - Alex Jude</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
+        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-04</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>3:50</v>
+        <v>3:03</v>
       </c>
       <c r="H83" t="str">
-        <v>Social Distortion</v>
+        <v>gracie</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
+        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
       </c>
       <c r="L83" t="str">
-        <v>Born to Kill - Social Distortion</v>
+        <v>Not Your Mother - gracie</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>When the Love is Gone</v>
+        <v>Born to Kill</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
+        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-04</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>When the Love is Gone - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G84" t="str">
-        <v>3:20</v>
+        <v>3:50</v>
       </c>
       <c r="H84" t="str">
-        <v>Des Rocs</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
+        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
       </c>
       <c r="L84" t="str">
-        <v>When the Love is Gone - Des Rocs</v>
+        <v>Born to Kill - Social Distortion</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Miami Crest</v>
+        <v>When the Love is Gone</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
+        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-04</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Miami Crest - Single</v>
+        <v>When the Love is Gone - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>2:39</v>
+        <v>3:20</v>
       </c>
       <c r="H85" t="str">
-        <v>Namasenda</v>
+        <v>Des Rocs</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
+        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
+        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
       </c>
       <c r="L85" t="str">
-        <v>Miami Crest - Namasenda</v>
+        <v>When the Love is Gone - Des Rocs</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Say No Prayer</v>
+        <v>Miami Crest</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
+        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-04</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Say No Prayer - Single</v>
+        <v>Miami Crest - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>2:29</v>
+        <v>2:39</v>
       </c>
       <c r="H86" t="str">
-        <v>oskar med k</v>
+        <v>Namasenda</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
+        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
+        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
       </c>
       <c r="L86" t="str">
-        <v>Say No Prayer - oskar med k</v>
+        <v>Miami Crest - Namasenda</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>You Always Liked Me Better When I Was Stoned</v>
+        <v>Say No Prayer</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
+        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-04</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - Single</v>
+        <v>Say No Prayer - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>3:09</v>
+        <v>2:29</v>
       </c>
       <c r="H87" t="str">
-        <v>eee gee</v>
+        <v>oskar med k</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
+        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
+        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
       </c>
       <c r="L87" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
+        <v>Say No Prayer - oskar med k</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Pink Tongue</v>
+        <v>You Always Liked Me Better When I Was Stoned</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
+        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-04</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Porcelain Heart</v>
+        <v>You Always Liked Me Better When I Was Stoned - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>3:43</v>
+        <v>3:09</v>
       </c>
       <c r="H88" t="str">
-        <v>Diane Emerita</v>
+        <v>eee gee</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
+        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
+        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
       </c>
       <c r="L88" t="str">
-        <v>Pink Tongue - Diane Emerita</v>
+        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Hey, Bluebird</v>
+        <v>Pink Tongue</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
+        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-04</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Hey, Bluebird - Single</v>
+        <v>Porcelain Heart</v>
       </c>
       <c r="G89" t="str">
-        <v>3:23</v>
+        <v>3:43</v>
       </c>
       <c r="H89" t="str">
-        <v>Ber</v>
+        <v>Diane Emerita</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/ber/1020679397</v>
+        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
+        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
       </c>
       <c r="L89" t="str">
-        <v>Hey, Bluebird - Ber</v>
+        <v>Pink Tongue - Diane Emerita</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>You’ll Be The Proof</v>
+        <v>Hey, Bluebird</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
+        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-04</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>You’ll Be The Proof - Single</v>
+        <v>Hey, Bluebird - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>3:26</v>
+        <v>3:23</v>
       </c>
       <c r="H90" t="str">
-        <v>Forest Blakk</v>
+        <v>Ber</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
+        <v>https://music.apple.com/us/artist/ber/1020679397</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
+        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
       </c>
       <c r="L90" t="str">
-        <v>You’ll Be The Proof - Forest Blakk</v>
+        <v>Hey, Bluebird - Ber</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Heartbeat</v>
+        <v>You’ll Be The Proof</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
+        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-04</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Heartbeat - Single</v>
+        <v>You’ll Be The Proof - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>2:52</v>
+        <v>3:26</v>
       </c>
       <c r="H91" t="str">
-        <v>Lola Blue</v>
+        <v>Forest Blakk</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
+        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
       </c>
       <c r="L91" t="str">
-        <v>Heartbeat - Lola Blue</v>
+        <v>You’ll Be The Proof - Forest Blakk</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Imitation (how to become you)</v>
+        <v>Heartbeat</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
+        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-04</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Imitation (how to become you) - Single</v>
+        <v>Heartbeat - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>4:16</v>
+        <v>2:52</v>
       </c>
       <c r="H92" t="str">
-        <v>doggone</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
+        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
       </c>
       <c r="L92" t="str">
-        <v>Imitation (how to become you) - doggone</v>
+        <v>Heartbeat - Lola Blue</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>I’m Every Woman</v>
+        <v>Imitation (how to become you)</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
+        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-04</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Cover Girl - EP</v>
+        <v>Imitation (how to become you) - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>4:35</v>
+        <v>4:16</v>
       </c>
       <c r="H93" t="str">
-        <v>Ashley Jackson</v>
+        <v>doggone</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
+        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
+        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
       </c>
       <c r="L93" t="str">
-        <v>I’m Every Woman - Ashley Jackson</v>
+        <v>Imitation (how to become you) - doggone</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Hard To See (feat. Norah Jones)</v>
+        <v>I’m Every Woman</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
+        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-04</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Infinite Source Of Heat</v>
+        <v>Cover Girl - EP</v>
       </c>
       <c r="G94" t="str">
-        <v>2:46</v>
+        <v>4:35</v>
       </c>
       <c r="H94" t="str">
-        <v>Chris Morrissey</v>
+        <v>Ashley Jackson</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
+        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
+        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
       </c>
       <c r="L94" t="str">
-        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
+        <v>I’m Every Woman - Ashley Jackson</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Slow Tonight</v>
+        <v>Hard To See (feat. Norah Jones)</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
+        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-04</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Full Circle</v>
+        <v>Infinite Source Of Heat</v>
       </c>
       <c r="G95" t="str">
-        <v>3:12</v>
+        <v>2:46</v>
       </c>
       <c r="H95" t="str">
-        <v>Tom Misch</v>
+        <v>Chris Morrissey</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
+        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
       </c>
       <c r="L95" t="str">
-        <v>Slow Tonight - Tom Misch</v>
+        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Freak No More</v>
+        <v>Slow Tonight</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
+        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-04</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Freak No More - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G96" t="str">
-        <v>3:57</v>
+        <v>3:12</v>
       </c>
       <c r="H96" t="str">
-        <v>AC Slater</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
+        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
       </c>
       <c r="L96" t="str">
-        <v>Freak No More - AC Slater</v>
+        <v>Slow Tonight - Tom Misch</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Don't Stop</v>
+        <v>Freak No More</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
+        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-04</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Don't Stop - Single</v>
+        <v>Freak No More - Single</v>
       </c>
       <c r="G97" t="str">
-        <v>2:55</v>
+        <v>3:57</v>
       </c>
       <c r="H97" t="str">
-        <v>HoneyLuv</v>
+        <v>AC Slater</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
+        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
+        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
       </c>
       <c r="L97" t="str">
-        <v>Don't Stop - HoneyLuv</v>
+        <v>Freak No More - AC Slater</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Cause I Do</v>
+        <v>Don't Stop</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
+        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-04</v>
@@ -4099,36 +4099,36 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>Cause I Do - Single</v>
+        <v>Don't Stop - Single</v>
       </c>
       <c r="G98" t="str">
-        <v>2:39</v>
+        <v>2:55</v>
       </c>
       <c r="H98" t="str">
-        <v>Preston Pablo</v>
+        <v>HoneyLuv</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
+        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
+        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
       </c>
       <c r="L98" t="str">
-        <v>Cause I Do - Preston Pablo</v>
+        <v>Don't Stop - HoneyLuv</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Morning Comes</v>
+        <v>Cause I Do</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
+        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-04</v>
@@ -4137,36 +4137,36 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Cause I Do - Single</v>
       </c>
       <c r="G99" t="str">
-        <v>4:11</v>
+        <v>2:39</v>
       </c>
       <c r="H99" t="str">
-        <v>Ty Myers</v>
+        <v>Preston Pablo</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
+        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
       </c>
       <c r="L99" t="str">
-        <v>Morning Comes - Ty Myers</v>
+        <v>Cause I Do - Preston Pablo</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>BETTER ON ME</v>
+        <v>Morning Comes</v>
       </c>
       <c r="B100" t="str">
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
+        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-04</v>
@@ -4175,36 +4175,36 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>BETTER ON ME - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G100" t="str">
-        <v>3:24</v>
+        <v>4:11</v>
       </c>
       <c r="H100" t="str">
-        <v>Johnny Huynh</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
+        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
       </c>
       <c r="L100" t="str">
-        <v>BETTER ON ME - Johnny Huynh</v>
+        <v>Morning Comes - Ty Myers</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Speed or Perish</v>
+        <v>BETTER ON ME</v>
       </c>
       <c r="B101" t="str">
         <v/>
       </c>
       <c r="C101" t="str">
-        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
       </c>
       <c r="D101" t="str">
         <v>2026-03-04</v>
@@ -4213,68 +4213,106 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>Leather Temple</v>
+        <v>BETTER ON ME - Single</v>
       </c>
       <c r="G101" t="str">
-        <v>4:30</v>
+        <v>3:24</v>
       </c>
       <c r="H101" t="str">
-        <v>Carpenter Brut</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J101" t="str">
-        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K101" t="str">
-        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
       </c>
       <c r="L101" t="str">
-        <v>Speed or Perish - Carpenter Brut</v>
+        <v>BETTER ON ME - Johnny Huynh</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
+        <v>Speed or Perish</v>
+      </c>
+      <c r="B102" t="str">
+        <v/>
+      </c>
+      <c r="C102" t="str">
+        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+      </c>
+      <c r="D102" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v>Leather Temple</v>
+      </c>
+      <c r="G102" t="str">
+        <v>4:30</v>
+      </c>
+      <c r="H102" t="str">
+        <v>Carpenter Brut</v>
+      </c>
+      <c r="I102" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J102" t="str">
+        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+      </c>
+      <c r="K102" t="str">
+        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+      </c>
+      <c r="L102" t="str">
+        <v>Speed or Perish - Carpenter Brut</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
         <v>The Scumbag Grift</v>
       </c>
-      <c r="B102" t="str">
-        <v/>
-      </c>
-      <c r="C102" t="str">
+      <c r="B103" t="str">
+        <v/>
+      </c>
+      <c r="C103" t="str">
         <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
       </c>
-      <c r="D102" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="E102" t="str">
-        <v/>
-      </c>
-      <c r="F102" t="str">
+      <c r="D103" t="str">
+        <v>2026-03-04</v>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
         <v>Cheap Heat</v>
       </c>
-      <c r="G102" t="str">
+      <c r="G103" t="str">
         <v>2:27</v>
       </c>
-      <c r="H102" t="str">
+      <c r="H103" t="str">
         <v>A Wilhelm Scream</v>
       </c>
-      <c r="I102" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J102" t="str">
+      <c r="I103" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J103" t="str">
         <v>https://music.apple.com/us/artist/a-wilhelm-scream/7375447</v>
       </c>
-      <c r="K102" t="str">
+      <c r="K103" t="str">
         <v>https://music.apple.com/us/album/the-scumbag-grift/1870588948</v>
       </c>
-      <c r="L102" t="str">
+      <c r="L103" t="str">
         <v>The Scumbag Grift - A Wilhelm Scream</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L102"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L103"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week01/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/medicine/1874168009</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/go/1870067581</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/ganga/1879903219</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/with-me/1874015492</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/miss-that/1875987505</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/old-technology/1867531318</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/alice/1874333652</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/tonto/1879859729</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/mariah/1874948938</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/blackhole/1873882200</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/walk/1875008123</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/flammable/1879896026</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/gentleman/1876982929</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/nyx00/1878551807</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/helicopters/1870313516</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/my-loving/1875970777</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/beautiful/1864389804</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/control-freak/1859044257</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/done-for/1873391195</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/moonlight/1878731568</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/free/1872250568</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/mantis/1868686720</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/the-blade/1876388273</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/the-place/1869119815</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/facts/1878765800</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/me-you/1878168773</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/badman/1877577830</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/automatic/1875133428</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-04</v>
+        <v>2026-03-05</v>
       </c>
       <c r="E103" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L103"/>
+  <dimension ref="A1:L104"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,40 +436,40 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Medicine</v>
+        <v>bad bitch alert</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/medicine/1874168009</v>
+        <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Medicine - Single</v>
+        <v>girl music vol. 1 - EP</v>
       </c>
       <c r="G2" t="str">
-        <v>2:34</v>
+        <v>2:24</v>
       </c>
       <c r="H2" t="str">
-        <v>Channel Tres</v>
+        <v>Ty Dolla $ign</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
+        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/medicine/1874168007</v>
+        <v>https://music.apple.com/us/album/bad-bitch-alert/1878416755</v>
       </c>
       <c r="L2" t="str">
-        <v>Medicine - Channel Tres</v>
+        <v>bad bitch alert - Ty Dolla $ign</v>
       </c>
     </row>
     <row r="3">
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/go/1870067581</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/ganga/1879903219</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/with-me/1874015492</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/miss-that/1875987505</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -854,40 +854,40 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SOMEWHERE ELSE</v>
+        <v>Medicine</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
+        <v>https://music.apple.com/us/song/medicine/1874168009</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>COME CLOSER</v>
+        <v>Medicine - Single</v>
       </c>
       <c r="G13" t="str">
-        <v>4:11</v>
+        <v>2:34</v>
       </c>
       <c r="H13" t="str">
-        <v>TOMORA</v>
+        <v>Channel Tres</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
+        <v>https://music.apple.com/us/album/medicine/1874168007</v>
       </c>
       <c r="L13" t="str">
-        <v>SOMEWHERE ELSE - TOMORA</v>
+        <v>Medicine - Channel Tres</v>
       </c>
     </row>
     <row r="14">
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -930,40 +930,40 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Dog</v>
+        <v>SOMEWHERE ELSE</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/dog/1871594836</v>
+        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Torn</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G15" t="str">
-        <v>2:37</v>
+        <v>4:11</v>
       </c>
       <c r="H15" t="str">
-        <v>Cobrah</v>
+        <v>TOMORA</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/dog/1871594546</v>
+        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
       </c>
       <c r="L15" t="str">
-        <v>Dog - Cobrah</v>
+        <v>SOMEWHERE ELSE - TOMORA</v>
       </c>
     </row>
     <row r="16">
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/old-technology/1867531318</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1006,3313 +1006,3351 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ALICE</v>
+        <v>Dog</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/alice/1874333652</v>
+        <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>PAREIDOLIA - EP</v>
+        <v>Torn</v>
       </c>
       <c r="G17" t="str">
-        <v>4:39</v>
+        <v>2:37</v>
       </c>
       <c r="H17" t="str">
-        <v>Erin LeCount</v>
+        <v>Cobrah</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/alice/1874333566</v>
+        <v>https://music.apple.com/us/album/dog/1871594546</v>
       </c>
       <c r="L17" t="str">
-        <v>ALICE - Erin LeCount</v>
+        <v>Dog - Cobrah</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Tiny Light</v>
+        <v>ALICE</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
+        <v>https://music.apple.com/us/song/alice/1874333652</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Tiny Light - Single</v>
+        <v>PAREIDOLIA - EP</v>
       </c>
       <c r="G18" t="str">
-        <v>3:27</v>
+        <v>4:39</v>
       </c>
       <c r="H18" t="str">
-        <v>SEVENTEEN</v>
+        <v>Erin LeCount</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
+        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
+        <v>https://music.apple.com/us/album/alice/1874333566</v>
       </c>
       <c r="L18" t="str">
-        <v>Tiny Light - SEVENTEEN</v>
+        <v>ALICE - Erin LeCount</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!)</v>
+        <v>Tiny Light</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
+        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
+        <v>Tiny Light - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>2:50</v>
+        <v>3:27</v>
       </c>
       <c r="H19" t="str">
-        <v>aespa</v>
+        <v>SEVENTEEN</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
+        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
       </c>
       <c r="L19" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
+        <v>Tiny Light - SEVENTEEN</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>16 YEAR OLD DRANK</v>
+        <v>Keychain (FROM THE FILM K-POPS!)</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
+        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>It's Us Vol. 2</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>3:23</v>
+        <v>2:50</v>
       </c>
       <c r="H20" t="str">
-        <v>Concrete Boys</v>
+        <v>aespa</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
+        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
       </c>
       <c r="L20" t="str">
-        <v>16 YEAR OLD DRANK - Concrete Boys</v>
+        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>If I Leave</v>
+        <v>16 YEAR OLD DRANK</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
+        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>It's Us Vol. 2</v>
       </c>
       <c r="G21" t="str">
-        <v>3:00</v>
+        <v>3:23</v>
       </c>
       <c r="H21" t="str">
-        <v>Mitski</v>
+        <v>Concrete Boys</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
+        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
       </c>
       <c r="L21" t="str">
-        <v>If I Leave - Mitski</v>
+        <v>16 YEAR OLD DRANK - Concrete Boys</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Time Will Tell</v>
+        <v>If I Leave</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
+        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Time Will Tell - Single</v>
+        <v>Nothing's About to Happen to Me</v>
       </c>
       <c r="G22" t="str">
-        <v>3:04</v>
+        <v>3:00</v>
       </c>
       <c r="H22" t="str">
-        <v>Lee Brice</v>
+        <v>Mitski</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
+        <v>https://music.apple.com/us/artist/mitski/497546276</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
+        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
       </c>
       <c r="L22" t="str">
-        <v>Time Will Tell - Lee Brice</v>
+        <v>If I Leave - Mitski</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>How I Get</v>
+        <v>Time Will Tell</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
+        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>Time Will Tell - Single</v>
       </c>
       <c r="G23" t="str">
-        <v>3:39</v>
+        <v>3:04</v>
       </c>
       <c r="H23" t="str">
-        <v>Laufey</v>
+        <v>Lee Brice</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
+        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
       </c>
       <c r="L23" t="str">
-        <v>How I Get - Laufey</v>
+        <v>Time Will Tell - Lee Brice</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7)</v>
+        <v>How I Get</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
+        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
+        <v>A Matter of Time: The Final Hour</v>
       </c>
       <c r="G24" t="str">
-        <v>3:19</v>
+        <v>3:39</v>
       </c>
       <c r="H24" t="str">
-        <v>Jessie Murph</v>
+        <v>Laufey</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
+        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
+        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
       </c>
       <c r="L24" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
+        <v>How I Get - Laufey</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Tonto</v>
+        <v>Criminal (From the Original Motion Picture Scream 7)</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/tonto/1879859729</v>
+        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Tonto - Single</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
       </c>
       <c r="G25" t="str">
-        <v>2:20</v>
+        <v>3:19</v>
       </c>
       <c r="H25" t="str">
-        <v>J Balvin</v>
+        <v>Jessie Murph</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/tonto/1879859725</v>
+        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
       </c>
       <c r="L25" t="str">
-        <v>Tonto - J Balvin</v>
+        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>nothin lasts 4ever</v>
+        <v>Tonto</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
+        <v>https://music.apple.com/us/song/tonto/1879859729</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>nothin lasts 4ever - Single</v>
+        <v>Tonto - Single</v>
       </c>
       <c r="G26" t="str">
-        <v>2:41</v>
+        <v>2:20</v>
       </c>
       <c r="H26" t="str">
-        <v>BLOND:ISH</v>
+        <v>J Balvin</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
+        <v>https://music.apple.com/us/album/tonto/1879859725</v>
       </c>
       <c r="L26" t="str">
-        <v>nothin lasts 4ever - BLOND:ISH</v>
+        <v>Tonto - J Balvin</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>MUERDO Mi LENGUA</v>
+        <v>nothin lasts 4ever</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
+        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>MUERDO Mi LENGUA - Single</v>
+        <v>nothin lasts 4ever - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>2:50</v>
+        <v>2:41</v>
       </c>
       <c r="H27" t="str">
-        <v>Bautiii</v>
+        <v>BLOND:ISH</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
+        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
+        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
       </c>
       <c r="L27" t="str">
-        <v>MUERDO Mi LENGUA - Bautiii</v>
+        <v>nothin lasts 4ever - BLOND:ISH</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage]</v>
+        <v>MUERDO Mi LENGUA</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
+        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
+        <v>MUERDO Mi LENGUA - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>3:41</v>
+        <v>2:50</v>
       </c>
       <c r="H28" t="str">
-        <v>Mýa</v>
+        <v>Bautiii</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
+        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
       </c>
       <c r="L28" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
+        <v>MUERDO Mi LENGUA - Bautiii</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Smugglers &amp; Scholars</v>
+        <v>ASAP (Remix) [feat. 21 Savage]</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
+        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>FENIAN</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>3:11</v>
+        <v>3:41</v>
       </c>
       <c r="H29" t="str">
-        <v>Kneecap</v>
+        <v>Mýa</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
+        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
       </c>
       <c r="L29" t="str">
-        <v>Smugglers &amp; Scholars - Kneecap</v>
+        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>What You Want</v>
+        <v>Smugglers &amp; Scholars</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
+        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>What You Want - Single</v>
+        <v>FENIAN</v>
       </c>
       <c r="G30" t="str">
-        <v>3:08</v>
+        <v>3:11</v>
       </c>
       <c r="H30" t="str">
-        <v>Angèle</v>
+        <v>Kneecap</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
+        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
+        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
       </c>
       <c r="L30" t="str">
-        <v>What You Want - Angèle</v>
+        <v>Smugglers &amp; Scholars - Kneecap</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>psychokiller</v>
+        <v>What You Want</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
+        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>getting up to no good</v>
+        <v>What You Want - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>1:53</v>
+        <v>3:08</v>
       </c>
       <c r="H31" t="str">
-        <v>Artemas</v>
+        <v>Angèle</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
+        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
       </c>
       <c r="L31" t="str">
-        <v>psychokiller - Artemas</v>
+        <v>What You Want - Angèle</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>DISNEY PRINCESS</v>
+        <v>psychokiller</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
+        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>HADES</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G32" t="str">
-        <v>4:05</v>
+        <v>1:53</v>
       </c>
       <c r="H32" t="str">
-        <v>Melanie Martinez</v>
+        <v>Artemas</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
+        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
       </c>
       <c r="L32" t="str">
-        <v>DISNEY PRINCESS - Melanie Martinez</v>
+        <v>psychokiller - Artemas</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>mariah</v>
+        <v>DISNEY PRINCESS</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/mariah/1874948938</v>
+        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>songs i couldn't forget - EP</v>
+        <v>HADES</v>
       </c>
       <c r="G33" t="str">
-        <v>2:48</v>
+        <v>4:05</v>
       </c>
       <c r="H33" t="str">
-        <v>Lauv</v>
+        <v>Melanie Martinez</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/mariah/1874948926</v>
+        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
       </c>
       <c r="L33" t="str">
-        <v>mariah - Lauv</v>
+        <v>DISNEY PRINCESS - Melanie Martinez</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>BLACKHOLE</v>
+        <v>mariah</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
+        <v>https://music.apple.com/us/song/mariah/1874948938</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>REVIVE+</v>
+        <v>songs i couldn't forget - EP</v>
       </c>
       <c r="G34" t="str">
-        <v>3:14</v>
+        <v>2:48</v>
       </c>
       <c r="H34" t="str">
-        <v>IVE</v>
+        <v>Lauv</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
+        <v>https://music.apple.com/us/album/mariah/1874948926</v>
       </c>
       <c r="L34" t="str">
-        <v>BLACKHOLE - IVE</v>
+        <v>mariah - Lauv</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Walk</v>
+        <v>BLACKHOLE</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/walk/1875008123</v>
+        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Walk - Single</v>
+        <v>REVIVE+</v>
       </c>
       <c r="G35" t="str">
-        <v>2:56</v>
+        <v>3:14</v>
       </c>
       <c r="H35" t="str">
-        <v>Skye Newman</v>
+        <v>IVE</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/ive/1594159996</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/walk/1875008118</v>
+        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
       </c>
       <c r="L35" t="str">
-        <v>Walk - Skye Newman</v>
+        <v>BLACKHOLE - IVE</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>FLAMMABLE</v>
+        <v>Walk</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/flammable/1879896026</v>
+        <v>https://music.apple.com/us/song/walk/1875008123</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>FLAMMABLE - Single</v>
+        <v>Walk - Single</v>
       </c>
       <c r="G36" t="str">
-        <v>3:17</v>
+        <v>2:56</v>
       </c>
       <c r="H36" t="str">
-        <v>Swae Lee</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/flammable/1879896025</v>
+        <v>https://music.apple.com/us/album/walk/1875008118</v>
       </c>
       <c r="L36" t="str">
-        <v>FLAMMABLE - Swae Lee</v>
+        <v>Walk - Skye Newman</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>3am (Remix)</v>
+        <v>FLAMMABLE</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
+        <v>https://music.apple.com/us/song/flammable/1879896026</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3am (Remix) - Single</v>
+        <v>FLAMMABLE - Single</v>
       </c>
       <c r="G37" t="str">
-        <v>2:44</v>
+        <v>3:17</v>
       </c>
       <c r="H37" t="str">
-        <v>Łaszewo</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/%C5%82aszewo/1438035296</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/3am-remix/1878278386</v>
+        <v>https://music.apple.com/us/album/flammable/1879896025</v>
       </c>
       <c r="L37" t="str">
-        <v>3am (Remix) - Łaszewo</v>
+        <v>FLAMMABLE - Swae Lee</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>mutual destruction</v>
+        <v>3am (Remix)</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
+        <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>mutual destruction - Single</v>
+        <v>3am (Remix) - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>2:31</v>
+        <v>2:44</v>
       </c>
       <c r="H38" t="str">
-        <v>kenzie</v>
+        <v>Łaszewo</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/%C5%82aszewo/1438035296</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
+        <v>https://music.apple.com/us/album/3am-remix/1878278386</v>
       </c>
       <c r="L38" t="str">
-        <v>mutual destruction - kenzie</v>
+        <v>3am (Remix) - Łaszewo</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Dear Worry</v>
+        <v>mutual destruction</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
+        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Dear Worry - Single</v>
+        <v>mutual destruction - Single</v>
       </c>
       <c r="G39" t="str">
-        <v>3:01</v>
+        <v>2:31</v>
       </c>
       <c r="H39" t="str">
-        <v>Common People</v>
+        <v>kenzie</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
+        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
       </c>
       <c r="L39" t="str">
-        <v>Dear Worry - Common People</v>
+        <v>mutual destruction - kenzie</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Gentleman</v>
+        <v>Dear Worry</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
+        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Gentleman - Single</v>
+        <v>Dear Worry - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>2:16</v>
+        <v>3:01</v>
       </c>
       <c r="H40" t="str">
-        <v>Towa Bird</v>
+        <v>Common People</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
+        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
       </c>
       <c r="L40" t="str">
-        <v>Gentleman - Towa Bird</v>
+        <v>Dear Worry - Common People</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>NYX00</v>
+        <v>Gentleman</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
+        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>NYX00 - Single</v>
+        <v>Gentleman - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>3:00</v>
+        <v>2:16</v>
       </c>
       <c r="H41" t="str">
-        <v>Dei V</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
+        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
+        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
       </c>
       <c r="L41" t="str">
-        <v>NYX00 - Dei V</v>
+        <v>Gentleman - Towa Bird</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Helicopters</v>
+        <v>NYX00</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
+        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>HELP(2)</v>
+        <v>NYX00 - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>3:58</v>
+        <v>3:00</v>
       </c>
       <c r="H42" t="str">
-        <v>Ezra Collective</v>
+        <v>Dei V</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
+        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
       </c>
       <c r="L42" t="str">
-        <v>Helicopters - Ezra Collective</v>
+        <v>NYX00 - Dei V</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
+        <v>Helicopters</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
+        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Max Richter: Hamnet Live</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G43" t="str">
-        <v>4:58</v>
+        <v>3:58</v>
       </c>
       <c r="H43" t="str">
-        <v>Max Richter</v>
+        <v>Ezra Collective</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
+        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
+        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
       </c>
       <c r="L43" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
+        <v>Helicopters - Ezra Collective</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>It's You I Want</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
+        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
+        <v>Max Richter: Hamnet Live</v>
       </c>
       <c r="G44" t="str">
-        <v>1:39</v>
+        <v>4:58</v>
       </c>
       <c r="H44" t="str">
-        <v>Kris Bowers</v>
+        <v>Max Richter</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
+        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
+        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
       </c>
       <c r="L44" t="str">
-        <v>It's You I Want - Kris Bowers</v>
+        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>If I Was With You</v>
+        <v>It's You I Want</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
+        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>If I Was With You - Single</v>
+        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
       </c>
       <c r="G45" t="str">
-        <v>3:25</v>
+        <v>1:39</v>
       </c>
       <c r="H45" t="str">
-        <v>Presley Regier</v>
+        <v>Kris Bowers</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
+        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
       </c>
       <c r="L45" t="str">
-        <v>If I Was With You - Presley Regier</v>
+        <v>It's You I Want - Kris Bowers</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Stay With Me</v>
+        <v>If I Was With You</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
+        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>If I Was With You - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>3:47</v>
+        <v>3:25</v>
       </c>
       <c r="H46" t="str">
-        <v>Nessa Barrett</v>
+        <v>Presley Regier</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
+        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
       </c>
       <c r="L46" t="str">
-        <v>Stay With Me - Nessa Barrett</v>
+        <v>If I Was With You - Presley Regier</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>My Loving</v>
+        <v>Stay With Me</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
+        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>My Loving - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G47" t="str">
-        <v>2:50</v>
+        <v>3:47</v>
       </c>
       <c r="H47" t="str">
-        <v>Sonny Fodera</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
+        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
       </c>
       <c r="L47" t="str">
-        <v>My Loving - Sonny Fodera</v>
+        <v>Stay With Me - Nessa Barrett</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Easy On The Eyes</v>
+        <v>My Loving</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
+        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Easy On The Eyes - Single</v>
+        <v>My Loving - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>3:44</v>
+        <v>2:50</v>
       </c>
       <c r="H48" t="str">
-        <v>Willow Avalon</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
+        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
       </c>
       <c r="L48" t="str">
-        <v>Easy On The Eyes - Willow Avalon</v>
+        <v>My Loving - Sonny Fodera</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Beautiful</v>
+        <v>Easy On The Eyes</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
+        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Let It Die Here</v>
+        <v>Easy On The Eyes - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>3:47</v>
+        <v>3:44</v>
       </c>
       <c r="H49" t="str">
-        <v>Linda Perry</v>
+        <v>Willow Avalon</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
+        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
       </c>
       <c r="L49" t="str">
-        <v>Beautiful - Linda Perry</v>
+        <v>Easy On The Eyes - Willow Avalon</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3")</v>
+        <v>Beautiful</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
+        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G50" t="str">
-        <v>4:34</v>
+        <v>3:47</v>
       </c>
       <c r="H50" t="str">
-        <v>Jason Segel</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
+        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
       </c>
       <c r="L50" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
+        <v>Beautiful - Linda Perry</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Control Freak</v>
+        <v>Nightswimming (from "Shrinking: Season 3")</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
+        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Control Freak - Single</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>2:53</v>
+        <v>4:34</v>
       </c>
       <c r="H51" t="str">
-        <v>Broadside</v>
+        <v>Jason Segel</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/broadside/169939373</v>
+        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
+        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
       </c>
       <c r="L51" t="str">
-        <v>Control Freak - Broadside</v>
+        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Done For</v>
+        <v>Control Freak</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/done-for/1873391195</v>
+        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Done For - Single</v>
+        <v>Control Freak - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>2:33</v>
+        <v>2:53</v>
       </c>
       <c r="H52" t="str">
-        <v>Max McNown</v>
+        <v>Broadside</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/broadside/169939373</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/done-for/1873391193</v>
+        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
       </c>
       <c r="L52" t="str">
-        <v>Done For - Max McNown</v>
+        <v>Control Freak - Broadside</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Ready for the Ride</v>
+        <v>Done For</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
+        <v>https://music.apple.com/us/song/done-for/1873391195</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Ready for the Ride - Single</v>
+        <v>Done For - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>3:27</v>
+        <v>2:33</v>
       </c>
       <c r="H53" t="str">
-        <v>Sean Paul</v>
+        <v>Max McNown</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
+        <v>https://music.apple.com/us/album/done-for/1873391193</v>
       </c>
       <c r="L53" t="str">
-        <v>Ready for the Ride - Sean Paul</v>
+        <v>Done For - Max McNown</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>push the pipe</v>
+        <v>Ready for the Ride</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
+        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>HYPERYOUTH (afterparty)</v>
+        <v>Ready for the Ride - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>3:08</v>
+        <v>3:27</v>
       </c>
       <c r="H54" t="str">
-        <v>Joey Valence &amp; Brae</v>
+        <v>Sean Paul</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
+        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
+        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
       </c>
       <c r="L54" t="str">
-        <v>push the pipe - Joey Valence &amp; Brae</v>
+        <v>Ready for the Ride - Sean Paul</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>push the pipe</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>With No Due Respect</v>
+        <v>HYPERYOUTH (afterparty)</v>
       </c>
       <c r="G55" t="str">
-        <v>3:13</v>
+        <v>3:08</v>
       </c>
       <c r="H55" t="str">
-        <v>Foggieraw</v>
+        <v>Joey Valence &amp; Brae</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
       </c>
       <c r="L55" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>push the pipe - Joey Valence &amp; Brae</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Moonlight</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>McKenzie 2.0</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G56" t="str">
-        <v>2:00</v>
+        <v>3:13</v>
       </c>
       <c r="H56" t="str">
-        <v>FattMack</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L56" t="str">
-        <v>Moonlight - FattMack</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Boat Named After You</v>
+        <v>Moonlight</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
+        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Boat Named After You - Single</v>
+        <v>McKenzie 2.0</v>
       </c>
       <c r="G57" t="str">
-        <v>3:56</v>
+        <v>2:00</v>
       </c>
       <c r="H57" t="str">
-        <v>ERNEST</v>
+        <v>FattMack</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
+        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
       </c>
       <c r="L57" t="str">
-        <v>Boat Named After You - ERNEST</v>
+        <v>Moonlight - FattMack</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>fall into you</v>
+        <v>Boat Named After You</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
+        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>fall into you - Single</v>
+        <v>Boat Named After You - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:28</v>
+        <v>3:56</v>
       </c>
       <c r="H58" t="str">
-        <v>Camylio</v>
+        <v>ERNEST</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
+        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
       </c>
       <c r="L58" t="str">
-        <v>fall into you - Camylio</v>
+        <v>Boat Named After You - ERNEST</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Van Gogh</v>
+        <v>fall into you</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
+        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Tales of a Failed Shapeshifter</v>
+        <v>fall into you - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>2:25</v>
+        <v>3:28</v>
       </c>
       <c r="H59" t="str">
-        <v>Em Beihold</v>
+        <v>Camylio</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
+        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
       </c>
       <c r="L59" t="str">
-        <v>Van Gogh - Em Beihold</v>
+        <v>fall into you - Camylio</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>popstar Nervous</v>
+        <v>Van Gogh</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
+        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>the rumors are true - EP</v>
+        <v>Tales of a Failed Shapeshifter</v>
       </c>
       <c r="G60" t="str">
         <v>2:25</v>
       </c>
       <c r="H60" t="str">
-        <v>DC THE DON</v>
+        <v>Em Beihold</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
+        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
       </c>
       <c r="L60" t="str">
-        <v>popstar Nervous - DC THE DON</v>
+        <v>Van Gogh - Em Beihold</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Free</v>
+        <v>popstar Nervous</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/free/1872250568</v>
+        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Free - Single</v>
+        <v>the rumors are true - EP</v>
       </c>
       <c r="G61" t="str">
-        <v>3:08</v>
+        <v>2:25</v>
       </c>
       <c r="H61" t="str">
-        <v>Beartooth</v>
+        <v>DC THE DON</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/free/1872250308</v>
+        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
       </c>
       <c r="L61" t="str">
-        <v>Free - Beartooth</v>
+        <v>popstar Nervous - DC THE DON</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>never come never morning</v>
+        <v>Free</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
+        <v>https://music.apple.com/us/song/free/1872250568</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>a short history of decay</v>
+        <v>Free - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>3:39</v>
+        <v>3:08</v>
       </c>
       <c r="H62" t="str">
-        <v>Nothing</v>
+        <v>Beartooth</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/nothing/593213453</v>
+        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
+        <v>https://music.apple.com/us/album/free/1872250308</v>
       </c>
       <c r="L62" t="str">
-        <v>never come never morning - Nothing</v>
+        <v>Free - Beartooth</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Over My Head</v>
+        <v>never come never morning</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
+        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>A Beautiful Lie (20 Year Anniversary)</v>
+        <v>a short history of decay</v>
       </c>
       <c r="G63" t="str">
-        <v>2:30</v>
+        <v>3:39</v>
       </c>
       <c r="H63" t="str">
-        <v>Thirty Seconds to Mars</v>
+        <v>Nothing</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
+        <v>https://music.apple.com/us/artist/nothing/593213453</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
+        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
       </c>
       <c r="L63" t="str">
-        <v>Over My Head - Thirty Seconds to Mars</v>
+        <v>never come never morning - Nothing</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Mantis</v>
+        <v>Over My Head</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/mantis/1868686720</v>
+        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Creature of Habit</v>
+        <v>A Beautiful Lie (20 Year Anniversary)</v>
       </c>
       <c r="G64" t="str">
-        <v>4:40</v>
+        <v>2:30</v>
       </c>
       <c r="H64" t="str">
-        <v>Courtney Barnett</v>
+        <v>Thirty Seconds to Mars</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/mantis/1868686713</v>
+        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
       </c>
       <c r="L64" t="str">
-        <v>Mantis - Courtney Barnett</v>
+        <v>Over My Head - Thirty Seconds to Mars</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Soft Launch</v>
+        <v>Mantis</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
+        <v>https://music.apple.com/us/song/mantis/1868686720</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Soft Launch - Single</v>
+        <v>Creature of Habit</v>
       </c>
       <c r="G65" t="str">
-        <v>2:25</v>
+        <v>4:40</v>
       </c>
       <c r="H65" t="str">
-        <v>Cely</v>
+        <v>Courtney Barnett</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/cely/1259609505</v>
+        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
+        <v>https://music.apple.com/us/album/mantis/1868686713</v>
       </c>
       <c r="L65" t="str">
-        <v>Soft Launch - Cely</v>
+        <v>Mantis - Courtney Barnett</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>picky choosy</v>
+        <v>Soft Launch</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
+        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Soft Launch - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>2:53</v>
+        <v>2:25</v>
       </c>
       <c r="H66" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Cely</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/cely/1259609505</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
+        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
       </c>
       <c r="L66" t="str">
-        <v>picky choosy - Chelsea Jordan</v>
+        <v>Soft Launch - Cely</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>La Mala Era Yo</v>
+        <v>picky choosy</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
+        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>La Mala Era Yo - Single</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G67" t="str">
-        <v>2:30</v>
+        <v>2:53</v>
       </c>
       <c r="H67" t="str">
-        <v>Kany García</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
+        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
       </c>
       <c r="L67" t="str">
-        <v>La Mala Era Yo - Kany García</v>
+        <v>picky choosy - Chelsea Jordan</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Quiet Part Loud</v>
+        <v>La Mala Era Yo</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
+        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Joy Next Door</v>
+        <v>La Mala Era Yo - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>3:08</v>
+        <v>2:30</v>
       </c>
       <c r="H68" t="str">
-        <v>The Maine</v>
+        <v>Kany García</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
+        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
       </c>
       <c r="L68" t="str">
-        <v>Quiet Part Loud - The Maine</v>
+        <v>La Mala Era Yo - Kany García</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>favorite girl</v>
+        <v>Quiet Part Loud</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
+        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>favorite girl - Single</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G69" t="str">
-        <v>3:24</v>
+        <v>3:08</v>
       </c>
       <c r="H69" t="str">
-        <v>Alaina Castillo</v>
+        <v>The Maine</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
+        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
       </c>
       <c r="L69" t="str">
-        <v>favorite girl - Alaina Castillo</v>
+        <v>Quiet Part Loud - The Maine</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>The Blade</v>
+        <v>favorite girl</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
+        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>The Blade - Single</v>
+        <v>favorite girl - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>3:15</v>
+        <v>3:24</v>
       </c>
       <c r="H70" t="str">
-        <v>Kingfishr</v>
+        <v>Alaina Castillo</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
+        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
       </c>
       <c r="L70" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>favorite girl - Alaina Castillo</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Blunt Force Blues</v>
+        <v>The Blade</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
+        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Into Oblivion</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>4:11</v>
+        <v>3:15</v>
       </c>
       <c r="H71" t="str">
-        <v>Lamb of God</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
+        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
       </c>
       <c r="L71" t="str">
-        <v>Blunt Force Blues - Lamb of God</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>The Black Scorpion</v>
+        <v>Blunt Force Blues</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
+        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>The Great Satan</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G72" t="str">
-        <v>1:33</v>
+        <v>4:11</v>
       </c>
       <c r="H72" t="str">
-        <v>Rob Zombie</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
+        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
       </c>
       <c r="L72" t="str">
-        <v>The Black Scorpion - Rob Zombie</v>
+        <v>Blunt Force Blues - Lamb of God</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>The Place</v>
+        <v>The Black Scorpion</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/the-place/1869119815</v>
+        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>The Great Satan</v>
       </c>
       <c r="G73" t="str">
-        <v>5:58</v>
+        <v>1:33</v>
       </c>
       <c r="H73" t="str">
-        <v>Sepultura</v>
+        <v>Rob Zombie</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/the-place/1869119453</v>
+        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
       </c>
       <c r="L73" t="str">
-        <v>The Place - Sepultura</v>
+        <v>The Black Scorpion - Rob Zombie</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>SONG OF THE SWAMP</v>
+        <v>The Place</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
+        <v>https://music.apple.com/us/song/the-place/1869119815</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>The Cloud Of Unknowing - EP</v>
       </c>
       <c r="G74" t="str">
-        <v>3:18</v>
+        <v>5:58</v>
       </c>
       <c r="H74" t="str">
-        <v>Wage War</v>
+        <v>Sepultura</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/sepultura/918092</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
+        <v>https://music.apple.com/us/album/the-place/1869119453</v>
       </c>
       <c r="L74" t="str">
-        <v>SONG OF THE SWAMP - Wage War</v>
+        <v>The Place - Sepultura</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez)</v>
+        <v>SONG OF THE SWAMP</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
+        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G75" t="str">
-        <v>2:26</v>
+        <v>3:18</v>
       </c>
       <c r="H75" t="str">
-        <v>LOS DOS DE TAMAULIPAS</v>
+        <v>Wage War</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
+        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
       </c>
       <c r="L75" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
+        <v>SONG OF THE SWAMP - Wage War</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Tu Cárcel</v>
+        <v>Súper Snake (feat. Luis R Conriquez)</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
+        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Tu Cárcel - Single</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>3:36</v>
+        <v>2:26</v>
       </c>
       <c r="H76" t="str">
-        <v>Morat</v>
+        <v>LOS DOS DE TAMAULIPAS</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/morat/955657302</v>
+        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
+        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
       </c>
       <c r="L76" t="str">
-        <v>Tu Cárcel - Morat</v>
+        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Facts</v>
+        <v>Tu Cárcel</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/facts/1878765800</v>
+        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Be Very Afraid (Vol. 1)</v>
+        <v>Tu Cárcel - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>3:29</v>
+        <v>3:36</v>
       </c>
       <c r="H77" t="str">
-        <v>CHASE B</v>
+        <v>Morat</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
+        <v>https://music.apple.com/us/artist/morat/955657302</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/facts/1878765796</v>
+        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
       </c>
       <c r="L77" t="str">
-        <v>Facts - CHASE B</v>
+        <v>Tu Cárcel - Morat</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>me &amp; you</v>
+        <v>Facts</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/me-you/1878168773</v>
+        <v>https://music.apple.com/us/song/facts/1878765800</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>big country</v>
+        <v>Be Very Afraid (Vol. 1)</v>
       </c>
       <c r="G78" t="str">
-        <v>2:29</v>
+        <v>3:29</v>
       </c>
       <c r="H78" t="str">
-        <v>sosocamo</v>
+        <v>CHASE B</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
+        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/me-you/1878168770</v>
+        <v>https://music.apple.com/us/album/facts/1878765796</v>
       </c>
       <c r="L78" t="str">
-        <v>me &amp; you - sosocamo</v>
+        <v>Facts - CHASE B</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>badman</v>
+        <v>me &amp; you</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/badman/1877577830</v>
+        <v>https://music.apple.com/us/song/me-you/1878168773</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>badman - Single</v>
+        <v>big country</v>
       </c>
       <c r="G79" t="str">
-        <v>2:54</v>
+        <v>2:29</v>
       </c>
       <c r="H79" t="str">
-        <v>nomi.</v>
+        <v>sosocamo</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
+        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/badman/1877577829</v>
+        <v>https://music.apple.com/us/album/me-you/1878168770</v>
       </c>
       <c r="L79" t="str">
-        <v>badman - nomi.</v>
+        <v>me &amp; you - sosocamo</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Shut It Down</v>
+        <v>badman</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
+        <v>https://music.apple.com/us/song/badman/1877577830</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Shut It Down - Single</v>
+        <v>badman - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>2:26</v>
+        <v>2:54</v>
       </c>
       <c r="H80" t="str">
-        <v>TheARTI$t</v>
+        <v>nomi.</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
+        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
+        <v>https://music.apple.com/us/album/badman/1877577829</v>
       </c>
       <c r="L80" t="str">
-        <v>Shut It Down - TheARTI$t</v>
+        <v>badman - nomi.</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>AUTOMATIC</v>
+        <v>Shut It Down</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/automatic/1875133428</v>
+        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>AUTOMATIC - Single</v>
+        <v>Shut It Down - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>2:08</v>
+        <v>2:26</v>
       </c>
       <c r="H81" t="str">
-        <v>Hulvey</v>
+        <v>TheARTI$t</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/automatic/1875133426</v>
+        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
       </c>
       <c r="L81" t="str">
-        <v>AUTOMATIC - Hulvey</v>
+        <v>Shut It Down - TheARTI$t</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Leaving Egypt</v>
+        <v>AUTOMATIC</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
+        <v>https://music.apple.com/us/song/automatic/1875133428</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Leaving Egypt - Single</v>
+        <v>AUTOMATIC - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>3:17</v>
+        <v>2:08</v>
       </c>
       <c r="H82" t="str">
-        <v>Alex Jude</v>
+        <v>Hulvey</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
+        <v>https://music.apple.com/us/album/automatic/1875133426</v>
       </c>
       <c r="L82" t="str">
-        <v>Leaving Egypt - Alex Jude</v>
+        <v>AUTOMATIC - Hulvey</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Not Your Mother</v>
+        <v>Leaving Egypt</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
+        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Not Your Mother - Single</v>
+        <v>Leaving Egypt - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>3:03</v>
+        <v>3:17</v>
       </c>
       <c r="H83" t="str">
-        <v>gracie</v>
+        <v>Alex Jude</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
+        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
+        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
       </c>
       <c r="L83" t="str">
-        <v>Not Your Mother - gracie</v>
+        <v>Leaving Egypt - Alex Jude</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
+        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Born to Kill</v>
+        <v>Not Your Mother - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>3:50</v>
+        <v>3:03</v>
       </c>
       <c r="H84" t="str">
-        <v>Social Distortion</v>
+        <v>gracie</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
+        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
       </c>
       <c r="L84" t="str">
-        <v>Born to Kill - Social Distortion</v>
+        <v>Not Your Mother - gracie</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>When the Love is Gone</v>
+        <v>Born to Kill</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
+        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>When the Love is Gone - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G85" t="str">
-        <v>3:20</v>
+        <v>3:50</v>
       </c>
       <c r="H85" t="str">
-        <v>Des Rocs</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
+        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
       </c>
       <c r="L85" t="str">
-        <v>When the Love is Gone - Des Rocs</v>
+        <v>Born to Kill - Social Distortion</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Miami Crest</v>
+        <v>When the Love is Gone</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
+        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Miami Crest - Single</v>
+        <v>When the Love is Gone - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>2:39</v>
+        <v>3:20</v>
       </c>
       <c r="H86" t="str">
-        <v>Namasenda</v>
+        <v>Des Rocs</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
+        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
+        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
       </c>
       <c r="L86" t="str">
-        <v>Miami Crest - Namasenda</v>
+        <v>When the Love is Gone - Des Rocs</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Say No Prayer</v>
+        <v>Miami Crest</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
+        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Say No Prayer - Single</v>
+        <v>Miami Crest - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>2:29</v>
+        <v>2:39</v>
       </c>
       <c r="H87" t="str">
-        <v>oskar med k</v>
+        <v>Namasenda</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
+        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
+        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
       </c>
       <c r="L87" t="str">
-        <v>Say No Prayer - oskar med k</v>
+        <v>Miami Crest - Namasenda</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>You Always Liked Me Better When I Was Stoned</v>
+        <v>Say No Prayer</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
+        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - Single</v>
+        <v>Say No Prayer - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>3:09</v>
+        <v>2:29</v>
       </c>
       <c r="H88" t="str">
-        <v>eee gee</v>
+        <v>oskar med k</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
+        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
+        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
       </c>
       <c r="L88" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
+        <v>Say No Prayer - oskar med k</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Pink Tongue</v>
+        <v>You Always Liked Me Better When I Was Stoned</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
+        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Porcelain Heart</v>
+        <v>You Always Liked Me Better When I Was Stoned - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>3:43</v>
+        <v>3:09</v>
       </c>
       <c r="H89" t="str">
-        <v>Diane Emerita</v>
+        <v>eee gee</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
+        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
+        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
       </c>
       <c r="L89" t="str">
-        <v>Pink Tongue - Diane Emerita</v>
+        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Hey, Bluebird</v>
+        <v>Pink Tongue</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
+        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Hey, Bluebird - Single</v>
+        <v>Porcelain Heart</v>
       </c>
       <c r="G90" t="str">
-        <v>3:23</v>
+        <v>3:43</v>
       </c>
       <c r="H90" t="str">
-        <v>Ber</v>
+        <v>Diane Emerita</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/ber/1020679397</v>
+        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
+        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
       </c>
       <c r="L90" t="str">
-        <v>Hey, Bluebird - Ber</v>
+        <v>Pink Tongue - Diane Emerita</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>You’ll Be The Proof</v>
+        <v>Hey, Bluebird</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
+        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>You’ll Be The Proof - Single</v>
+        <v>Hey, Bluebird - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>3:26</v>
+        <v>3:23</v>
       </c>
       <c r="H91" t="str">
-        <v>Forest Blakk</v>
+        <v>Ber</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
+        <v>https://music.apple.com/us/artist/ber/1020679397</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
+        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
       </c>
       <c r="L91" t="str">
-        <v>You’ll Be The Proof - Forest Blakk</v>
+        <v>Hey, Bluebird - Ber</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Heartbeat</v>
+        <v>You’ll Be The Proof</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
+        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Heartbeat - Single</v>
+        <v>You’ll Be The Proof - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>2:52</v>
+        <v>3:26</v>
       </c>
       <c r="H92" t="str">
-        <v>Lola Blue</v>
+        <v>Forest Blakk</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
+        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
       </c>
       <c r="L92" t="str">
-        <v>Heartbeat - Lola Blue</v>
+        <v>You’ll Be The Proof - Forest Blakk</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Imitation (how to become you)</v>
+        <v>Heartbeat</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
+        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Imitation (how to become you) - Single</v>
+        <v>Heartbeat - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>4:16</v>
+        <v>2:52</v>
       </c>
       <c r="H93" t="str">
-        <v>doggone</v>
+        <v>Lola Blue</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
+        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
+        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
       </c>
       <c r="L93" t="str">
-        <v>Imitation (how to become you) - doggone</v>
+        <v>Heartbeat - Lola Blue</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>I’m Every Woman</v>
+        <v>Imitation (how to become you)</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
+        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Cover Girl - EP</v>
+        <v>Imitation (how to become you) - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>4:35</v>
+        <v>4:16</v>
       </c>
       <c r="H94" t="str">
-        <v>Ashley Jackson</v>
+        <v>doggone</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
+        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
+        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
       </c>
       <c r="L94" t="str">
-        <v>I’m Every Woman - Ashley Jackson</v>
+        <v>Imitation (how to become you) - doggone</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Hard To See (feat. Norah Jones)</v>
+        <v>I’m Every Woman</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
+        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Infinite Source Of Heat</v>
+        <v>Cover Girl - EP</v>
       </c>
       <c r="G95" t="str">
-        <v>2:46</v>
+        <v>4:35</v>
       </c>
       <c r="H95" t="str">
-        <v>Chris Morrissey</v>
+        <v>Ashley Jackson</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
+        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
+        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
       </c>
       <c r="L95" t="str">
-        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
+        <v>I’m Every Woman - Ashley Jackson</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Slow Tonight</v>
+        <v>Hard To See (feat. Norah Jones)</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
+        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Full Circle</v>
+        <v>Infinite Source Of Heat</v>
       </c>
       <c r="G96" t="str">
-        <v>3:12</v>
+        <v>2:46</v>
       </c>
       <c r="H96" t="str">
-        <v>Tom Misch</v>
+        <v>Chris Morrissey</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
+        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
       </c>
       <c r="L96" t="str">
-        <v>Slow Tonight - Tom Misch</v>
+        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Freak No More</v>
+        <v>Slow Tonight</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
+        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Freak No More - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G97" t="str">
-        <v>3:57</v>
+        <v>3:12</v>
       </c>
       <c r="H97" t="str">
-        <v>AC Slater</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
+        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
       </c>
       <c r="L97" t="str">
-        <v>Freak No More - AC Slater</v>
+        <v>Slow Tonight - Tom Misch</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Don't Stop</v>
+        <v>Freak No More</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
+        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>Don't Stop - Single</v>
+        <v>Freak No More - Single</v>
       </c>
       <c r="G98" t="str">
-        <v>2:55</v>
+        <v>3:57</v>
       </c>
       <c r="H98" t="str">
-        <v>HoneyLuv</v>
+        <v>AC Slater</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
+        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
+        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
       </c>
       <c r="L98" t="str">
-        <v>Don't Stop - HoneyLuv</v>
+        <v>Freak No More - AC Slater</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Cause I Do</v>
+        <v>Don't Stop</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
+        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>Cause I Do - Single</v>
+        <v>Don't Stop - Single</v>
       </c>
       <c r="G99" t="str">
-        <v>2:39</v>
+        <v>2:55</v>
       </c>
       <c r="H99" t="str">
-        <v>Preston Pablo</v>
+        <v>HoneyLuv</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
+        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
+        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
       </c>
       <c r="L99" t="str">
-        <v>Cause I Do - Preston Pablo</v>
+        <v>Don't Stop - HoneyLuv</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Morning Comes</v>
+        <v>Cause I Do</v>
       </c>
       <c r="B100" t="str">
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
+        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>Heavy On The Soul</v>
+        <v>Cause I Do - Single</v>
       </c>
       <c r="G100" t="str">
-        <v>4:11</v>
+        <v>2:39</v>
       </c>
       <c r="H100" t="str">
-        <v>Ty Myers</v>
+        <v>Preston Pablo</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
+        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
       </c>
       <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
+        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
       </c>
       <c r="L100" t="str">
-        <v>Morning Comes - Ty Myers</v>
+        <v>Cause I Do - Preston Pablo</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>BETTER ON ME</v>
+        <v>Morning Comes</v>
       </c>
       <c r="B101" t="str">
         <v/>
       </c>
       <c r="C101" t="str">
-        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
+        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>BETTER ON ME - Single</v>
+        <v>Heavy On The Soul</v>
       </c>
       <c r="G101" t="str">
-        <v>3:24</v>
+        <v>4:11</v>
       </c>
       <c r="H101" t="str">
-        <v>Johnny Huynh</v>
+        <v>Ty Myers</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J101" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
+        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
       </c>
       <c r="K101" t="str">
-        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
+        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
       </c>
       <c r="L101" t="str">
-        <v>BETTER ON ME - Johnny Huynh</v>
+        <v>Morning Comes - Ty Myers</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Speed or Perish</v>
+        <v>BETTER ON ME</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-06</v>
       </c>
       <c r="E102" t="str">
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Leather Temple</v>
+        <v>BETTER ON ME - Single</v>
       </c>
       <c r="G102" t="str">
-        <v>4:30</v>
+        <v>3:24</v>
       </c>
       <c r="H102" t="str">
-        <v>Carpenter Brut</v>
+        <v>Johnny Huynh</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
       </c>
       <c r="L102" t="str">
-        <v>Speed or Perish - Carpenter Brut</v>
+        <v>BETTER ON ME - Johnny Huynh</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
+        <v>Speed or Perish</v>
+      </c>
+      <c r="B103" t="str">
+        <v/>
+      </c>
+      <c r="C103" t="str">
+        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
+      </c>
+      <c r="D103" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v>Leather Temple</v>
+      </c>
+      <c r="G103" t="str">
+        <v>4:30</v>
+      </c>
+      <c r="H103" t="str">
+        <v>Carpenter Brut</v>
+      </c>
+      <c r="I103" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J103" t="str">
+        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
+      </c>
+      <c r="K103" t="str">
+        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
+      </c>
+      <c r="L103" t="str">
+        <v>Speed or Perish - Carpenter Brut</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
         <v>The Scumbag Grift</v>
       </c>
-      <c r="B103" t="str">
-        <v/>
-      </c>
-      <c r="C103" t="str">
+      <c r="B104" t="str">
+        <v/>
+      </c>
+      <c r="C104" t="str">
         <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
       </c>
-      <c r="D103" t="str">
-        <v>2026-03-05</v>
-      </c>
-      <c r="E103" t="str">
-        <v/>
-      </c>
-      <c r="F103" t="str">
+      <c r="D104" t="str">
+        <v>2026-03-06</v>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
         <v>Cheap Heat</v>
       </c>
-      <c r="G103" t="str">
+      <c r="G104" t="str">
         <v>2:27</v>
       </c>
-      <c r="H103" t="str">
+      <c r="H104" t="str">
         <v>A Wilhelm Scream</v>
       </c>
-      <c r="I103" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J103" t="str">
+      <c r="I104" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J104" t="str">
         <v>https://music.apple.com/us/artist/a-wilhelm-scream/7375447</v>
       </c>
-      <c r="K103" t="str">
+      <c r="K104" t="str">
         <v>https://music.apple.com/us/album/the-scumbag-grift/1870588948</v>
       </c>
-      <c r="L103" t="str">
+      <c r="L104" t="str">
         <v>The Scumbag Grift - A Wilhelm Scream</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L103"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L104"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L104"/>
+  <dimension ref="A1:L98"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>bad bitch alert</v>
+        <v>American Girls</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
+        <v>https://music.apple.com/us/song/american-girls/1870984036</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-06</v>
@@ -451,36 +451,36 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>girl music vol. 1 - EP</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G2" t="str">
-        <v>2:24</v>
+        <v>3:33</v>
       </c>
       <c r="H2" t="str">
-        <v>Ty Dolla $ign</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch-alert/1878416755</v>
+        <v>https://music.apple.com/us/album/american-girls/1870984032</v>
       </c>
       <c r="L2" t="str">
-        <v>bad bitch alert - Ty Dolla $ign</v>
+        <v>American Girls - Harry Styles</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought)</v>
+        <v>ALGO TÚ</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>https://music.apple.com/us/song/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237761</v>
+        <v>https://music.apple.com/us/song/algo-t%C3%BA/1880768673</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-06</v>
@@ -489,36 +489,36 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>The Mountain</v>
+        <v>ALGO TÚ - Single</v>
       </c>
       <c r="G3" t="str">
-        <v>4:57</v>
+        <v>3:33</v>
       </c>
       <c r="H3" t="str">
-        <v>Gorillaz</v>
+        <v>Shakira</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
-        <v>https://music.apple.com/us/artist/gorillaz/567072</v>
+        <v>https://music.apple.com/us/artist/shakira/889327</v>
       </c>
       <c r="K3" t="str">
-        <v>https://music.apple.com/us/album/the-moon-cave-feat-asha-puthli-bobby-womack-david/1837237742</v>
+        <v>https://music.apple.com/us/album/algo-t%C3%BA/1880768670</v>
       </c>
       <c r="L3" t="str">
-        <v>The Moon Cave (feat. Asha Puthli, Bobby Womack, David Jolicoeur, Jalen Ngonda &amp; Black Thought) - Gorillaz</v>
+        <v>ALGO TÚ - Shakira</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>GO</v>
+        <v>New Religion</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>https://music.apple.com/us/song/go/1870067581</v>
+        <v>https://music.apple.com/us/song/new-religion/1878015314</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-06</v>
@@ -527,36 +527,36 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>DEADLINE - EP</v>
+        <v>New Religion - Single</v>
       </c>
       <c r="G4" t="str">
-        <v>3:15</v>
+        <v>2:54</v>
       </c>
       <c r="H4" t="str">
-        <v>BLACKPINK</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
-        <v>https://music.apple.com/us/artist/blackpink/1141774019</v>
+        <v>https://music.apple.com/us/artist/bebe-rexha/466059563</v>
       </c>
       <c r="K4" t="str">
-        <v>https://music.apple.com/us/album/go/1870067304</v>
+        <v>https://music.apple.com/us/album/new-religion/1878015313</v>
       </c>
       <c r="L4" t="str">
-        <v>GO - BLACKPINK</v>
+        <v>New Religion - Bebe Rexha</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Risk It All</v>
+        <v>Where Do We Go</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/risk-it-all/1866732797</v>
+        <v>https://music.apple.com/us/song/where-do-we-go/1880521218</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-06</v>
@@ -565,36 +565,36 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>The Romantic</v>
+        <v>Where Do We Go - Single</v>
       </c>
       <c r="G5" t="str">
-        <v>3:24</v>
+        <v>2:56</v>
       </c>
       <c r="H5" t="str">
-        <v>Bruno Mars</v>
+        <v>Ayra Starr</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/ayra-starr/1536429348</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/risk-it-all/1866732792</v>
+        <v>https://music.apple.com/us/album/where-do-we-go/1880521216</v>
       </c>
       <c r="L5" t="str">
-        <v>Risk It All - Bruno Mars</v>
+        <v>Where Do We Go - Ayra Starr</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>FEVER DREAM</v>
+        <v>if you wanna party, come over to my house</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>https://music.apple.com/us/song/fever-dream/1879983789</v>
+        <v>https://music.apple.com/us/song/if-you-wanna-party-come-over-to-my-house/1861895281</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-06</v>
@@ -603,36 +603,36 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>FEVER DREAM - Single</v>
+        <v>Ö</v>
       </c>
       <c r="G6" t="str">
-        <v>2:33</v>
+        <v>2:51</v>
       </c>
       <c r="H6" t="str">
-        <v>Alex Warren</v>
+        <v>Fcukers</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v>https://music.apple.com/us/artist/fcukers/1679474991</v>
       </c>
       <c r="K6" t="str">
-        <v>https://music.apple.com/us/album/fever-dream/1879983782</v>
+        <v>https://music.apple.com/us/album/if-you-wanna-party-come-over-to-my-house/1861895134</v>
       </c>
       <c r="L6" t="str">
-        <v>FEVER DREAM - Alex Warren</v>
+        <v>if you wanna party, come over to my house - Fcukers</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Nightingale Lane.</v>
+        <v>We Don’t Get Along</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>https://music.apple.com/us/song/nightingale-lane/1871085724</v>
+        <v>https://music.apple.com/us/song/we-dont-get-along/1880045873</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-06</v>
@@ -641,36 +641,36 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
+        <v>We Don’t Get Along - Single</v>
       </c>
       <c r="G7" t="str">
-        <v>5:02</v>
+        <v>2:29</v>
       </c>
       <c r="H7" t="str">
-        <v>RAYE</v>
+        <v>Juice WRLD</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
-        <v>https://music.apple.com/us/artist/raye/261686</v>
+        <v>https://music.apple.com/us/artist/juice-wrld/1368733420</v>
       </c>
       <c r="K7" t="str">
-        <v>https://music.apple.com/us/album/nightingale-lane/1871085677</v>
+        <v>https://music.apple.com/us/album/we-dont-get-along/1880045872</v>
       </c>
       <c r="L7" t="str">
-        <v>Nightingale Lane. - RAYE</v>
+        <v>We Don’t Get Along - Juice WRLD</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Made It On Our Own</v>
+        <v>bad bitch alert</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>https://music.apple.com/us/song/made-it-on-our-own/1880447180</v>
+        <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-06</v>
@@ -679,36 +679,36 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>Made It On Our Own - Single</v>
+        <v>girl music vol. 1 - EP</v>
       </c>
       <c r="G8" t="str">
-        <v>2:49</v>
+        <v>2:24</v>
       </c>
       <c r="H8" t="str">
-        <v>Yeat</v>
+        <v>Ty Dolla $ign</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
-        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
+        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
       </c>
       <c r="K8" t="str">
-        <v>https://music.apple.com/us/album/made-it-on-our-own/1880447179</v>
+        <v>https://music.apple.com/us/album/bad-bitch-alert/1878416755</v>
       </c>
       <c r="L8" t="str">
-        <v>Made It On Our Own - Yeat</v>
+        <v>bad bitch alert - Ty Dolla $ign</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ganga</v>
+        <v>Medicine</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/ganga/1879903219</v>
+        <v>https://music.apple.com/us/song/medicine/1874168009</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-06</v>
@@ -717,36 +717,36 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>DINASTÍA (DELUXE)</v>
+        <v>Medicine - Single</v>
       </c>
       <c r="G9" t="str">
-        <v>2:45</v>
+        <v>2:34</v>
       </c>
       <c r="H9" t="str">
-        <v>Peso Pluma</v>
+        <v>Channel Tres</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/peso-pluma/1500139475</v>
+        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/ganga/1879902711</v>
+        <v>https://music.apple.com/us/album/medicine/1874168007</v>
       </c>
       <c r="L9" t="str">
-        <v>ganga - Peso Pluma</v>
+        <v>Medicine - Channel Tres</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>WITH ME</v>
+        <v>SOMEWHERE ELSE</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>https://music.apple.com/us/song/with-me/1874015492</v>
+        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-06</v>
@@ -755,36 +755,36 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G10" t="str">
-        <v>3:03</v>
+        <v>4:11</v>
       </c>
       <c r="H10" t="str">
-        <v>John Summit</v>
+        <v>TOMORA</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K10" t="str">
-        <v>https://music.apple.com/us/album/with-me/1874015470</v>
+        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
       </c>
       <c r="L10" t="str">
-        <v>WITH ME - John Summit</v>
+        <v>SOMEWHERE ELSE - TOMORA</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Sorry... I Meant Tonight (Bonus)</v>
+        <v>Dog</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/sorry-i-meant-tonight-bonus/1880181826</v>
+        <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-06</v>
@@ -793,36 +793,36 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>Cloud 9</v>
+        <v>Torn</v>
       </c>
       <c r="G11" t="str">
-        <v>3:33</v>
+        <v>2:37</v>
       </c>
       <c r="H11" t="str">
-        <v>Megan Moroney</v>
+        <v>Cobrah</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/sorry-i-meant-tonight-bonus/1880181535</v>
+        <v>https://music.apple.com/us/album/dog/1871594546</v>
       </c>
       <c r="L11" t="str">
-        <v>Sorry... I Meant Tonight (Bonus) - Megan Moroney</v>
+        <v>Dog - Cobrah</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Miss That</v>
+        <v>Dance No More</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/miss-that/1875987505</v>
+        <v>https://music.apple.com/us/song/dance-no-more/1870984050</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-06</v>
@@ -831,36 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>Miss That - Single</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G12" t="str">
-        <v>2:56</v>
+        <v>3:14</v>
       </c>
       <c r="H12" t="str">
-        <v>Naomi Sharon</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/miss-that/1875987504</v>
+        <v>https://music.apple.com/us/album/dance-no-more/1870984032</v>
       </c>
       <c r="L12" t="str">
-        <v>Miss That - Naomi Sharon</v>
+        <v>Dance No More - Harry Styles</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Medicine</v>
+        <v>Burial (from Mother Mary)</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/medicine/1874168009</v>
+        <v>https://music.apple.com/us/song/burial-from-mother-mary/1879807598</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-06</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Medicine - Single</v>
+        <v>Burial (from Mother Mary) - Single</v>
       </c>
       <c r="G13" t="str">
-        <v>2:34</v>
+        <v>3:09</v>
       </c>
       <c r="H13" t="str">
-        <v>Channel Tres</v>
+        <v>Anne Hathaway</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
+        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/medicine/1874168007</v>
+        <v>https://music.apple.com/us/album/burial-from-mother-mary/1879807585</v>
       </c>
       <c r="L13" t="str">
-        <v>Medicine - Channel Tres</v>
+        <v>Burial (from Mother Mary) - Anne Hathaway</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>glass houses</v>
+        <v>Tweak</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/glass-houses/1875303124</v>
+        <v>https://music.apple.com/us/song/tweak/1875414202</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-06</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>ghosted - EP</v>
+        <v>Tweak - Single</v>
       </c>
       <c r="G14" t="str">
-        <v>2:09</v>
+        <v>2:28</v>
       </c>
       <c r="H14" t="str">
-        <v>Saint Harison</v>
+        <v>GIRLSET</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/girlset/1833111616</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/glass-houses/1875302904</v>
+        <v>https://music.apple.com/us/album/tweak/1875414200</v>
       </c>
       <c r="L14" t="str">
-        <v>glass houses - Saint Harison</v>
+        <v>Tweak - GIRLSET</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SOMEWHERE ELSE</v>
+        <v>ATTITUDE</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
+        <v>https://music.apple.com/us/song/attitude/1879665813</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-06</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>COME CLOSER</v>
+        <v>ATTITUDE - Single</v>
       </c>
       <c r="G15" t="str">
-        <v>4:11</v>
+        <v>3:05</v>
       </c>
       <c r="H15" t="str">
-        <v>TOMORA</v>
+        <v>aespa</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/somewhere-else/1871184398</v>
+        <v>https://music.apple.com/us/album/attitude/1879665810</v>
       </c>
       <c r="L15" t="str">
-        <v>SOMEWHERE ELSE - TOMORA</v>
+        <v>ATTITUDE - aespa</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>OLD TECHNOLOGY</v>
+        <v>Blame Texas</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/old-technology/1867531318</v>
+        <v>https://music.apple.com/us/song/blame-texas/1879648698</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-06</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>WOR$T GIRL IN AMERICA</v>
+        <v>Blame Texas - Single</v>
       </c>
       <c r="G16" t="str">
-        <v>2:39</v>
+        <v>3:12</v>
       </c>
       <c r="H16" t="str">
-        <v>Slayyyter</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/old-technology/1867530577</v>
+        <v>https://music.apple.com/us/album/blame-texas/1879648687</v>
       </c>
       <c r="L16" t="str">
-        <v>OLD TECHNOLOGY - Slayyyter</v>
+        <v>Blame Texas - Cody Johnson</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Dog</v>
+        <v>Kerosene</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/dog/1871594836</v>
+        <v>https://music.apple.com/us/song/kerosene/1878542369</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-06</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Torn</v>
+        <v>Kerosene - Single</v>
       </c>
       <c r="G17" t="str">
-        <v>2:37</v>
+        <v>3:26</v>
       </c>
       <c r="H17" t="str">
-        <v>Cobrah</v>
+        <v>The Warning</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/cobrah/1441162293</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/dog/1871594546</v>
+        <v>https://music.apple.com/us/album/kerosene/1878542368</v>
       </c>
       <c r="L17" t="str">
-        <v>Dog - Cobrah</v>
+        <v>Kerosene - The Warning</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ALICE</v>
+        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™]</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/alice/1874333652</v>
+        <v>https://music.apple.com/us/song/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499140</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-06</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>PAREIDOLIA - EP</v>
+        <v>JUMP (Coca-Cola Anthem for the FIFA World Cup 26™) [feat. Steve Vai &amp; Travis Barker] - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>4:39</v>
+        <v>3:28</v>
       </c>
       <c r="H18" t="str">
-        <v>Erin LeCount</v>
+        <v>J Balvin</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/erin-lecount/1637270394</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/alice/1874333566</v>
+        <v>https://music.apple.com/us/album/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499139</v>
       </c>
       <c r="L18" t="str">
-        <v>ALICE - Erin LeCount</v>
+        <v>Jump (feat. Steve Vai &amp; Travis Barker) [Coca-Cola Anthem for the FIFA World Cup 26™] - J Balvin</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Tiny Light</v>
+        <v>Save Me Tonight</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/tiny-light/1877599754</v>
+        <v>https://music.apple.com/us/song/save-me-tonight/1878974345</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-06</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Tiny Light - Single</v>
+        <v>Save Me Tonight - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>3:27</v>
+        <v>3:16</v>
       </c>
       <c r="H19" t="str">
-        <v>SEVENTEEN</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/seventeen/999644772</v>
+        <v>https://music.apple.com/us/artist/jennifer-lopez/463009</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/tiny-light/1877599751</v>
+        <v>https://music.apple.com/us/album/save-me-tonight/1878974339</v>
       </c>
       <c r="L19" t="str">
-        <v>Tiny Light - SEVENTEEN</v>
+        <v>Save Me Tonight - Jennifer Lopez</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!)</v>
+        <v>Universal Soldier</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/keychain-from-the-film-k-pops/1878278841</v>
+        <v>https://music.apple.com/us/song/universal-soldier/1870313513</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-06</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - Single</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G20" t="str">
-        <v>2:50</v>
+        <v>3:20</v>
       </c>
       <c r="H20" t="str">
-        <v>aespa</v>
+        <v>Depeche Mode</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/aespa/1540251304</v>
+        <v>https://music.apple.com/us/artist/depeche-mode/148377</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/keychain-from-the-film-k-pops/1878278834</v>
+        <v>https://music.apple.com/us/album/universal-soldier/1870313498</v>
       </c>
       <c r="L20" t="str">
-        <v>Keychain (FROM THE FILM K-POPS!) - aespa</v>
+        <v>Universal Soldier - Depeche Mode</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>16 YEAR OLD DRANK</v>
+        <v>Coming Up Roses</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/16-year-old-drank/1878016233</v>
+        <v>https://music.apple.com/us/song/coming-up-roses/1870984045</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-06</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>It's Us Vol. 2</v>
+        <v>Kiss All The Time. Disco, Occasionally.</v>
       </c>
       <c r="G21" t="str">
-        <v>3:23</v>
+        <v>4:08</v>
       </c>
       <c r="H21" t="str">
-        <v>Concrete Boys</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/concrete-boys/1715339951</v>
+        <v>https://music.apple.com/us/artist/harry-styles/471260289</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/16-year-old-drank/1878016122</v>
+        <v>https://music.apple.com/us/album/coming-up-roses/1870984032</v>
       </c>
       <c r="L21" t="str">
-        <v>16 YEAR OLD DRANK - Concrete Boys</v>
+        <v>Coming Up Roses - Harry Styles</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>If I Leave</v>
+        <v>Light Over the Hill (from Reminders of Him)</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/if-i-leave/1860622560</v>
+        <v>https://music.apple.com/us/song/light-over-the-hill-from-reminders-of-him/1876966582</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-06</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Nothing's About to Happen to Me</v>
+        <v>Light Over the Hill (from Reminders of Him) - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>3:00</v>
+        <v>4:43</v>
       </c>
       <c r="H22" t="str">
-        <v>Mitski</v>
+        <v>Noah Cyrus</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/mitski/497546276</v>
+        <v>https://music.apple.com/us/artist/noah-cyrus/333158887</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/if-i-leave/1860622550</v>
+        <v>https://music.apple.com/us/album/light-over-the-hill-from-reminders-of-him/1876966581</v>
       </c>
       <c r="L22" t="str">
-        <v>If I Leave - Mitski</v>
+        <v>Light Over the Hill (from Reminders of Him) - Noah Cyrus</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Time Will Tell</v>
+        <v>Feel Better</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/time-will-tell/1870698022</v>
+        <v>https://music.apple.com/us/song/feel-better/1882859321</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-06</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Time Will Tell - Single</v>
+        <v>"These Are Going Nowhere": A Mixtape by Koe Wetzel - EP</v>
       </c>
       <c r="G23" t="str">
-        <v>3:04</v>
+        <v>3:46</v>
       </c>
       <c r="H23" t="str">
-        <v>Lee Brice</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/lee-brice/216359623</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/time-will-tell/1870698021</v>
+        <v>https://music.apple.com/us/album/feel-better/1882859320</v>
       </c>
       <c r="L23" t="str">
-        <v>Time Will Tell - Lee Brice</v>
+        <v>Feel Better - Koe Wetzel</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>How I Get</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/how-i-get/1873116859</v>
+        <v>https://music.apple.com/us/song/love-love-love/1880198189</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-06</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G24" t="str">
-        <v>3:39</v>
+        <v>4:02</v>
       </c>
       <c r="H24" t="str">
-        <v>Laufey</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/how-i-get/1873116455</v>
+        <v>https://music.apple.com/us/album/love-love-love/1880197844</v>
       </c>
       <c r="L24" t="str">
-        <v>How I Get - Laufey</v>
+        <v>LOVE, LOVE, LOVE - Stephen Sanchez</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7)</v>
+        <v>Pinterest (Portuguese)</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/criminal-from-the-original-motion-picture-scream-7/1876039438</v>
+        <v>https://music.apple.com/us/song/pinterest-portuguese/1880535160</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-06</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Single</v>
+        <v>Pinterest (Portuguese) - Single</v>
       </c>
       <c r="G25" t="str">
-        <v>3:19</v>
+        <v>2:14</v>
       </c>
       <c r="H25" t="str">
-        <v>Jessie Murph</v>
+        <v>Anitta</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/jessie-murph/1548067332</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/criminal-from-the-original-motion-picture-scream-7/1876039437</v>
+        <v>https://music.apple.com/us/album/pinterest-portuguese/1880535159</v>
       </c>
       <c r="L25" t="str">
-        <v>Criminal (From the Original Motion Picture Scream 7) - Jessie Murph</v>
+        <v>Pinterest (Portuguese) - Anitta</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Tonto</v>
+        <v>San Charly</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/tonto/1879859729</v>
+        <v>https://music.apple.com/us/song/san-charly/1880240036</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-06</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Tonto - Single</v>
+        <v>San Charly - Single</v>
       </c>
       <c r="G26" t="str">
-        <v>2:20</v>
+        <v>2:54</v>
       </c>
       <c r="H26" t="str">
-        <v>J Balvin</v>
+        <v>Xavi</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/tonto/1879859725</v>
+        <v>https://music.apple.com/us/album/san-charly/1880239644</v>
       </c>
       <c r="L26" t="str">
-        <v>Tonto - J Balvin</v>
+        <v>San Charly - Xavi</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>nothin lasts 4ever</v>
+        <v>Timelapse de Sol</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/nothin-lasts-4ever/1876578527</v>
+        <v>https://music.apple.com/us/song/timelapse-de-sol/1873150111</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-06</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>nothin lasts 4ever - Single</v>
+        <v>JuanesTeban</v>
       </c>
       <c r="G27" t="str">
-        <v>2:41</v>
+        <v>3:05</v>
       </c>
       <c r="H27" t="str">
-        <v>BLOND:ISH</v>
+        <v>Juanes</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/blond-ish/394776491</v>
+        <v>https://music.apple.com/us/artist/juanes/103856</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/nothin-lasts-4ever/1876578523</v>
+        <v>https://music.apple.com/us/album/timelapse-de-sol/1873149712</v>
       </c>
       <c r="L27" t="str">
-        <v>nothin lasts 4ever - BLOND:ISH</v>
+        <v>Timelapse de Sol - Juanes</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>MUERDO Mi LENGUA</v>
+        <v>solo (KETTAMA remix)</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/muerdo-mi-lengua/1876018479</v>
+        <v>https://music.apple.com/us/song/solo-kettama-remix/1871555343</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-06</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>MUERDO Mi LENGUA - Single</v>
+        <v>USB002 REMIXES</v>
       </c>
       <c r="G28" t="str">
-        <v>2:50</v>
+        <v>4:20</v>
       </c>
       <c r="H28" t="str">
-        <v>Bautiii</v>
+        <v>Fred again..</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/bautiii/1610245142</v>
+        <v>https://music.apple.com/us/artist/fred-again/1455262408</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/muerdo-mi-lengua/1876018475</v>
+        <v>https://music.apple.com/us/album/solo-kettama-remix/1871555339</v>
       </c>
       <c r="L28" t="str">
-        <v>MUERDO Mi LENGUA - Bautiii</v>
+        <v>solo (KETTAMA remix) - Fred again..</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage]</v>
+        <v>It’s Been Too Long</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/asap-remix-feat-21-savage/1875970765</v>
+        <v>https://music.apple.com/us/song/its-been-too-long/1877910661</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-06</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Single</v>
+        <v>Long Long Road</v>
       </c>
       <c r="G29" t="str">
-        <v>3:41</v>
+        <v>2:42</v>
       </c>
       <c r="H29" t="str">
-        <v>Mýa</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/m%C3%BDa/108751</v>
+        <v>https://music.apple.com/us/artist/ringo-starr/52017</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/asap-remix-feat-21-savage/1875970760</v>
+        <v>https://music.apple.com/us/album/its-been-too-long/1877910655</v>
       </c>
       <c r="L29" t="str">
-        <v>ASAP (Remix) [feat. 21 Savage] - Mýa</v>
+        <v>It’s Been Too Long - Ringo Starr</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Smugglers &amp; Scholars</v>
+        <v>Turn Your Heart Back On</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/smugglers-scholars/1862223567</v>
+        <v>https://music.apple.com/us/song/turn-your-heart-back-on/1866732466</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-06</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>FENIAN</v>
+        <v>Atlanta</v>
       </c>
       <c r="G30" t="str">
-        <v>3:11</v>
+        <v>3:07</v>
       </c>
       <c r="H30" t="str">
-        <v>Kneecap</v>
+        <v>Gnarls Barkley</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/kneecap/1330315811</v>
+        <v>https://music.apple.com/us/artist/gnarls-barkley/129039724</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/smugglers-scholars/1862223497</v>
+        <v>https://music.apple.com/us/album/turn-your-heart-back-on/1866732458</v>
       </c>
       <c r="L30" t="str">
-        <v>Smugglers &amp; Scholars - Kneecap</v>
+        <v>Turn Your Heart Back On - Gnarls Barkley</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>What You Want</v>
+        <v>Devil You Know</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/what-you-want/1874973639</v>
+        <v>https://music.apple.com/us/song/devil-you-know/1878649396</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-06</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>What You Want - Single</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G31" t="str">
-        <v>3:08</v>
+        <v>3:10</v>
       </c>
       <c r="H31" t="str">
-        <v>Angèle</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/ang%C3%A8le/1373339414</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/what-you-want/1874973633</v>
+        <v>https://music.apple.com/us/album/devil-you-know/1878649394</v>
       </c>
       <c r="L31" t="str">
-        <v>What You Want - Angèle</v>
+        <v>Devil You Know - Maya Hawke</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>psychokiller</v>
+        <v>Earth, Wind &amp; California</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/psychokiller/1878764654</v>
+        <v>https://music.apple.com/us/song/earth-wind-california/1877157671</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-06</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>getting up to no good</v>
+        <v>Jean</v>
       </c>
       <c r="G32" t="str">
-        <v>1:53</v>
+        <v>3:04</v>
       </c>
       <c r="H32" t="str">
-        <v>Artemas</v>
+        <v>Yebba</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/psychokiller/1878764647</v>
+        <v>https://music.apple.com/us/album/earth-wind-california/1877157664</v>
       </c>
       <c r="L32" t="str">
-        <v>psychokiller - Artemas</v>
+        <v>Earth, Wind &amp; California - Yebba</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>DISNEY PRINCESS</v>
+        <v>400 Cities</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/disney-princess/1874456215</v>
+        <v>https://music.apple.com/us/song/400-cities/1872496994</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-06</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>HADES</v>
+        <v>Miracle Mile</v>
       </c>
       <c r="G33" t="str">
-        <v>4:05</v>
+        <v>2:17</v>
       </c>
       <c r="H33" t="str">
-        <v>Melanie Martinez</v>
+        <v>Paul Russell</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/melanie-martinez/993014053</v>
+        <v>https://music.apple.com/us/artist/paul-russell/1304377463</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/disney-princess/1874455968</v>
+        <v>https://music.apple.com/us/album/400-cities/1872496993</v>
       </c>
       <c r="L33" t="str">
-        <v>DISNEY PRINCESS - Melanie Martinez</v>
+        <v>400 Cities - Paul Russell</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>mariah</v>
+        <v>THE BOXER</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/mariah/1874948938</v>
+        <v>https://music.apple.com/us/song/the-boxer/1877115548</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-06</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>songs i couldn't forget - EP</v>
+        <v>THE BOXER - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>2:48</v>
+        <v>3:19</v>
       </c>
       <c r="H34" t="str">
-        <v>Lauv</v>
+        <v>Kids That Fly</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/kids-that-fly/1458452953</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/mariah/1874948926</v>
+        <v>https://music.apple.com/us/album/the-boxer/1877115547</v>
       </c>
       <c r="L34" t="str">
-        <v>mariah - Lauv</v>
+        <v>THE BOXER - Kids That Fly</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>BLACKHOLE</v>
+        <v>Borrowed Time</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/blackhole/1873882200</v>
+        <v>https://music.apple.com/us/song/borrowed-time/1881773696</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-06</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>REVIVE+</v>
+        <v>Borrowed Time - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>3:14</v>
+        <v>3:49</v>
       </c>
       <c r="H35" t="str">
-        <v>IVE</v>
+        <v>Sam Barber</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/ive/1594159996</v>
+        <v>https://music.apple.com/us/artist/sam-barber/1584802114</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/blackhole/1873882195</v>
+        <v>https://music.apple.com/us/album/borrowed-time/1881773382</v>
       </c>
       <c r="L35" t="str">
-        <v>BLACKHOLE - IVE</v>
+        <v>Borrowed Time - Sam Barber</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Walk</v>
+        <v>BREEZER</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/walk/1875008123</v>
+        <v>https://music.apple.com/us/song/breezer/1858041251</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-06</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Walk - Single</v>
+        <v>Lost on You</v>
       </c>
       <c r="G36" t="str">
-        <v>2:56</v>
+        <v>3:30</v>
       </c>
       <c r="H36" t="str">
-        <v>Skye Newman</v>
+        <v>Tigers Jaw</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/tigers-jaw/266702551</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/walk/1875008118</v>
+        <v>https://music.apple.com/us/album/breezer/1858041075</v>
       </c>
       <c r="L36" t="str">
-        <v>Walk - Skye Newman</v>
+        <v>BREEZER - Tigers Jaw</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>FLAMMABLE</v>
+        <v>War To Love</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/flammable/1879896026</v>
+        <v>https://music.apple.com/us/song/war-to-love/1843558736</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-06</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>FLAMMABLE - Single</v>
+        <v>Tragic Magic</v>
       </c>
       <c r="G37" t="str">
-        <v>3:17</v>
+        <v>3:46</v>
       </c>
       <c r="H37" t="str">
-        <v>Swae Lee</v>
+        <v>Matt Corby</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/matt-corby/268919290</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/flammable/1879896025</v>
+        <v>https://music.apple.com/us/album/war-to-love/1843558452</v>
       </c>
       <c r="L37" t="str">
-        <v>FLAMMABLE - Swae Lee</v>
+        <v>War To Love - Matt Corby</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>3am (Remix)</v>
+        <v>Incompatibles</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/3am-remix/1878278389</v>
+        <v>https://music.apple.com/us/song/incompatibles/1877143121</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-06</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3am (Remix) - Single</v>
+        <v>Incompatibles - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>2:44</v>
+        <v>2:53</v>
       </c>
       <c r="H38" t="str">
-        <v>Łaszewo</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/%C5%82aszewo/1438035296</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/3am-remix/1878278386</v>
+        <v>https://music.apple.com/us/album/incompatibles/1877143118</v>
       </c>
       <c r="L38" t="str">
-        <v>3am (Remix) - Łaszewo</v>
+        <v>Incompatibles - Christian Nodal</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>mutual destruction</v>
+        <v>Oídos Sordos</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/mutual-destruction/1875309103</v>
+        <v>https://music.apple.com/us/song/o%C3%ADdos-sordos/1882108993</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-06</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>mutual destruction - Single</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G39" t="str">
-        <v>2:31</v>
+        <v>3:34</v>
       </c>
       <c r="H39" t="str">
-        <v>kenzie</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/mutual-destruction/1875309102</v>
+        <v>https://music.apple.com/us/album/o%C3%ADdos-sordos/1882108989</v>
       </c>
       <c r="L39" t="str">
-        <v>mutual destruction - kenzie</v>
+        <v>Oídos Sordos - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Dear Worry</v>
+        <v>Angel</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/dear-worry/1875432913</v>
+        <v>https://music.apple.com/us/song/angel/1877142613</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-06</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Dear Worry - Single</v>
+        <v>Angel - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>3:01</v>
+        <v>2:27</v>
       </c>
       <c r="H40" t="str">
-        <v>Common People</v>
+        <v>December 10</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/common-people/1829795802</v>
+        <v>https://music.apple.com/us/artist/december-10/1414032285</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/dear-worry/1875432912</v>
+        <v>https://music.apple.com/us/album/angel/1877142610</v>
       </c>
       <c r="L40" t="str">
-        <v>Dear Worry - Common People</v>
+        <v>Angel - December 10</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Gentleman</v>
+        <v>Trust Myself</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/gentleman/1876982929</v>
+        <v>https://music.apple.com/us/song/trust-myself/1867012216</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-06</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Gentleman - Single</v>
+        <v>Tell Me How You Really Feel</v>
       </c>
       <c r="G41" t="str">
-        <v>2:16</v>
+        <v>3:03</v>
       </c>
       <c r="H41" t="str">
-        <v>Towa Bird</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/towa-bird/1517035946</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/gentleman/1876982922</v>
+        <v>https://music.apple.com/us/album/trust-myself/1867012005</v>
       </c>
       <c r="L41" t="str">
-        <v>Gentleman - Towa Bird</v>
+        <v>Trust Myself - Katelyn Tarver</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>NYX00</v>
+        <v>Tears Ago</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/nyx00/1878551807</v>
+        <v>https://music.apple.com/us/song/tears-ago/1875885122</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-06</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>NYX00 - Single</v>
+        <v>Tears Ago - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>3:00</v>
+        <v>2:35</v>
       </c>
       <c r="H42" t="str">
-        <v>Dei V</v>
+        <v>ili</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/dei-v/1515317241</v>
+        <v>https://music.apple.com/us/artist/ili/1474855634</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/nyx00/1878551803</v>
+        <v>https://music.apple.com/us/album/tears-ago/1875885121</v>
       </c>
       <c r="L42" t="str">
-        <v>NYX00 - Dei V</v>
+        <v>Tears Ago - ili</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Helicopters</v>
+        <v>Bleed</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/helicopters/1870313516</v>
+        <v>https://music.apple.com/us/song/bleed/1871562994</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-06</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>HELP(2)</v>
+        <v>House of Cards</v>
       </c>
       <c r="G43" t="str">
-        <v>3:58</v>
+        <v>3:40</v>
       </c>
       <c r="H43" t="str">
-        <v>Ezra Collective</v>
+        <v>The Amity Affliction</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/ezra-collective/1103640281</v>
+        <v>https://music.apple.com/us/artist/the-amity-affliction/449513466</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/helicopters/1870313498</v>
+        <v>https://music.apple.com/us/album/bleed/1871562765</v>
       </c>
       <c r="L43" t="str">
-        <v>Helicopters - Ezra Collective</v>
+        <v>Bleed - The Amity Affliction</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral)</v>
+        <v>Die for You</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/of-the-sky-from-the-original-motion-picture-hamnet/1878721869</v>
+        <v>https://music.apple.com/us/song/die-for-you/1860126456</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-06</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Max Richter: Hamnet Live</v>
+        <v>Reflections</v>
       </c>
       <c r="G44" t="str">
-        <v>4:58</v>
+        <v>3:27</v>
       </c>
       <c r="H44" t="str">
-        <v>Max Richter</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/max-richter/54782697</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/of-the-sky-from-the-original-motion-picture-hamnet/1878721550</v>
+        <v>https://music.apple.com/us/album/die-for-you/1860126452</v>
       </c>
       <c r="L44" t="str">
-        <v>Of the sky (From The Original Motion Picture "Hamnet" / Live from Southwark Cathedral) - Max Richter</v>
+        <v>Die for You - From Ashes to New</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>It's You I Want</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF)</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/its-you-i-want/1876956937</v>
+        <v>https://music.apple.com/us/song/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892629</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-06</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Bridgerton Season Four (Soundtrack from the Netflix Series)</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>1:39</v>
+        <v>3:35</v>
       </c>
       <c r="H45" t="str">
-        <v>Kris Bowers</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/kris-bowers/396377227</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/its-you-i-want/1876956599</v>
+        <v>https://music.apple.com/us/album/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892504</v>
       </c>
       <c r="L45" t="str">
-        <v>It's You I Want - Kris Bowers</v>
+        <v>Just Friends (feat. Adi Oasis, Danielle Ponder &amp; Suni MF) - Honey Dijon</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>If I Was With You</v>
+        <v>Wish</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/if-i-was-with-you/1877971870</v>
+        <v>https://music.apple.com/us/song/wish/1876893995</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-06</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>If I Was With You - Single</v>
+        <v>Wish - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>3:25</v>
+        <v>2:45</v>
       </c>
       <c r="H46" t="str">
-        <v>Presley Regier</v>
+        <v>Cash Cobain</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/presley-regier/1398568172</v>
+        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/if-i-was-with-you/1877971868</v>
+        <v>https://music.apple.com/us/album/wish/1876893993</v>
       </c>
       <c r="L46" t="str">
-        <v>If I Was With You - Presley Regier</v>
+        <v>Wish - Cash Cobain</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Stay With Me</v>
+        <v>Clean Up Song</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/stay-with-me/1878796038</v>
+        <v>https://music.apple.com/us/song/clean-up-song/1872849995</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-06</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>Clean Up Song - EP</v>
       </c>
       <c r="G47" t="str">
-        <v>3:47</v>
+        <v>2:46</v>
       </c>
       <c r="H47" t="str">
-        <v>Nessa Barrett</v>
+        <v>Tessa Violet</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/tessa-violet/829841579</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/stay-with-me/1878795618</v>
+        <v>https://music.apple.com/us/album/clean-up-song/1872849994</v>
       </c>
       <c r="L47" t="str">
-        <v>Stay With Me - Nessa Barrett</v>
+        <v>Clean Up Song - Tessa Violet</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>My Loving</v>
+        <v>Fantasy</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/my-loving/1875970777</v>
+        <v>https://music.apple.com/us/song/fantasy/1880786931</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-06</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>My Loving - Single</v>
+        <v>Fantasy - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>2:50</v>
+        <v>3:42</v>
       </c>
       <c r="H48" t="str">
-        <v>Sonny Fodera</v>
+        <v>Omarion</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/omarion/15559682</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/my-loving/1875970776</v>
+        <v>https://music.apple.com/us/album/fantasy/1880786930</v>
       </c>
       <c r="L48" t="str">
-        <v>My Loving - Sonny Fodera</v>
+        <v>Fantasy - Omarion</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Easy On The Eyes</v>
+        <v>why am i like this</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/easy-on-the-eyes/1878452263</v>
+        <v>https://music.apple.com/us/song/why-am-i-like-this/1877773990</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-06</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Easy On The Eyes - Single</v>
+        <v>why am i like this - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>3:44</v>
+        <v>2:56</v>
       </c>
       <c r="H49" t="str">
-        <v>Willow Avalon</v>
+        <v>bbno$</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/willow-avalon/1579587659</v>
+        <v>https://music.apple.com/us/artist/bbno%24/1161580951</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/easy-on-the-eyes/1878452252</v>
+        <v>https://music.apple.com/us/album/why-am-i-like-this/1877773989</v>
       </c>
       <c r="L49" t="str">
-        <v>Easy On The Eyes - Willow Avalon</v>
+        <v>why am i like this - bbno$</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Beautiful</v>
+        <v>How the Fire Started</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/beautiful/1864389804</v>
+        <v>https://music.apple.com/us/song/how-the-fire-started/1877981814</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-06</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Let It Die Here</v>
+        <v>How the Fire Started - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>3:47</v>
+        <v>2:55</v>
       </c>
       <c r="H50" t="str">
-        <v>Linda Perry</v>
+        <v>Eric Nam</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/beautiful/1864389779</v>
+        <v>https://music.apple.com/us/album/how-the-fire-started/1877981801</v>
       </c>
       <c r="L50" t="str">
-        <v>Beautiful - Linda Perry</v>
+        <v>How the Fire Started - Eric Nam</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3")</v>
+        <v>Take Off Late</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/nightswimming-from-shrinking-season-3/1872556262</v>
+        <v>https://music.apple.com/us/song/take-off-late/1858554342</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-06</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Single</v>
+        <v>Mārara</v>
       </c>
       <c r="G51" t="str">
-        <v>4:34</v>
+        <v>3:23</v>
       </c>
       <c r="H51" t="str">
-        <v>Jason Segel</v>
+        <v>15 15</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/jason-segel/271908778</v>
+        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/nightswimming-from-shrinking-season-3/1872556255</v>
+        <v>https://music.apple.com/us/album/take-off-late/1858554036</v>
       </c>
       <c r="L51" t="str">
-        <v>Nightswimming (from "Shrinking: Season 3") - Jason Segel</v>
+        <v>Take Off Late - 15 15</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Control Freak</v>
+        <v>Disrespectfully Decline</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/control-freak/1859044257</v>
+        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-06</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Control Freak - Single</v>
+        <v>With No Due Respect</v>
       </c>
       <c r="G52" t="str">
-        <v>2:53</v>
+        <v>3:13</v>
       </c>
       <c r="H52" t="str">
-        <v>Broadside</v>
+        <v>Foggieraw</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/broadside/169939373</v>
+        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/control-freak/1859044256</v>
+        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
       </c>
       <c r="L52" t="str">
-        <v>Control Freak - Broadside</v>
+        <v>Disrespectfully Decline - Foggieraw</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Done For</v>
+        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi)</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/done-for/1873391195</v>
+        <v>https://music.apple.com/us/song/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519644</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-06</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Done For - Single</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G53" t="str">
-        <v>2:33</v>
+        <v>4:06</v>
       </c>
       <c r="H53" t="str">
-        <v>Max McNown</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/done-for/1873391193</v>
+        <v>https://music.apple.com/us/album/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519270</v>
       </c>
       <c r="L53" t="str">
-        <v>Done For - Max McNown</v>
+        <v>UP (feat. Rich The Kid, A$AP Ferg &amp; SadBoi) - Denzel Curry</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Ready for the Ride</v>
+        <v>Wonderful Thing</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/ready-for-the-ride/1874018137</v>
+        <v>https://music.apple.com/us/song/wonderful-thing/1878259633</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-06</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Ready for the Ride - Single</v>
+        <v>Wonderful Thing - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>3:27</v>
+        <v>2:14</v>
       </c>
       <c r="H54" t="str">
-        <v>Sean Paul</v>
+        <v>aron!</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/sean-paul/155138</v>
+        <v>https://music.apple.com/us/artist/aron/1673838787</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/ready-for-the-ride/1874018131</v>
+        <v>https://music.apple.com/us/album/wonderful-thing/1878259631</v>
       </c>
       <c r="L54" t="str">
-        <v>Ready for the Ride - Sean Paul</v>
+        <v>Wonderful Thing - aron!</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>push the pipe</v>
+        <v>leaving is easy</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/push-the-pipe/1874348865</v>
+        <v>https://music.apple.com/us/song/leaving-is-easy/1877935819</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-06</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>HYPERYOUTH (afterparty)</v>
+        <v>leaving is easy - Single</v>
       </c>
       <c r="G55" t="str">
-        <v>3:08</v>
+        <v>3:33</v>
       </c>
       <c r="H55" t="str">
-        <v>Joey Valence &amp; Brae</v>
+        <v>almost monday</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/joey-valence-brae/1643989506</v>
+        <v>https://music.apple.com/us/artist/almost-monday/1300723925</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/push-the-pipe/1874348487</v>
+        <v>https://music.apple.com/us/album/leaving-is-easy/1877935817</v>
       </c>
       <c r="L55" t="str">
-        <v>push the pipe - Joey Valence &amp; Brae</v>
+        <v>leaving is easy - almost monday</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Disrespectfully Decline</v>
+        <v>You and Me</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
+        <v>https://music.apple.com/us/song/you-and-me/1879844183</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-06</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>With No Due Respect</v>
+        <v>You and Me - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>3:13</v>
+        <v>2:46</v>
       </c>
       <c r="H56" t="str">
-        <v>Foggieraw</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/foggieraw/1152021457</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/disrespectfully-decline/1871675010</v>
+        <v>https://music.apple.com/us/album/you-and-me/1879844182</v>
       </c>
       <c r="L56" t="str">
-        <v>Disrespectfully Decline - Foggieraw</v>
+        <v>You and Me - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Moonlight</v>
+        <v>Tumbleweeds and Chewing Gum</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/moonlight/1878731568</v>
+        <v>https://music.apple.com/us/song/tumbleweeds-and-chewing-gum/1875421507</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-06</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>McKenzie 2.0</v>
+        <v>Tumbleweeds and Chewing Gum - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>2:00</v>
+        <v>2:39</v>
       </c>
       <c r="H57" t="str">
-        <v>FattMack</v>
+        <v>Lily Meola</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/lily-meola/678241726</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/moonlight/1878731566</v>
+        <v>https://music.apple.com/us/album/tumbleweeds-and-chewing-gum/1875421236</v>
       </c>
       <c r="L57" t="str">
-        <v>Moonlight - FattMack</v>
+        <v>Tumbleweeds and Chewing Gum - Lily Meola</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Boat Named After You</v>
+        <v>Everything to Nothing</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/boat-named-after-you/1875118975</v>
+        <v>https://music.apple.com/us/song/everything-to-nothing/1877226198</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-06</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Boat Named After You - Single</v>
+        <v>Everything to Nothing - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:56</v>
+        <v>3:31</v>
       </c>
       <c r="H58" t="str">
-        <v>ERNEST</v>
+        <v>Michael Sanzone</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/michael-sanzone/1728761540</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/boat-named-after-you/1875118972</v>
+        <v>https://music.apple.com/us/album/everything-to-nothing/1877226197</v>
       </c>
       <c r="L58" t="str">
-        <v>Boat Named After You - ERNEST</v>
+        <v>Everything to Nothing - Michael Sanzone</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>fall into you</v>
+        <v>DELETED</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/fall-into-you/1877054132</v>
+        <v>https://music.apple.com/us/song/deleted/1880220796</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-06</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>fall into you - Single</v>
+        <v>DELETED - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>3:28</v>
+        <v>3:24</v>
       </c>
       <c r="H59" t="str">
-        <v>Camylio</v>
+        <v>vaultboy</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/vaultboy/1542387120</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/fall-into-you/1877054131</v>
+        <v>https://music.apple.com/us/album/deleted/1880220075</v>
       </c>
       <c r="L59" t="str">
-        <v>fall into you - Camylio</v>
+        <v>DELETED - vaultboy</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Van Gogh</v>
+        <v>A Thousand Years</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/van-gogh/1861005841</v>
+        <v>https://music.apple.com/us/song/a-thousand-years/1877017640</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-06</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Tales of a Failed Shapeshifter</v>
+        <v>A Thousand Years - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>2:25</v>
+        <v>3:00</v>
       </c>
       <c r="H60" t="str">
-        <v>Em Beihold</v>
+        <v>John Michael Howell</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/em-beihold/1505702878</v>
+        <v>https://music.apple.com/us/artist/john-michael-howell/1603499505</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/van-gogh/1861005676</v>
+        <v>https://music.apple.com/us/album/a-thousand-years/1877017638</v>
       </c>
       <c r="L60" t="str">
-        <v>Van Gogh - Em Beihold</v>
+        <v>A Thousand Years - John Michael Howell</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>popstar Nervous</v>
+        <v>Freedom (feat. EZI)</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/popstar-nervous/1878441485</v>
+        <v>https://music.apple.com/us/song/freedom-feat-ezi/1877036442</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-06</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>the rumors are true - EP</v>
+        <v>Freedom (feat. EZI) - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>2:25</v>
+        <v>5:29</v>
       </c>
       <c r="H61" t="str">
-        <v>DC THE DON</v>
+        <v>Kaskade</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/dc-the-don/1293634796</v>
+        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/popstar-nervous/1878441479</v>
+        <v>https://music.apple.com/us/album/freedom-feat-ezi/1877036441</v>
       </c>
       <c r="L61" t="str">
-        <v>popstar Nervous - DC THE DON</v>
+        <v>Freedom (feat. EZI) - Kaskade</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Free</v>
+        <v>HEAVEN KNOWS (feat. Tenille Townes)</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/free/1872250568</v>
+        <v>https://music.apple.com/us/song/heaven-knows-feat-tenille-townes/1869465111</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-06</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Free - Single</v>
+        <v>HEARTLAND (Deluxe Version)</v>
       </c>
       <c r="G62" t="str">
-        <v>3:08</v>
+        <v>3:16</v>
       </c>
       <c r="H62" t="str">
-        <v>Beartooth</v>
+        <v>MORGXN</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/beartooth/590762561</v>
+        <v>https://music.apple.com/us/artist/morgxn/1116360149</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/free/1872250308</v>
+        <v>https://music.apple.com/us/album/heaven-knows-feat-tenille-townes/1869464853</v>
       </c>
       <c r="L62" t="str">
-        <v>Free - Beartooth</v>
+        <v>HEAVEN KNOWS (feat. Tenille Townes) - MORGXN</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>never come never morning</v>
+        <v>To Myself</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/never-come-never-morning/1846939468</v>
+        <v>https://music.apple.com/us/song/to-myself/1880458049</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-06</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>a short history of decay</v>
+        <v>MINDFIELDS</v>
       </c>
       <c r="G63" t="str">
-        <v>3:39</v>
+        <v>3:40</v>
       </c>
       <c r="H63" t="str">
-        <v>Nothing</v>
+        <v>Alicia Creti</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/nothing/593213453</v>
+        <v>https://music.apple.com/us/artist/alicia-creti/1593954404</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/never-come-never-morning/1846939466</v>
+        <v>https://music.apple.com/us/album/to-myself/1880457670</v>
       </c>
       <c r="L63" t="str">
-        <v>never come never morning - Nothing</v>
+        <v>To Myself - Alicia Creti</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Over My Head</v>
+        <v>TABOO</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/over-my-head/1867087281</v>
+        <v>https://music.apple.com/us/song/taboo/1880750236</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-06</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>A Beautiful Lie (20 Year Anniversary)</v>
+        <v>TABOO - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>2:30</v>
+        <v>2:45</v>
       </c>
       <c r="H64" t="str">
-        <v>Thirty Seconds to Mars</v>
+        <v>Isaiah Falls</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/thirty-seconds-to-mars/2307416</v>
+        <v>https://music.apple.com/us/artist/isaiah-falls/1607911349</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/over-my-head/1867086773</v>
+        <v>https://music.apple.com/us/album/taboo/1880750235</v>
       </c>
       <c r="L64" t="str">
-        <v>Over My Head - Thirty Seconds to Mars</v>
+        <v>TABOO - Isaiah Falls</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Mantis</v>
+        <v>Under The Table (feat. Chris Lane)</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/mantis/1868686720</v>
+        <v>https://music.apple.com/us/song/under-the-table-feat-chris-lane/1878134823</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-06</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Creature of Habit</v>
+        <v>Under The Table (feat. Chris Lane) - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>4:40</v>
+        <v>2:52</v>
       </c>
       <c r="H65" t="str">
-        <v>Courtney Barnett</v>
+        <v>Two Friends</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/courtney-barnett/479276137</v>
+        <v>https://music.apple.com/us/artist/two-friends/383451910</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/mantis/1868686713</v>
+        <v>https://music.apple.com/us/album/under-the-table-feat-chris-lane/1878134822</v>
       </c>
       <c r="L65" t="str">
-        <v>Mantis - Courtney Barnett</v>
+        <v>Under The Table (feat. Chris Lane) - Two Friends</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Soft Launch</v>
+        <v>Be Mine</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/soft-launch/1878329767</v>
+        <v>https://music.apple.com/us/song/be-mine/1877013471</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-06</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Soft Launch - Single</v>
+        <v>Be Mine - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>2:25</v>
+        <v>1:53</v>
       </c>
       <c r="H66" t="str">
-        <v>Cely</v>
+        <v>James Hype</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/cely/1259609505</v>
+        <v>https://music.apple.com/us/artist/james-hype/925734064</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/soft-launch/1878329766</v>
+        <v>https://music.apple.com/us/album/be-mine/1877013470</v>
       </c>
       <c r="L66" t="str">
-        <v>Soft Launch - Cely</v>
+        <v>Be Mine - James Hype</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>picky choosy</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra]</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/picky-choosy/1878512868</v>
+        <v>https://music.apple.com/us/song/talk-to-you-ft-54-ultra-feat-54-ultra/1870514330</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-06</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>2:53</v>
+        <v>3:11</v>
       </c>
       <c r="H67" t="str">
-        <v>Chelsea Jordan</v>
+        <v>ANOTR</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/anotr/1037517622</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/picky-choosy/1878512860</v>
+        <v>https://music.apple.com/us/album/talk-to-you-ft-54-ultra-feat-54-ultra/1870514329</v>
       </c>
       <c r="L67" t="str">
-        <v>picky choosy - Chelsea Jordan</v>
+        <v>Talk To You (ft 54 Ultra) [feat. 54 Ultra] - ANOTR</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>La Mala Era Yo</v>
+        <v>Evil Against Me</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/la-mala-era-yo/1877196514</v>
+        <v>https://music.apple.com/us/song/evil-against-me/1880764671</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-06</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>La Mala Era Yo - Single</v>
+        <v>Evil Against Me - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>2:30</v>
+        <v>3:24</v>
       </c>
       <c r="H68" t="str">
-        <v>Kany García</v>
+        <v>Shaya Zamora</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/shaya-zamora/1697577211</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/la-mala-era-yo/1877196503</v>
+        <v>https://music.apple.com/us/album/evil-against-me/1880764670</v>
       </c>
       <c r="L68" t="str">
-        <v>La Mala Era Yo - Kany García</v>
+        <v>Evil Against Me - Shaya Zamora</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Quiet Part Loud</v>
+        <v>Still Do</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/quiet-part-loud/1874354313</v>
+        <v>https://music.apple.com/us/song/still-do/1877250216</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-06</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Joy Next Door</v>
+        <v>Still Do - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>3:08</v>
+        <v>3:03</v>
       </c>
       <c r="H69" t="str">
-        <v>The Maine</v>
+        <v>Anne Wilson</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/anne-wilson/1561871798</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/quiet-part-loud/1874354034</v>
+        <v>https://music.apple.com/us/album/still-do/1877250210</v>
       </c>
       <c r="L69" t="str">
-        <v>Quiet Part Loud - The Maine</v>
+        <v>Still Do - Anne Wilson</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>favorite girl</v>
+        <v>DIE 4 ME</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/favorite-girl/1875976857</v>
+        <v>https://music.apple.com/us/song/die-4-me/1874690944</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-06</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>favorite girl - Single</v>
+        <v>DIE 4 ME - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>3:24</v>
+        <v>2:37</v>
       </c>
       <c r="H70" t="str">
-        <v>Alaina Castillo</v>
+        <v>Taylor Hill</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/alaina-castillo/1481640775</v>
+        <v>https://music.apple.com/us/artist/taylor-hill/588153976</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/favorite-girl/1875976855</v>
+        <v>https://music.apple.com/us/album/die-4-me/1874690942</v>
       </c>
       <c r="L70" t="str">
-        <v>favorite girl - Alaina Castillo</v>
+        <v>DIE 4 ME - Taylor Hill</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>The Blade</v>
+        <v>Havin'</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1876388273</v>
+        <v>https://music.apple.com/us/song/havin/1878165152</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-06</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>The Blade - Single</v>
+        <v>Havin' - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>3:15</v>
+        <v>2:49</v>
       </c>
       <c r="H71" t="str">
-        <v>Kingfishr</v>
+        <v>1K Phew</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/1k-phew/1168127389</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1876388272</v>
+        <v>https://music.apple.com/us/album/havin/1878165149</v>
       </c>
       <c r="L71" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>Havin' - 1K Phew</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Blunt Force Blues</v>
+        <v>Se Me Va A Pasar</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/blunt-force-blues/1868804171</v>
+        <v>https://music.apple.com/us/song/se-me-va-a-pasar/1877981780</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-06</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Into Oblivion</v>
+        <v>Coleccionando Corazones</v>
       </c>
       <c r="G72" t="str">
-        <v>4:11</v>
+        <v>3:16</v>
       </c>
       <c r="H72" t="str">
-        <v>Lamb of God</v>
+        <v>Carolina Ross</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/carolina-ross/731144150</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/blunt-force-blues/1868804163</v>
+        <v>https://music.apple.com/us/album/se-me-va-a-pasar/1877981770</v>
       </c>
       <c r="L72" t="str">
-        <v>Blunt Force Blues - Lamb of God</v>
+        <v>Se Me Va A Pasar - Carolina Ross</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>The Black Scorpion</v>
+        <v>Mi Amante</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/the-black-scorpion/1839888306</v>
+        <v>https://music.apple.com/us/song/mi-amante/1867549554</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-06</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>The Great Satan</v>
+        <v>Mi Amante - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>1:33</v>
+        <v>3:16</v>
       </c>
       <c r="H73" t="str">
-        <v>Rob Zombie</v>
+        <v>Juanchito</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/rob-zombie/110374</v>
+        <v>https://music.apple.com/us/artist/juanchito/411411086</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/the-black-scorpion/1839887790</v>
+        <v>https://music.apple.com/us/album/mi-amante/1867549551</v>
       </c>
       <c r="L73" t="str">
-        <v>The Black Scorpion - Rob Zombie</v>
+        <v>Mi Amante - Juanchito</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>The Place</v>
+        <v>Ay Pequeña</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/the-place/1869119815</v>
+        <v>https://music.apple.com/us/song/ay-peque%C3%B1a/1876456533</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-06</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>The Cloud Of Unknowing - EP</v>
+        <v>La Rubia Enamorada - EP</v>
       </c>
       <c r="G74" t="str">
-        <v>5:58</v>
+        <v>2:00</v>
       </c>
       <c r="H74" t="str">
-        <v>Sepultura</v>
+        <v>Flavia Laos</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/sepultura/918092</v>
+        <v>https://music.apple.com/us/artist/flavia-laos/1292143540</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/the-place/1869119453</v>
+        <v>https://music.apple.com/us/album/ay-peque%C3%B1a/1876456334</v>
       </c>
       <c r="L74" t="str">
-        <v>The Place - Sepultura</v>
+        <v>Ay Pequeña - Flavia Laos</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>SONG OF THE SWAMP</v>
+        <v>Need it Bad</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-swamp/1876593204</v>
+        <v>https://music.apple.com/us/song/need-it-bad/1879918897</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-06</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>Need it Bad - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>3:18</v>
+        <v>3:07</v>
       </c>
       <c r="H75" t="str">
-        <v>Wage War</v>
+        <v>Ama</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-swamp/1876593203</v>
+        <v>https://music.apple.com/us/album/need-it-bad/1879918896</v>
       </c>
       <c r="L75" t="str">
-        <v>SONG OF THE SWAMP - Wage War</v>
+        <v>Need it Bad - Ama</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez)</v>
+        <v>Time Is A Bomb</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/s%C3%BAper-snake-feat-luis-r-conriquez/1878695141</v>
+        <v>https://music.apple.com/us/song/time-is-a-bomb/1861918608</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-06</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - Single</v>
+        <v>Romanticize The Dive</v>
       </c>
       <c r="G76" t="str">
-        <v>2:26</v>
+        <v>4:24</v>
       </c>
       <c r="H76" t="str">
-        <v>LOS DOS DE TAMAULIPAS</v>
+        <v>Metric</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/los-dos-de-tamaulipas/1459678954</v>
+        <v>https://music.apple.com/us/artist/metric/4125821</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/s%C3%BAper-snake-feat-luis-r-conriquez/1878695106</v>
+        <v>https://music.apple.com/us/album/time-is-a-bomb/1861918507</v>
       </c>
       <c r="L76" t="str">
-        <v>Súper Snake (feat. Luis R Conriquez) - LOS DOS DE TAMAULIPAS</v>
+        <v>Time Is A Bomb - Metric</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Tu Cárcel</v>
+        <v>NOISE</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/tu-c%C3%A1rcel/1878500776</v>
+        <v>https://music.apple.com/us/song/noise/1878401282</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-06</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Tu Cárcel - Single</v>
+        <v>NOISE - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>3:36</v>
+        <v>2:42</v>
       </c>
       <c r="H77" t="str">
-        <v>Morat</v>
+        <v>ivri</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/morat/955657302</v>
+        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/tu-c%C3%A1rcel/1878500589</v>
+        <v>https://music.apple.com/us/album/noise/1878401279</v>
       </c>
       <c r="L77" t="str">
-        <v>Tu Cárcel - Morat</v>
+        <v>NOISE - ivri</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Facts</v>
+        <v>Delicate (feat. Jake Clemons)</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/facts/1878765800</v>
+        <v>https://music.apple.com/us/song/delicate-feat-jake-clemons/1875071828</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-06</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Be Very Afraid (Vol. 1)</v>
+        <v>Prairie</v>
       </c>
       <c r="G78" t="str">
-        <v>3:29</v>
+        <v>4:46</v>
       </c>
       <c r="H78" t="str">
-        <v>CHASE B</v>
+        <v>Bike Routes</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/chase-b/1473980539</v>
+        <v>https://music.apple.com/us/artist/bike-routes/1507733686</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/facts/1878765796</v>
+        <v>https://music.apple.com/us/album/delicate-feat-jake-clemons/1875071512</v>
       </c>
       <c r="L78" t="str">
-        <v>Facts - CHASE B</v>
+        <v>Delicate (feat. Jake Clemons) - Bike Routes</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>me &amp; you</v>
+        <v>Bird Eye View</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/me-you/1878168773</v>
+        <v>https://music.apple.com/us/song/bird-eye-view/1872125049</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-06</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>big country</v>
+        <v>Bird Eye View - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>2:29</v>
+        <v>4:24</v>
       </c>
       <c r="H79" t="str">
-        <v>sosocamo</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/sosocamo/1615285313</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/me-you/1878168770</v>
+        <v>https://music.apple.com/us/album/bird-eye-view/1872125042</v>
       </c>
       <c r="L79" t="str">
-        <v>me &amp; you - sosocamo</v>
+        <v>Bird Eye View - Hayden Everett</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>badman</v>
+        <v>Whip-Poor-Will</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/badman/1877577830</v>
+        <v>https://music.apple.com/us/song/whip-poor-will/1875093565</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-06</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>badman - Single</v>
+        <v>Whip-Poor-Will - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>2:54</v>
+        <v>3:46</v>
       </c>
       <c r="H80" t="str">
-        <v>nomi.</v>
+        <v>Erin Rae</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/nomi/1843014984</v>
+        <v>https://music.apple.com/us/artist/erin-rae/589208872</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/badman/1877577829</v>
+        <v>https://music.apple.com/us/album/whip-poor-will/1875093563</v>
       </c>
       <c r="L80" t="str">
-        <v>badman - nomi.</v>
+        <v>Whip-Poor-Will - Erin Rae</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Shut It Down</v>
+        <v>Good Friend</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/shut-it-down/1875975503</v>
+        <v>https://music.apple.com/us/song/good-friend/1869047706</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-06</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Shut It Down - Single</v>
+        <v>Singing</v>
       </c>
       <c r="G81" t="str">
-        <v>2:26</v>
+        <v>3:39</v>
       </c>
       <c r="H81" t="str">
-        <v>TheARTI$t</v>
+        <v>Gia Margaret</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/thearti%24t/1504775415</v>
+        <v>https://music.apple.com/us/artist/gia-margaret/1460162196</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/shut-it-down/1875975502</v>
+        <v>https://music.apple.com/us/album/good-friend/1869047383</v>
       </c>
       <c r="L81" t="str">
-        <v>Shut It Down - TheARTI$t</v>
+        <v>Good Friend - Gia Margaret</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>AUTOMATIC</v>
+        <v>NEVER BE THE SAME</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/automatic/1875133428</v>
+        <v>https://music.apple.com/us/song/never-be-the-same/1876492032</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-06</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>AUTOMATIC - Single</v>
+        <v>NEVER BE THE SAME - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>2:08</v>
+        <v>2:52</v>
       </c>
       <c r="H82" t="str">
-        <v>Hulvey</v>
+        <v>THEHONESTGUY</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/automatic/1875133426</v>
+        <v>https://music.apple.com/us/album/never-be-the-same/1876492031</v>
       </c>
       <c r="L82" t="str">
-        <v>AUTOMATIC - Hulvey</v>
+        <v>NEVER BE THE SAME - THEHONESTGUY</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Leaving Egypt</v>
+        <v>Tellme</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/leaving-egypt/1876009616</v>
+        <v>https://music.apple.com/us/song/tellme/1880089949</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-06</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Leaving Egypt - Single</v>
+        <v>Tellme - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>3:17</v>
+        <v>3:04</v>
       </c>
       <c r="H83" t="str">
-        <v>Alex Jude</v>
+        <v>Joon</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/alex-jude/1662264049</v>
+        <v>https://music.apple.com/us/artist/joon/1515228137</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/leaving-egypt/1876009615</v>
+        <v>https://music.apple.com/us/album/tellme/1880089948</v>
       </c>
       <c r="L83" t="str">
-        <v>Leaving Egypt - Alex Jude</v>
+        <v>Tellme - Joon</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Not Your Mother</v>
+        <v>I Can Be Yours</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/not-your-mother/1873456213</v>
+        <v>https://music.apple.com/us/song/i-can-be-yours/1878355948</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-06</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Not Your Mother - Single</v>
+        <v>I Can Be Yours - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>3:03</v>
+        <v>4:07</v>
       </c>
       <c r="H84" t="str">
-        <v>gracie</v>
+        <v>zzzahara</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/gracie/1873447528</v>
+        <v>https://music.apple.com/us/artist/zzzahara/1459215872</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/not-your-mother/1873456212</v>
+        <v>https://music.apple.com/us/album/i-can-be-yours/1878355945</v>
       </c>
       <c r="L84" t="str">
-        <v>Not Your Mother - gracie</v>
+        <v>I Can Be Yours - zzzahara</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Born to Kill</v>
+        <v>Soren</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/born-to-kill/1873280357</v>
+        <v>https://music.apple.com/us/song/soren/1876596568</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-06</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Born to Kill</v>
+        <v>Soren - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:50</v>
+        <v>3:41</v>
       </c>
       <c r="H85" t="str">
-        <v>Social Distortion</v>
+        <v>Orca</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/orca/1741045781</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/born-to-kill/1873280355</v>
+        <v>https://music.apple.com/us/album/soren/1876596567</v>
       </c>
       <c r="L85" t="str">
-        <v>Born to Kill - Social Distortion</v>
+        <v>Soren - Orca</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>When the Love is Gone</v>
+        <v>Gloria</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/when-the-love-is-gone/1877592567</v>
+        <v>https://music.apple.com/us/song/gloria/1842363092</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-06</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>When the Love is Gone - Single</v>
+        <v>The Guesthouse</v>
       </c>
       <c r="G86" t="str">
-        <v>3:20</v>
+        <v>3:24</v>
       </c>
       <c r="H86" t="str">
-        <v>Des Rocs</v>
+        <v>Shai Maestro</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/des-rocs/1344839704</v>
+        <v>https://music.apple.com/us/artist/shai-maestro/397591781</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/when-the-love-is-gone/1877592566</v>
+        <v>https://music.apple.com/us/album/gloria/1842362686</v>
       </c>
       <c r="L86" t="str">
-        <v>When the Love is Gone - Des Rocs</v>
+        <v>Gloria - Shai Maestro</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Miami Crest</v>
+        <v>Gemini Eyes</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/miami-crest/1874845104</v>
+        <v>https://music.apple.com/us/song/gemini-eyes/1869127743</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-06</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Miami Crest - Single</v>
+        <v>A Rush To Nowhere</v>
       </c>
       <c r="G87" t="str">
-        <v>2:39</v>
+        <v>4:59</v>
       </c>
       <c r="H87" t="str">
-        <v>Namasenda</v>
+        <v>Arima Ederra</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/namasenda/1147832293</v>
+        <v>https://music.apple.com/us/artist/arima-ederra/689907169</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/miami-crest/1874845103</v>
+        <v>https://music.apple.com/us/album/gemini-eyes/1869127443</v>
       </c>
       <c r="L87" t="str">
-        <v>Miami Crest - Namasenda</v>
+        <v>Gemini Eyes - Arima Ederra</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Say No Prayer</v>
+        <v>Tough</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/say-no-prayer/1878210721</v>
+        <v>https://music.apple.com/us/song/tough/1878716666</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-06</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Say No Prayer - Single</v>
+        <v>Tough - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>2:29</v>
+        <v>3:15</v>
       </c>
       <c r="H88" t="str">
-        <v>oskar med k</v>
+        <v>Nia Smith</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/oskar-med-k/1671429234</v>
+        <v>https://music.apple.com/us/artist/nia-smith/1755576018</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/say-no-prayer/1878210720</v>
+        <v>https://music.apple.com/us/album/tough/1878716664</v>
       </c>
       <c r="L88" t="str">
-        <v>Say No Prayer - oskar med k</v>
+        <v>Tough - Nia Smith</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>You Always Liked Me Better When I Was Stoned</v>
+        <v>NO HOOK</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/you-always-liked-me-better-when-i-was-stoned/1871925769</v>
+        <v>https://music.apple.com/us/song/no-hook/1880501939</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-06</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - Single</v>
+        <v>NO HOOK - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>3:09</v>
+        <v>1:08</v>
       </c>
       <c r="H89" t="str">
-        <v>eee gee</v>
+        <v>KARRAHBOOO</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/eee-gee/1564347407</v>
+        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/you-always-liked-me-better-when-i-was-stoned/1871925762</v>
+        <v>https://music.apple.com/us/album/no-hook/1880501938</v>
       </c>
       <c r="L89" t="str">
-        <v>You Always Liked Me Better When I Was Stoned - eee gee</v>
+        <v>NO HOOK - KARRAHBOOO</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Pink Tongue</v>
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet)</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/pink-tongue/1878101990</v>
+        <v>https://music.apple.com/us/song/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980382</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-06</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Porcelain Heart</v>
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>3:43</v>
+        <v>4:08</v>
       </c>
       <c r="H90" t="str">
-        <v>Diane Emerita</v>
+        <v>Rosie Bennet</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/diane-emerita/1645834838</v>
+        <v>https://music.apple.com/us/artist/rosie-bennet/1843608457</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/pink-tongue/1878101985</v>
+        <v>https://music.apple.com/us/album/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980379</v>
       </c>
       <c r="L90" t="str">
-        <v>Pink Tongue - Diane Emerita</v>
+        <v>What He Wrote (Transcr. for Guitar by Rosie Bennet) - Rosie Bennet</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Hey, Bluebird</v>
+        <v>Mean 2 Me</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/hey-bluebird/1860985999</v>
+        <v>https://music.apple.com/us/song/mean-2-me/1861088760</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-06</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Hey, Bluebird - Single</v>
+        <v>Mean 2 Me - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>3:23</v>
+        <v>4:27</v>
       </c>
       <c r="H91" t="str">
-        <v>Ber</v>
+        <v>Skyla Tylaa</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/ber/1020679397</v>
+        <v>https://music.apple.com/us/artist/skyla-tylaa/1732572444</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/hey-bluebird/1860985998</v>
+        <v>https://music.apple.com/us/album/mean-2-me/1861088756</v>
       </c>
       <c r="L91" t="str">
-        <v>Hey, Bluebird - Ber</v>
+        <v>Mean 2 Me - Skyla Tylaa</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>You’ll Be The Proof</v>
+        <v>CAPTAIN KERNEL</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/youll-be-the-proof/1879618816</v>
+        <v>https://music.apple.com/us/song/captain-kernel/1868763228</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-06</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>You’ll Be The Proof - Single</v>
+        <v>BIG MAMA</v>
       </c>
       <c r="G92" t="str">
-        <v>3:26</v>
+        <v>3:04</v>
       </c>
       <c r="H92" t="str">
-        <v>Forest Blakk</v>
+        <v>Flying Lotus</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/forest-blakk/962489105</v>
+        <v>https://music.apple.com/us/artist/flying-lotus/120737020</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/youll-be-the-proof/1879618565</v>
+        <v>https://music.apple.com/us/album/captain-kernel/1868763221</v>
       </c>
       <c r="L92" t="str">
-        <v>You’ll Be The Proof - Forest Blakk</v>
+        <v>CAPTAIN KERNEL - Flying Lotus</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Heartbeat</v>
+        <v>Nothings What It Seems</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/heartbeat/1872049965</v>
+        <v>https://music.apple.com/us/song/nothings-what-it-seems/1872820240</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-06</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Heartbeat - Single</v>
+        <v>Midwest Memoir</v>
       </c>
       <c r="G93" t="str">
-        <v>2:52</v>
+        <v>3:12</v>
       </c>
       <c r="H93" t="str">
-        <v>Lola Blue</v>
+        <v>Tyler Nance</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/lola-blue/1874555980</v>
+        <v>https://music.apple.com/us/artist/tyler-nance/1484602101</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/heartbeat/1872049962</v>
+        <v>https://music.apple.com/us/album/nothings-what-it-seems/1872819971</v>
       </c>
       <c r="L93" t="str">
-        <v>Heartbeat - Lola Blue</v>
+        <v>Nothings What It Seems - Tyler Nance</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Imitation (how to become you)</v>
+        <v>No Need For Leavin'</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/imitation-how-to-become-you/1878754246</v>
+        <v>https://music.apple.com/us/song/no-need-for-leavin/1878743975</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-06</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Imitation (how to become you) - Single</v>
+        <v>No Need For Leavin' - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>4:16</v>
+        <v>3:35</v>
       </c>
       <c r="H94" t="str">
-        <v>doggone</v>
+        <v>Kameron Marlowe</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/doggone/1776167584</v>
+        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/imitation-how-to-become-you/1878754245</v>
+        <v>https://music.apple.com/us/album/no-need-for-leavin/1878743974</v>
       </c>
       <c r="L94" t="str">
-        <v>Imitation (how to become you) - doggone</v>
+        <v>No Need For Leavin' - Kameron Marlowe</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>I’m Every Woman</v>
+        <v>ii. in the gut of the wolf</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/im-every-woman/1870996227</v>
+        <v>https://music.apple.com/us/song/ii-in-the-gut-of-the-wolf/1867614406</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-06</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Cover Girl - EP</v>
+        <v>silence outlives the earth</v>
       </c>
       <c r="G95" t="str">
-        <v>4:35</v>
+        <v>3:30</v>
       </c>
       <c r="H95" t="str">
-        <v>Ashley Jackson</v>
+        <v>ERRA</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/ashley-jackson/1686974281</v>
+        <v>https://music.apple.com/us/artist/erra/408917738</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/im-every-woman/1870996225</v>
+        <v>https://music.apple.com/us/album/ii-in-the-gut-of-the-wolf/1867613901</v>
       </c>
       <c r="L95" t="str">
-        <v>I’m Every Woman - Ashley Jackson</v>
+        <v>ii. in the gut of the wolf - ERRA</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Hard To See (feat. Norah Jones)</v>
+        <v>Poison Icon</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/hard-to-see-feat-norah-jones/1860689593</v>
+        <v>https://music.apple.com/us/song/poison-icon/1847941146</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-06</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Infinite Source Of Heat</v>
+        <v>The Crawl</v>
       </c>
       <c r="G96" t="str">
-        <v>2:46</v>
+        <v>5:12</v>
       </c>
       <c r="H96" t="str">
-        <v>Chris Morrissey</v>
+        <v>Temple of Void</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/chris-morrissey/152809698</v>
+        <v>https://music.apple.com/us/artist/temple-of-void/882930593</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/hard-to-see-feat-norah-jones/1860689131</v>
+        <v>https://music.apple.com/us/album/poison-icon/1847941140</v>
       </c>
       <c r="L96" t="str">
-        <v>Hard To See (feat. Norah Jones) - Chris Morrissey</v>
+        <v>Poison Icon - Temple of Void</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Slow Tonight</v>
+        <v>Lay Down Your Soul</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/slow-tonight/1868437910</v>
+        <v>https://music.apple.com/us/song/lay-down-your-soul/1872651251</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-06</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Full Circle</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G97" t="str">
-        <v>3:12</v>
+        <v>3:13</v>
       </c>
       <c r="H97" t="str">
-        <v>Tom Misch</v>
+        <v>Venom</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/slow-tonight/1868437787</v>
+        <v>https://music.apple.com/us/album/lay-down-your-soul/1872651243</v>
       </c>
       <c r="L97" t="str">
-        <v>Slow Tonight - Tom Misch</v>
+        <v>Lay Down Your Soul - Venom</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Freak No More</v>
+        <v>Ghost Notes</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/freak-no-more/1873443577</v>
+        <v>https://music.apple.com/us/song/ghost-notes/1862229148</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-06</v>
@@ -4099,258 +4099,30 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>Freak No More - Single</v>
+        <v>Slave Machine</v>
       </c>
       <c r="G98" t="str">
-        <v>3:57</v>
+        <v>4:27</v>
       </c>
       <c r="H98" t="str">
-        <v>AC Slater</v>
+        <v>Nervosa</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/ac-slater/253002292</v>
+        <v>https://music.apple.com/us/artist/nervosa/511556134</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/freak-no-more/1873443576</v>
+        <v>https://music.apple.com/us/album/ghost-notes/1862228924</v>
       </c>
       <c r="L98" t="str">
-        <v>Freak No More - AC Slater</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v>Don't Stop</v>
-      </c>
-      <c r="B99" t="str">
-        <v/>
-      </c>
-      <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/dont-stop/1877058099</v>
-      </c>
-      <c r="D99" t="str">
-        <v>2026-03-06</v>
-      </c>
-      <c r="E99" t="str">
-        <v/>
-      </c>
-      <c r="F99" t="str">
-        <v>Don't Stop - Single</v>
-      </c>
-      <c r="G99" t="str">
-        <v>2:55</v>
-      </c>
-      <c r="H99" t="str">
-        <v>HoneyLuv</v>
-      </c>
-      <c r="I99" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/honeyluv/1564761965</v>
-      </c>
-      <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/dont-stop/1877057795</v>
-      </c>
-      <c r="L99" t="str">
-        <v>Don't Stop - HoneyLuv</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
-        <v>Cause I Do</v>
-      </c>
-      <c r="B100" t="str">
-        <v/>
-      </c>
-      <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/cause-i-do/1875114037</v>
-      </c>
-      <c r="D100" t="str">
-        <v>2026-03-06</v>
-      </c>
-      <c r="E100" t="str">
-        <v/>
-      </c>
-      <c r="F100" t="str">
-        <v>Cause I Do - Single</v>
-      </c>
-      <c r="G100" t="str">
-        <v>2:39</v>
-      </c>
-      <c r="H100" t="str">
-        <v>Preston Pablo</v>
-      </c>
-      <c r="I100" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/preston-pablo/1449906625</v>
-      </c>
-      <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/cause-i-do/1875114028</v>
-      </c>
-      <c r="L100" t="str">
-        <v>Cause I Do - Preston Pablo</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>Morning Comes</v>
-      </c>
-      <c r="B101" t="str">
-        <v/>
-      </c>
-      <c r="C101" t="str">
-        <v>https://music.apple.com/us/song/morning-comes/1867275345</v>
-      </c>
-      <c r="D101" t="str">
-        <v>2026-03-06</v>
-      </c>
-      <c r="E101" t="str">
-        <v/>
-      </c>
-      <c r="F101" t="str">
-        <v>Heavy On The Soul</v>
-      </c>
-      <c r="G101" t="str">
-        <v>4:11</v>
-      </c>
-      <c r="H101" t="str">
-        <v>Ty Myers</v>
-      </c>
-      <c r="I101" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J101" t="str">
-        <v>https://music.apple.com/us/artist/ty-myers/1674345303</v>
-      </c>
-      <c r="K101" t="str">
-        <v>https://music.apple.com/us/album/morning-comes/1867275110</v>
-      </c>
-      <c r="L101" t="str">
-        <v>Morning Comes - Ty Myers</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>BETTER ON ME</v>
-      </c>
-      <c r="B102" t="str">
-        <v/>
-      </c>
-      <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/better-on-me/1876348243</v>
-      </c>
-      <c r="D102" t="str">
-        <v>2026-03-06</v>
-      </c>
-      <c r="E102" t="str">
-        <v/>
-      </c>
-      <c r="F102" t="str">
-        <v>BETTER ON ME - Single</v>
-      </c>
-      <c r="G102" t="str">
-        <v>3:24</v>
-      </c>
-      <c r="H102" t="str">
-        <v>Johnny Huynh</v>
-      </c>
-      <c r="I102" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/johnny-huynh/1708540956</v>
-      </c>
-      <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/better-on-me/1876348241</v>
-      </c>
-      <c r="L102" t="str">
-        <v>BETTER ON ME - Johnny Huynh</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>Speed or Perish</v>
-      </c>
-      <c r="B103" t="str">
-        <v/>
-      </c>
-      <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/speed-or-perish/1857651795</v>
-      </c>
-      <c r="D103" t="str">
-        <v>2026-03-06</v>
-      </c>
-      <c r="E103" t="str">
-        <v/>
-      </c>
-      <c r="F103" t="str">
-        <v>Leather Temple</v>
-      </c>
-      <c r="G103" t="str">
-        <v>4:30</v>
-      </c>
-      <c r="H103" t="str">
-        <v>Carpenter Brut</v>
-      </c>
-      <c r="I103" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/carpenter-brut/593656958</v>
-      </c>
-      <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/speed-or-perish/1857651780</v>
-      </c>
-      <c r="L103" t="str">
-        <v>Speed or Perish - Carpenter Brut</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>The Scumbag Grift</v>
-      </c>
-      <c r="B104" t="str">
-        <v/>
-      </c>
-      <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/the-scumbag-grift/1870589284</v>
-      </c>
-      <c r="D104" t="str">
-        <v>2026-03-06</v>
-      </c>
-      <c r="E104" t="str">
-        <v/>
-      </c>
-      <c r="F104" t="str">
-        <v>Cheap Heat</v>
-      </c>
-      <c r="G104" t="str">
-        <v>2:27</v>
-      </c>
-      <c r="H104" t="str">
-        <v>A Wilhelm Scream</v>
-      </c>
-      <c r="I104" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/a-wilhelm-scream/7375447</v>
-      </c>
-      <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/the-scumbag-grift/1870588948</v>
-      </c>
-      <c r="L104" t="str">
-        <v>The Scumbag Grift - A Wilhelm Scream</v>
+        <v>Ghost Notes - Nervosa</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L104"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L98"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week01/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week01/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/american-girls/1870984036</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/algo-t%C3%BA/1880768673</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/new-religion/1878015314</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/where-do-we-go/1880521218</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/if-you-wanna-party-come-over-to-my-house/1861895281</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/we-dont-get-along/1880045873</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/bad-bitch-alert/1878417350</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/medicine/1874168009</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/somewhere-else/1871185070</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/dog/1871594836</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/dance-no-more/1870984050</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/burial-from-mother-mary/1879807598</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/tweak/1875414202</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/attitude/1879665813</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/blame-texas/1879648698</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/kerosene/1878542369</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/jump-feat-steve-vai-travis-barker-coca-cola-anthem/1881499140</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/save-me-tonight/1878974345</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/universal-soldier/1870313513</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/coming-up-roses/1870984045</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/light-over-the-hill-from-reminders-of-him/1876966582</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/feel-better/1882859321</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/love-love-love/1880198189</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/pinterest-portuguese/1880535160</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/san-charly/1880240036</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/timelapse-de-sol/1873150111</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/solo-kettama-remix/1871555343</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/its-been-too-long/1877910661</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/turn-your-heart-back-on/1866732466</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/devil-you-know/1878649396</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/earth-wind-california/1877157671</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/400-cities/1872496994</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/the-boxer/1877115548</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/borrowed-time/1881773696</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/breezer/1858041251</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/war-to-love/1843558736</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/incompatibles/1877143121</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/o%C3%ADdos-sordos/1882108993</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/angel/1877142613</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/trust-myself/1867012216</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/tears-ago/1875885122</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/bleed/1871562994</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/die-for-you/1860126456</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/just-friends-feat-adi-oasis-danielle-ponder-suni-mf/1874892629</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/wish/1876893995</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/clean-up-song/1872849995</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/fantasy/1880786931</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/why-am-i-like-this/1877773990</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/how-the-fire-started/1877981814</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/take-off-late/1858554342</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/disrespectfully-decline/1871675017</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/up-feat-rich-the-kid-a%24ap-ferg-sadboi/1868519644</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/wonderful-thing/1878259633</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/leaving-is-easy/1877935819</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/you-and-me/1879844183</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/tumbleweeds-and-chewing-gum/1875421507</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/everything-to-nothing/1877226198</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/deleted/1880220796</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/a-thousand-years/1877017640</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/freedom-feat-ezi/1877036442</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/heaven-knows-feat-tenille-townes/1869465111</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/to-myself/1880458049</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/taboo/1880750236</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/under-the-table-feat-chris-lane/1878134823</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/be-mine/1877013471</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/talk-to-you-ft-54-ultra-feat-54-ultra/1870514330</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/evil-against-me/1880764671</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/still-do/1877250216</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/die-4-me/1874690944</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/havin/1878165152</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/se-me-va-a-pasar/1877981780</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/mi-amante/1867549554</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/ay-peque%C3%B1a/1876456533</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/need-it-bad/1879918897</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/time-is-a-bomb/1861918608</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/noise/1878401282</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/delicate-feat-jake-clemons/1875071828</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/bird-eye-view/1872125049</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/whip-poor-will/1875093565</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/good-friend/1869047706</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/never-be-the-same/1876492032</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/tellme/1880089949</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/i-can-be-yours/1878355948</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/soren/1876596568</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/gloria/1842363092</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/gemini-eyes/1869127743</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/tough/1878716666</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/no-hook/1880501939</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/what-he-wrote-transcr-for-guitar-by-rosie-bennet/1868980382</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/mean-2-me/1861088760</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/captain-kernel/1868763228</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/nothings-what-it-seems/1872820240</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/no-need-for-leavin/1878743975</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/ii-in-the-gut-of-the-wolf/1867614406</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/poison-icon/1847941146</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/lay-down-your-soul/1872651251</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/ghost-notes/1862229148</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-06</v>
+        <v>2026-03-07</v>
       </c>
       <c r="E98" t="str">
         <v/>
